--- a/tests/oracle/ORACULO_sim1.xlsx
+++ b/tests/oracle/ORACULO_sim1.xlsx
@@ -4444,7 +4444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EZ5"/>
+  <dimension ref="A1:GV5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="184" min="1" max="1"/>
@@ -5386,6 +5386,246 @@
           <t>CONS-08</t>
         </is>
       </c>
+      <c r="FA1" t="inlineStr">
+        <is>
+          <t>capitalInicial</t>
+        </is>
+      </c>
+      <c r="FB1" t="inlineStr">
+        <is>
+          <t>compraActivos</t>
+        </is>
+      </c>
+      <c r="FC1" t="inlineStr">
+        <is>
+          <t>adquisicionNeta</t>
+        </is>
+      </c>
+      <c r="FD1" t="inlineStr">
+        <is>
+          <t>valorCompradoNeto</t>
+        </is>
+      </c>
+      <c r="FE1" t="inlineStr">
+        <is>
+          <t>valorInventarioNeto</t>
+        </is>
+      </c>
+      <c r="FF1" t="inlineStr">
+        <is>
+          <t>cajaInicial</t>
+        </is>
+      </c>
+      <c r="FG1" t="inlineStr">
+        <is>
+          <t>tasaNuevoPrestamo</t>
+        </is>
+      </c>
+      <c r="FH1" t="inlineStr">
+        <is>
+          <t>interesMensual</t>
+        </is>
+      </c>
+      <c r="FI1" t="inlineStr">
+        <is>
+          <t>tasaMensual</t>
+        </is>
+      </c>
+      <c r="FJ1" t="inlineStr">
+        <is>
+          <t>intereses</t>
+        </is>
+      </c>
+      <c r="FK1" t="inlineStr">
+        <is>
+          <t>pagosOperacion</t>
+        </is>
+      </c>
+      <c r="FL1" t="inlineStr">
+        <is>
+          <t>cajaFinal</t>
+        </is>
+      </c>
+      <c r="FM1" t="inlineStr">
+        <is>
+          <t>depreciacionAcumulada</t>
+        </is>
+      </c>
+      <c r="FN1" t="inlineStr">
+        <is>
+          <t>activosCosto</t>
+        </is>
+      </c>
+      <c r="FO1" t="inlineStr">
+        <is>
+          <t>activosFijos</t>
+        </is>
+      </c>
+      <c r="FP1" t="inlineStr">
+        <is>
+          <t>financial.estadoResultados.ingresos</t>
+        </is>
+      </c>
+      <c r="FQ1" t="inlineStr">
+        <is>
+          <t>financial.estadoResultados.ventasNetas</t>
+        </is>
+      </c>
+      <c r="FR1" t="inlineStr">
+        <is>
+          <t>financial.estadoResultados.costos</t>
+        </is>
+      </c>
+      <c r="FS1" t="inlineStr">
+        <is>
+          <t>financial.estadoResultados.utilidad</t>
+        </is>
+      </c>
+      <c r="FT1" t="inlineStr">
+        <is>
+          <t>financial.estadoResultados.depreciacion</t>
+        </is>
+      </c>
+      <c r="FU1" t="inlineStr">
+        <is>
+          <t>financial.estadoResultados.intereses</t>
+        </is>
+      </c>
+      <c r="FV1" t="inlineStr">
+        <is>
+          <t>financial.estadoResultados.costosProduccion</t>
+        </is>
+      </c>
+      <c r="FW1" t="inlineStr">
+        <is>
+          <t>financial.balanceCaja.cajaInicial</t>
+        </is>
+      </c>
+      <c r="FX1" t="inlineStr">
+        <is>
+          <t>financial.balanceCaja.entradas</t>
+        </is>
+      </c>
+      <c r="FY1" t="inlineStr">
+        <is>
+          <t>financial.balanceCaja.salidas</t>
+        </is>
+      </c>
+      <c r="FZ1" t="inlineStr">
+        <is>
+          <t>financial.balanceCaja.cajaFinal</t>
+        </is>
+      </c>
+      <c r="GA1" t="inlineStr">
+        <is>
+          <t>financial.flujoCaja.cajaInicial</t>
+        </is>
+      </c>
+      <c r="GB1" t="inlineStr">
+        <is>
+          <t>financial.flujoCaja.cobrosVentas</t>
+        </is>
+      </c>
+      <c r="GC1" t="inlineStr">
+        <is>
+          <t>financial.flujoCaja.pagosOperacion</t>
+        </is>
+      </c>
+      <c r="GD1" t="inlineStr">
+        <is>
+          <t>financial.flujoCaja.compraActivos</t>
+        </is>
+      </c>
+      <c r="GE1" t="inlineStr">
+        <is>
+          <t>financial.flujoCaja.financiamiento</t>
+        </is>
+      </c>
+      <c r="GF1" t="inlineStr">
+        <is>
+          <t>financial.flujoCaja.operacion</t>
+        </is>
+      </c>
+      <c r="GG1" t="inlineStr">
+        <is>
+          <t>financial.flujoCaja.inversion</t>
+        </is>
+      </c>
+      <c r="GH1" t="inlineStr">
+        <is>
+          <t>financial.flujoCaja.flujoNeto</t>
+        </is>
+      </c>
+      <c r="GI1" t="inlineStr">
+        <is>
+          <t>financial.flujoCaja.cajaFinal</t>
+        </is>
+      </c>
+      <c r="GJ1" t="inlineStr">
+        <is>
+          <t>financial.balanceGeneral.efectivo</t>
+        </is>
+      </c>
+      <c r="GK1" t="inlineStr">
+        <is>
+          <t>financial.balanceGeneral.activosFijos</t>
+        </is>
+      </c>
+      <c r="GL1" t="inlineStr">
+        <is>
+          <t>financial.balanceGeneral.inventarioMP</t>
+        </is>
+      </c>
+      <c r="GM1" t="inlineStr">
+        <is>
+          <t>financial.balanceGeneral.activos</t>
+        </is>
+      </c>
+      <c r="GN1" t="inlineStr">
+        <is>
+          <t>financial.balanceGeneral.deuda</t>
+        </is>
+      </c>
+      <c r="GO1" t="inlineStr">
+        <is>
+          <t>financial.balanceGeneral.patrimonio</t>
+        </is>
+      </c>
+      <c r="GP1" t="inlineStr">
+        <is>
+          <t>financial.balanceGeneral.pasivoPatrimonio</t>
+        </is>
+      </c>
+      <c r="GQ1" t="inlineStr">
+        <is>
+          <t>financial.financiamiento.montoPrestamo</t>
+        </is>
+      </c>
+      <c r="GR1" t="inlineStr">
+        <is>
+          <t>financial.financiamiento.tasaTEA</t>
+        </is>
+      </c>
+      <c r="GS1" t="inlineStr">
+        <is>
+          <t>financial.financiamiento.deudaPrincipal</t>
+        </is>
+      </c>
+      <c r="GT1" t="inlineStr">
+        <is>
+          <t>financial.financiamiento.tasaAdicionalProximoPrestamo</t>
+        </is>
+      </c>
+      <c r="GU1" t="inlineStr">
+        <is>
+          <t>financial.financiamiento.tasaMensual</t>
+        </is>
+      </c>
+      <c r="GV1" t="inlineStr">
+        <is>
+          <t>financial.financiamiento.intereses</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="n">
@@ -5978,6 +6218,197 @@
         <f>AND(K2=0,AF2&lt;5)</f>
         <v/>
       </c>
+      <c r="FA2" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="FB2">
+        <f>1*2500*(1+0.03+0.02)+1*3500*(1+0.03+0.02)+1*1200*(1+0.03+0.02)+1*300*(1+0+0.01)</f>
+        <v/>
+      </c>
+      <c r="FC2">
+        <f>1*2500+1*3500+1*1200+1*300</f>
+        <v/>
+      </c>
+      <c r="FD2">
+        <f>(CF2*25+CH2*45+CJ2*80+CL2*4+CN2*9+CP2*2+CR2*4+CT2*7)*0.8924</f>
+        <v/>
+      </c>
+      <c r="FE2">
+        <f>(DC2*25+DE2*45+DG2*80+DJ2*4+DL2*9+DO2*2+DQ2*4+DS2*7)*0.8924</f>
+        <v/>
+      </c>
+      <c r="FF2">
+        <f>FA2</f>
+        <v/>
+      </c>
+      <c r="FG2">
+        <f>(1+AR2/100)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="FH2">
+        <f>0*0+AP2*FG2</f>
+        <v/>
+      </c>
+      <c r="FI2">
+        <f>IFERROR(FH2/(0+AP2),0)</f>
+        <v/>
+      </c>
+      <c r="FJ2">
+        <f>FH2*1</f>
+        <v/>
+      </c>
+      <c r="FK2">
+        <f>EQ2-DW2-DU2+FD2+FJ2</f>
+        <v/>
+      </c>
+      <c r="FL2">
+        <f>FF2+EJ2+AP2-FK2-FB2</f>
+        <v/>
+      </c>
+      <c r="FM2">
+        <f>0+DW2</f>
+        <v/>
+      </c>
+      <c r="FN2">
+        <f>0+FC2</f>
+        <v/>
+      </c>
+      <c r="FO2">
+        <f>FN2-FM2</f>
+        <v/>
+      </c>
+      <c r="FP2">
+        <f>EJ2</f>
+        <v/>
+      </c>
+      <c r="FQ2">
+        <f>EJ2</f>
+        <v/>
+      </c>
+      <c r="FR2">
+        <f>EQ2+FJ2</f>
+        <v/>
+      </c>
+      <c r="FS2">
+        <f>ER2-FJ2</f>
+        <v/>
+      </c>
+      <c r="FT2">
+        <f>DW2</f>
+        <v/>
+      </c>
+      <c r="FU2">
+        <f>FJ2</f>
+        <v/>
+      </c>
+      <c r="FV2">
+        <f>EQ2</f>
+        <v/>
+      </c>
+      <c r="FW2">
+        <f>FF2</f>
+        <v/>
+      </c>
+      <c r="FX2">
+        <f>EJ2+AP2</f>
+        <v/>
+      </c>
+      <c r="FY2">
+        <f>FK2+FB2</f>
+        <v/>
+      </c>
+      <c r="FZ2">
+        <f>FL2</f>
+        <v/>
+      </c>
+      <c r="GA2">
+        <f>FF2</f>
+        <v/>
+      </c>
+      <c r="GB2">
+        <f>EJ2</f>
+        <v/>
+      </c>
+      <c r="GC2">
+        <f>FK2</f>
+        <v/>
+      </c>
+      <c r="GD2">
+        <f>FB2</f>
+        <v/>
+      </c>
+      <c r="GE2">
+        <f>AP2</f>
+        <v/>
+      </c>
+      <c r="GF2">
+        <f>EJ2-FK2</f>
+        <v/>
+      </c>
+      <c r="GG2">
+        <f>-FB2</f>
+        <v/>
+      </c>
+      <c r="GH2">
+        <f>FL2-FF2</f>
+        <v/>
+      </c>
+      <c r="GI2">
+        <f>FL2</f>
+        <v/>
+      </c>
+      <c r="GJ2">
+        <f>FL2</f>
+        <v/>
+      </c>
+      <c r="GK2">
+        <f>FO2</f>
+        <v/>
+      </c>
+      <c r="GL2">
+        <f>FE2</f>
+        <v/>
+      </c>
+      <c r="GM2">
+        <f>FL2+FO2+FE2</f>
+        <v/>
+      </c>
+      <c r="GN2">
+        <f>AS2</f>
+        <v/>
+      </c>
+      <c r="GO2">
+        <f>FL2+FO2+FE2-AS2</f>
+        <v/>
+      </c>
+      <c r="GP2">
+        <f>FL2+FO2+FE2</f>
+        <v/>
+      </c>
+      <c r="GQ2">
+        <f>AP2</f>
+        <v/>
+      </c>
+      <c r="GR2">
+        <f>AR2</f>
+        <v/>
+      </c>
+      <c r="GS2">
+        <f>AS2</f>
+        <v/>
+      </c>
+      <c r="GT2">
+        <f>AT2</f>
+        <v/>
+      </c>
+      <c r="GU2">
+        <f>FI2</f>
+        <v/>
+      </c>
+      <c r="GV2">
+        <f>FJ2</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="n">
@@ -6570,6 +7001,197 @@
         <f>AND(K3=0,AF3&lt;5)</f>
         <v/>
       </c>
+      <c r="FA3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="FB3">
+        <f>1*2500*(1+0.03+0.02)+1*3500*(1+0.03+0.02)+1*1200*(1+0.03+0.02)+1*300*(1+0+0.01)</f>
+        <v/>
+      </c>
+      <c r="FC3">
+        <f>1*2500+1*3500+1*1200+1*300</f>
+        <v/>
+      </c>
+      <c r="FD3">
+        <f>(CF3*25+CH3*45+CJ3*80+CL3*4+CN3*9+CP3*2+CR3*4+CT3*7)*0.8924</f>
+        <v/>
+      </c>
+      <c r="FE3">
+        <f>(DC3*25+DE3*45+DG3*80+DJ3*4+DL3*9+DO3*2+DQ3*4+DS3*7)*0.8924</f>
+        <v/>
+      </c>
+      <c r="FF3">
+        <f>FA3</f>
+        <v/>
+      </c>
+      <c r="FG3">
+        <f>(1+AR3/100)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="FH3">
+        <f>0*0+AP3*FG3</f>
+        <v/>
+      </c>
+      <c r="FI3">
+        <f>IFERROR(FH3/(0+AP3),0)</f>
+        <v/>
+      </c>
+      <c r="FJ3">
+        <f>FH3*1</f>
+        <v/>
+      </c>
+      <c r="FK3">
+        <f>EQ3-DW3-DU3+FD3+FJ3</f>
+        <v/>
+      </c>
+      <c r="FL3">
+        <f>FF3+EJ3+AP3-FK3-FB3</f>
+        <v/>
+      </c>
+      <c r="FM3">
+        <f>0+DW3</f>
+        <v/>
+      </c>
+      <c r="FN3">
+        <f>0+FC3</f>
+        <v/>
+      </c>
+      <c r="FO3">
+        <f>FN3-FM3</f>
+        <v/>
+      </c>
+      <c r="FP3">
+        <f>EJ3</f>
+        <v/>
+      </c>
+      <c r="FQ3">
+        <f>EJ3</f>
+        <v/>
+      </c>
+      <c r="FR3">
+        <f>EQ3+FJ3</f>
+        <v/>
+      </c>
+      <c r="FS3">
+        <f>ER3-FJ3</f>
+        <v/>
+      </c>
+      <c r="FT3">
+        <f>DW3</f>
+        <v/>
+      </c>
+      <c r="FU3">
+        <f>FJ3</f>
+        <v/>
+      </c>
+      <c r="FV3">
+        <f>EQ3</f>
+        <v/>
+      </c>
+      <c r="FW3">
+        <f>FF3</f>
+        <v/>
+      </c>
+      <c r="FX3">
+        <f>EJ3+AP3</f>
+        <v/>
+      </c>
+      <c r="FY3">
+        <f>FK3+FB3</f>
+        <v/>
+      </c>
+      <c r="FZ3">
+        <f>FL3</f>
+        <v/>
+      </c>
+      <c r="GA3">
+        <f>FF3</f>
+        <v/>
+      </c>
+      <c r="GB3">
+        <f>EJ3</f>
+        <v/>
+      </c>
+      <c r="GC3">
+        <f>FK3</f>
+        <v/>
+      </c>
+      <c r="GD3">
+        <f>FB3</f>
+        <v/>
+      </c>
+      <c r="GE3">
+        <f>AP3</f>
+        <v/>
+      </c>
+      <c r="GF3">
+        <f>EJ3-FK3</f>
+        <v/>
+      </c>
+      <c r="GG3">
+        <f>-FB3</f>
+        <v/>
+      </c>
+      <c r="GH3">
+        <f>FL3-FF3</f>
+        <v/>
+      </c>
+      <c r="GI3">
+        <f>FL3</f>
+        <v/>
+      </c>
+      <c r="GJ3">
+        <f>FL3</f>
+        <v/>
+      </c>
+      <c r="GK3">
+        <f>FO3</f>
+        <v/>
+      </c>
+      <c r="GL3">
+        <f>FE3</f>
+        <v/>
+      </c>
+      <c r="GM3">
+        <f>FL3+FO3+FE3</f>
+        <v/>
+      </c>
+      <c r="GN3">
+        <f>AS3</f>
+        <v/>
+      </c>
+      <c r="GO3">
+        <f>FL3+FO3+FE3-AS3</f>
+        <v/>
+      </c>
+      <c r="GP3">
+        <f>FL3+FO3+FE3</f>
+        <v/>
+      </c>
+      <c r="GQ3">
+        <f>AP3</f>
+        <v/>
+      </c>
+      <c r="GR3">
+        <f>AR3</f>
+        <v/>
+      </c>
+      <c r="GS3">
+        <f>AS3</f>
+        <v/>
+      </c>
+      <c r="GT3">
+        <f>AT3</f>
+        <v/>
+      </c>
+      <c r="GU3">
+        <f>FI3</f>
+        <v/>
+      </c>
+      <c r="GV3">
+        <f>FJ3</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
@@ -7162,6 +7784,197 @@
         <f>AND(K4=0,AF4&lt;5)</f>
         <v/>
       </c>
+      <c r="FA4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="FB4">
+        <f>1*2500*(1+0.03+0.02)+1*3500*(1+0.03+0.02)+1*1200*(1+0.03+0.02)+1*300*(1+0+0.01)</f>
+        <v/>
+      </c>
+      <c r="FC4">
+        <f>1*2500+1*3500+1*1200+1*300</f>
+        <v/>
+      </c>
+      <c r="FD4">
+        <f>(CF4*25+CH4*45+CJ4*80+CL4*4+CN4*9+CP4*2+CR4*4+CT4*7)*0.8924</f>
+        <v/>
+      </c>
+      <c r="FE4">
+        <f>(DC4*25+DE4*45+DG4*80+DJ4*4+DL4*9+DO4*2+DQ4*4+DS4*7)*0.8924</f>
+        <v/>
+      </c>
+      <c r="FF4">
+        <f>FA4</f>
+        <v/>
+      </c>
+      <c r="FG4">
+        <f>(1+AR4/100)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="FH4">
+        <f>0*0+AP4*FG4</f>
+        <v/>
+      </c>
+      <c r="FI4">
+        <f>IFERROR(FH4/(0+AP4),0)</f>
+        <v/>
+      </c>
+      <c r="FJ4">
+        <f>FH4*1</f>
+        <v/>
+      </c>
+      <c r="FK4">
+        <f>EQ4-DW4-DU4+FD4+FJ4</f>
+        <v/>
+      </c>
+      <c r="FL4">
+        <f>FF4+EJ4+AP4-FK4-FB4</f>
+        <v/>
+      </c>
+      <c r="FM4">
+        <f>0+DW4</f>
+        <v/>
+      </c>
+      <c r="FN4">
+        <f>0+FC4</f>
+        <v/>
+      </c>
+      <c r="FO4">
+        <f>FN4-FM4</f>
+        <v/>
+      </c>
+      <c r="FP4">
+        <f>EJ4</f>
+        <v/>
+      </c>
+      <c r="FQ4">
+        <f>EJ4</f>
+        <v/>
+      </c>
+      <c r="FR4">
+        <f>EQ4+FJ4</f>
+        <v/>
+      </c>
+      <c r="FS4">
+        <f>ER4-FJ4</f>
+        <v/>
+      </c>
+      <c r="FT4">
+        <f>DW4</f>
+        <v/>
+      </c>
+      <c r="FU4">
+        <f>FJ4</f>
+        <v/>
+      </c>
+      <c r="FV4">
+        <f>EQ4</f>
+        <v/>
+      </c>
+      <c r="FW4">
+        <f>FF4</f>
+        <v/>
+      </c>
+      <c r="FX4">
+        <f>EJ4+AP4</f>
+        <v/>
+      </c>
+      <c r="FY4">
+        <f>FK4+FB4</f>
+        <v/>
+      </c>
+      <c r="FZ4">
+        <f>FL4</f>
+        <v/>
+      </c>
+      <c r="GA4">
+        <f>FF4</f>
+        <v/>
+      </c>
+      <c r="GB4">
+        <f>EJ4</f>
+        <v/>
+      </c>
+      <c r="GC4">
+        <f>FK4</f>
+        <v/>
+      </c>
+      <c r="GD4">
+        <f>FB4</f>
+        <v/>
+      </c>
+      <c r="GE4">
+        <f>AP4</f>
+        <v/>
+      </c>
+      <c r="GF4">
+        <f>EJ4-FK4</f>
+        <v/>
+      </c>
+      <c r="GG4">
+        <f>-FB4</f>
+        <v/>
+      </c>
+      <c r="GH4">
+        <f>FL4-FF4</f>
+        <v/>
+      </c>
+      <c r="GI4">
+        <f>FL4</f>
+        <v/>
+      </c>
+      <c r="GJ4">
+        <f>FL4</f>
+        <v/>
+      </c>
+      <c r="GK4">
+        <f>FO4</f>
+        <v/>
+      </c>
+      <c r="GL4">
+        <f>FE4</f>
+        <v/>
+      </c>
+      <c r="GM4">
+        <f>FL4+FO4+FE4</f>
+        <v/>
+      </c>
+      <c r="GN4">
+        <f>AS4</f>
+        <v/>
+      </c>
+      <c r="GO4">
+        <f>FL4+FO4+FE4-AS4</f>
+        <v/>
+      </c>
+      <c r="GP4">
+        <f>FL4+FO4+FE4</f>
+        <v/>
+      </c>
+      <c r="GQ4">
+        <f>AP4</f>
+        <v/>
+      </c>
+      <c r="GR4">
+        <f>AR4</f>
+        <v/>
+      </c>
+      <c r="GS4">
+        <f>AS4</f>
+        <v/>
+      </c>
+      <c r="GT4">
+        <f>AT4</f>
+        <v/>
+      </c>
+      <c r="GU4">
+        <f>FI4</f>
+        <v/>
+      </c>
+      <c r="GV4">
+        <f>FJ4</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
@@ -7752,6 +8565,197 @@
       </c>
       <c r="EZ5" s="0">
         <f>AND(K5=0,AF5&lt;5)</f>
+        <v/>
+      </c>
+      <c r="FA5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="FB5">
+        <f>1*2500*(1+0.03+0.02)+1*3500*(1+0.03+0.02)+1*1200*(1+0.03+0.02)+1*300*(1+0+0.01)</f>
+        <v/>
+      </c>
+      <c r="FC5">
+        <f>1*2500+1*3500+1*1200+1*300</f>
+        <v/>
+      </c>
+      <c r="FD5">
+        <f>(CF5*25+CH5*45+CJ5*80+CL5*4+CN5*9+CP5*2+CR5*4+CT5*7)*0.8924</f>
+        <v/>
+      </c>
+      <c r="FE5">
+        <f>(DC5*25+DE5*45+DG5*80+DJ5*4+DL5*9+DO5*2+DQ5*4+DS5*7)*0.8924</f>
+        <v/>
+      </c>
+      <c r="FF5">
+        <f>FA5</f>
+        <v/>
+      </c>
+      <c r="FG5">
+        <f>(1+AR5/100)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="FH5">
+        <f>0*0+AP5*FG5</f>
+        <v/>
+      </c>
+      <c r="FI5">
+        <f>IFERROR(FH5/(0+AP5),0)</f>
+        <v/>
+      </c>
+      <c r="FJ5">
+        <f>FH5*1</f>
+        <v/>
+      </c>
+      <c r="FK5">
+        <f>EQ5-DW5-DU5+FD5+FJ5</f>
+        <v/>
+      </c>
+      <c r="FL5">
+        <f>FF5+EJ5+AP5-FK5-FB5</f>
+        <v/>
+      </c>
+      <c r="FM5">
+        <f>0+DW5</f>
+        <v/>
+      </c>
+      <c r="FN5">
+        <f>0+FC5</f>
+        <v/>
+      </c>
+      <c r="FO5">
+        <f>FN5-FM5</f>
+        <v/>
+      </c>
+      <c r="FP5">
+        <f>EJ5</f>
+        <v/>
+      </c>
+      <c r="FQ5">
+        <f>EJ5</f>
+        <v/>
+      </c>
+      <c r="FR5">
+        <f>EQ5+FJ5</f>
+        <v/>
+      </c>
+      <c r="FS5">
+        <f>ER5-FJ5</f>
+        <v/>
+      </c>
+      <c r="FT5">
+        <f>DW5</f>
+        <v/>
+      </c>
+      <c r="FU5">
+        <f>FJ5</f>
+        <v/>
+      </c>
+      <c r="FV5">
+        <f>EQ5</f>
+        <v/>
+      </c>
+      <c r="FW5">
+        <f>FF5</f>
+        <v/>
+      </c>
+      <c r="FX5">
+        <f>EJ5+AP5</f>
+        <v/>
+      </c>
+      <c r="FY5">
+        <f>FK5+FB5</f>
+        <v/>
+      </c>
+      <c r="FZ5">
+        <f>FL5</f>
+        <v/>
+      </c>
+      <c r="GA5">
+        <f>FF5</f>
+        <v/>
+      </c>
+      <c r="GB5">
+        <f>EJ5</f>
+        <v/>
+      </c>
+      <c r="GC5">
+        <f>FK5</f>
+        <v/>
+      </c>
+      <c r="GD5">
+        <f>FB5</f>
+        <v/>
+      </c>
+      <c r="GE5">
+        <f>AP5</f>
+        <v/>
+      </c>
+      <c r="GF5">
+        <f>EJ5-FK5</f>
+        <v/>
+      </c>
+      <c r="GG5">
+        <f>-FB5</f>
+        <v/>
+      </c>
+      <c r="GH5">
+        <f>FL5-FF5</f>
+        <v/>
+      </c>
+      <c r="GI5">
+        <f>FL5</f>
+        <v/>
+      </c>
+      <c r="GJ5">
+        <f>FL5</f>
+        <v/>
+      </c>
+      <c r="GK5">
+        <f>FO5</f>
+        <v/>
+      </c>
+      <c r="GL5">
+        <f>FE5</f>
+        <v/>
+      </c>
+      <c r="GM5">
+        <f>FL5+FO5+FE5</f>
+        <v/>
+      </c>
+      <c r="GN5">
+        <f>AS5</f>
+        <v/>
+      </c>
+      <c r="GO5">
+        <f>FL5+FO5+FE5-AS5</f>
+        <v/>
+      </c>
+      <c r="GP5">
+        <f>FL5+FO5+FE5</f>
+        <v/>
+      </c>
+      <c r="GQ5">
+        <f>AP5</f>
+        <v/>
+      </c>
+      <c r="GR5">
+        <f>AR5</f>
+        <v/>
+      </c>
+      <c r="GS5">
+        <f>AS5</f>
+        <v/>
+      </c>
+      <c r="GT5">
+        <f>AT5</f>
+        <v/>
+      </c>
+      <c r="GU5">
+        <f>FI5</f>
+        <v/>
+      </c>
+      <c r="GV5">
+        <f>FJ5</f>
         <v/>
       </c>
     </row>
@@ -11287,2766 +12291,2766 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>ciclo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>empresa</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>segmento</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>molde</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>cuero</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>accesorios</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>hilo</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>cantidad</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="0" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="0" t="inlineStr">
         <is>
           <t>calidad</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="0" t="inlineStr">
         <is>
           <t>disponible_INS-01</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t>disponible_INS-02</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="0" t="inlineStr">
         <is>
           <t>disponible_INS-03</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>disponible_INS-04</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="0" t="inlineStr">
         <is>
           <t>disponible_INS-05</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>disponible_INS-06</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>disponible_INS-07</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="0" t="inlineStr">
         <is>
           <t>disponible_INS-08</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="0" t="inlineStr">
         <is>
           <t>capacidadAsignada</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="0" t="inlineStr">
         <is>
           <t>producidoPre</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="0" t="inlineStr">
         <is>
           <t>producido</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="0" t="inlineStr">
         <is>
           <t>usadoPre_INS-01</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="0" t="inlineStr">
         <is>
           <t>saldoPre_INS-01</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="0" t="inlineStr">
         <is>
           <t>usado_INS-01</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="0" t="inlineStr">
         <is>
           <t>usadoPre_INS-02</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="0" t="inlineStr">
         <is>
           <t>saldoPre_INS-02</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="0" t="inlineStr">
         <is>
           <t>usado_INS-02</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="0" t="inlineStr">
         <is>
           <t>usadoPre_INS-03</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="0" t="inlineStr">
         <is>
           <t>saldoPre_INS-03</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="0" t="inlineStr">
         <is>
           <t>usado_INS-03</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="0" t="inlineStr">
         <is>
           <t>usadoPre_INS-04</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="0" t="inlineStr">
         <is>
           <t>saldoPre_INS-04</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="0" t="inlineStr">
         <is>
           <t>usado_INS-04</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="0" t="inlineStr">
         <is>
           <t>usadoPre_INS-05</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="0" t="inlineStr">
         <is>
           <t>saldoPre_INS-05</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="0" t="inlineStr">
         <is>
           <t>usado_INS-05</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="0" t="inlineStr">
         <is>
           <t>usadoPre_INS-06</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="0" t="inlineStr">
         <is>
           <t>saldoPre_INS-06</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="0" t="inlineStr">
         <is>
           <t>usado_INS-06</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="0" t="inlineStr">
         <is>
           <t>usadoPre_INS-07</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="0" t="inlineStr">
         <is>
           <t>saldoPre_INS-07</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="0" t="inlineStr">
         <is>
           <t>usado_INS-07</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="0" t="inlineStr">
         <is>
           <t>usadoPre_INS-08</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="0" t="inlineStr">
         <is>
           <t>saldoPre_INS-08</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="0" t="inlineStr">
         <is>
           <t>usado_INS-08</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="0" t="inlineStr">
         <is>
           <t>precioFactor</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="0" t="inlineStr">
         <is>
           <t>precioEfectivo</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="0" t="inlineStr">
         <is>
           <t>stockAntes</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="0" t="inlineStr">
         <is>
           <t>vendido</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="0" t="inlineStr">
         <is>
           <t>ingreso</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="0" t="inlineStr">
         <is>
           <t>inventarioFinal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>SEG-01</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>INF-08</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>INS-01</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>INS-04</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>INS-06</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(E2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(F2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(G2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(D2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="K2">
+      <c r="K2" s="0">
         <f>'Pipeline_sim1'!CG2</f>
         <v/>
       </c>
-      <c r="L2">
+      <c r="L2" s="0">
         <f>'Pipeline_sim1'!CI2</f>
         <v/>
       </c>
-      <c r="M2">
+      <c r="M2" s="0">
         <f>'Pipeline_sim1'!CK2</f>
         <v/>
       </c>
-      <c r="N2">
+      <c r="N2" s="0">
         <f>'Pipeline_sim1'!CM2</f>
         <v/>
       </c>
-      <c r="O2">
+      <c r="O2" s="0">
         <f>'Pipeline_sim1'!CO2</f>
         <v/>
       </c>
-      <c r="P2">
+      <c r="P2" s="0">
         <f>'Pipeline_sim1'!CQ2</f>
         <v/>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="0">
         <f>'Pipeline_sim1'!CS2</f>
         <v/>
       </c>
-      <c r="R2">
+      <c r="R2" s="0">
         <f>'Pipeline_sim1'!CU2</f>
         <v/>
       </c>
-      <c r="S2">
+      <c r="S2" s="0">
         <f>IFERROR(ROUNDDOWN(H2*'Pipeline_sim1'!CE2/'Pipeline_sim1'!I2,0),0)</f>
         <v/>
       </c>
-      <c r="T2">
+      <c r="T2" s="0">
         <f>ROUNDDOWN(MIN(H2,S2,(K2)/0.3,(N2)/1,(P2)/6),0)</f>
         <v/>
       </c>
-      <c r="U2">
+      <c r="U2" s="0">
         <f>ROUNDDOWN(T2*'Pipeline_sim1'!AU2,0)</f>
         <v/>
       </c>
-      <c r="V2">
+      <c r="V2" s="0">
         <f>MIN(K2,MAX(0,T2*0.3))</f>
         <v/>
       </c>
-      <c r="W2">
+      <c r="W2" s="0">
         <f>K2-V2</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X2" s="0">
         <f>IFERROR(V2*U2/T2,0)</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y2" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="0">
         <f>L2-Y2</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA2" s="0">
         <f>IFERROR(Y2*U2/T2,0)</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB2" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>M2-AB2</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD2" s="0">
         <f>IFERROR(AB2*U2/T2,0)</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE2" s="0">
         <f>MIN(N2,MAX(0,T2*1))</f>
         <v/>
       </c>
-      <c r="AF2">
+      <c r="AF2" s="0">
         <f>N2-AE2</f>
         <v/>
       </c>
-      <c r="AG2">
+      <c r="AG2" s="0">
         <f>IFERROR(AE2*U2/T2,0)</f>
         <v/>
       </c>
-      <c r="AH2">
+      <c r="AH2" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AI2">
+      <c r="AI2" s="0">
         <f>O2-AH2</f>
         <v/>
       </c>
-      <c r="AJ2">
+      <c r="AJ2" s="0">
         <f>IFERROR(AH2*U2/T2,0)</f>
         <v/>
       </c>
-      <c r="AK2">
+      <c r="AK2" s="0">
         <f>MIN(P2,MAX(0,T2*6))</f>
         <v/>
       </c>
-      <c r="AL2">
+      <c r="AL2" s="0">
         <f>P2-AK2</f>
         <v/>
       </c>
-      <c r="AM2">
+      <c r="AM2" s="0">
         <f>IFERROR(AK2*U2/T2,0)</f>
         <v/>
       </c>
-      <c r="AN2">
+      <c r="AN2" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AO2">
+      <c r="AO2" s="0">
         <f>Q2-AN2</f>
         <v/>
       </c>
-      <c r="AP2">
+      <c r="AP2" s="0">
         <f>IFERROR(AN2*U2/T2,0)</f>
         <v/>
       </c>
-      <c r="AQ2">
+      <c r="AQ2" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AR2">
+      <c r="AR2" s="0">
         <f>R2-AQ2</f>
         <v/>
       </c>
-      <c r="AS2">
+      <c r="AS2" s="0">
         <f>IFERROR(AQ2*U2/T2,0)</f>
         <v/>
       </c>
-      <c r="AT2">
+      <c r="AT2" s="0">
         <f>IF(AND(C2="SEG-03",H2&gt;0),IF(J2&lt;4,0.65,IF(J2&gt;=7,1.4,1)),1)</f>
         <v/>
       </c>
-      <c r="AU2">
+      <c r="AU2" s="0">
         <f>I2*AT2</f>
         <v/>
       </c>
-      <c r="AV2">
+      <c r="AV2" s="0">
         <f>0+U2</f>
         <v/>
       </c>
-      <c r="AW2">
+      <c r="AW2" s="0">
         <f>MIN(AV2,MAX(0,'Mercados_Pipeline_sim1'!I2))</f>
         <v/>
       </c>
-      <c r="AX2">
+      <c r="AX2" s="0">
         <f>AW2*AU2</f>
         <v/>
       </c>
-      <c r="AY2">
+      <c r="AY2" s="0">
         <f>AV2-AW2</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>SEG-02</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>INF-09</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>INS-02</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>INS-04</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>INS-07</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="0" t="n">
         <v>120</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(E3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(F3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(G3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(D3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="K3">
+      <c r="K3" s="0">
         <f>'Lotes_Pipeline_sim1'!W2</f>
         <v/>
       </c>
-      <c r="L3">
+      <c r="L3" s="0">
         <f>'Lotes_Pipeline_sim1'!Z2</f>
         <v/>
       </c>
-      <c r="M3">
+      <c r="M3" s="0">
         <f>'Lotes_Pipeline_sim1'!AC2</f>
         <v/>
       </c>
-      <c r="N3">
+      <c r="N3" s="0">
         <f>'Lotes_Pipeline_sim1'!AF2</f>
         <v/>
       </c>
-      <c r="O3">
+      <c r="O3" s="0">
         <f>'Lotes_Pipeline_sim1'!AI2</f>
         <v/>
       </c>
-      <c r="P3">
+      <c r="P3" s="0">
         <f>'Lotes_Pipeline_sim1'!AL2</f>
         <v/>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="0">
         <f>'Lotes_Pipeline_sim1'!AO2</f>
         <v/>
       </c>
-      <c r="R3">
+      <c r="R3" s="0">
         <f>'Lotes_Pipeline_sim1'!AR2</f>
         <v/>
       </c>
-      <c r="S3">
+      <c r="S3" s="0">
         <f>IFERROR(ROUNDDOWN(H3*'Pipeline_sim1'!CE2/'Pipeline_sim1'!I2,0),0)</f>
         <v/>
       </c>
-      <c r="T3">
+      <c r="T3" s="0">
         <f>ROUNDDOWN(MIN(H3,S3,(L3)/0.4,(N3)/1,(Q3)/7),0)</f>
         <v/>
       </c>
-      <c r="U3">
+      <c r="U3" s="0">
         <f>ROUNDDOWN(T3*'Pipeline_sim1'!AU2,0)</f>
         <v/>
       </c>
-      <c r="V3">
+      <c r="V3" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="W3">
+      <c r="W3" s="0">
         <f>K3-V3</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X3" s="0">
         <f>IFERROR(V3*U3/T3,0)</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y3" s="0">
         <f>MIN(L3,MAX(0,T3*0.4-(V3)))</f>
         <v/>
       </c>
-      <c r="Z3">
+      <c r="Z3" s="0">
         <f>L3-Y3</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA3" s="0">
         <f>IFERROR(Y3*U3/T3,0)</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB3" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="0">
         <f>M3-AB3</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD3" s="0">
         <f>IFERROR(AB3*U3/T3,0)</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE3" s="0">
         <f>MIN(N3,MAX(0,T3*1))</f>
         <v/>
       </c>
-      <c r="AF3">
+      <c r="AF3" s="0">
         <f>N3-AE3</f>
         <v/>
       </c>
-      <c r="AG3">
+      <c r="AG3" s="0">
         <f>IFERROR(AE3*U3/T3,0)</f>
         <v/>
       </c>
-      <c r="AH3">
+      <c r="AH3" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AI3">
+      <c r="AI3" s="0">
         <f>O3-AH3</f>
         <v/>
       </c>
-      <c r="AJ3">
+      <c r="AJ3" s="0">
         <f>IFERROR(AH3*U3/T3,0)</f>
         <v/>
       </c>
-      <c r="AK3">
+      <c r="AK3" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AL3">
+      <c r="AL3" s="0">
         <f>P3-AK3</f>
         <v/>
       </c>
-      <c r="AM3">
+      <c r="AM3" s="0">
         <f>IFERROR(AK3*U3/T3,0)</f>
         <v/>
       </c>
-      <c r="AN3">
+      <c r="AN3" s="0">
         <f>MIN(Q3,MAX(0,T3*7-(AK3)))</f>
         <v/>
       </c>
-      <c r="AO3">
+      <c r="AO3" s="0">
         <f>Q3-AN3</f>
         <v/>
       </c>
-      <c r="AP3">
+      <c r="AP3" s="0">
         <f>IFERROR(AN3*U3/T3,0)</f>
         <v/>
       </c>
-      <c r="AQ3">
+      <c r="AQ3" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AR3">
+      <c r="AR3" s="0">
         <f>R3-AQ3</f>
         <v/>
       </c>
-      <c r="AS3">
+      <c r="AS3" s="0">
         <f>IFERROR(AQ3*U3/T3,0)</f>
         <v/>
       </c>
-      <c r="AT3">
+      <c r="AT3" s="0">
         <f>IF(AND(C3="SEG-03",H3&gt;0),IF(J3&lt;4,0.65,IF(J3&gt;=7,1.4,1)),1)</f>
         <v/>
       </c>
-      <c r="AU3">
+      <c r="AU3" s="0">
         <f>I3*AT3</f>
         <v/>
       </c>
-      <c r="AV3">
+      <c r="AV3" s="0">
         <f>0+U3</f>
         <v/>
       </c>
-      <c r="AW3">
+      <c r="AW3" s="0">
         <f>MIN(AV3,MAX(0,'Mercados_Pipeline_sim1'!I3))</f>
         <v/>
       </c>
-      <c r="AX3">
+      <c r="AX3" s="0">
         <f>AW3*AU3</f>
         <v/>
       </c>
-      <c r="AY3">
+      <c r="AY3" s="0">
         <f>AV3-AW3</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>SEG-03</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>INF-10</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>INS-03</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>INS-05</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>INS-08</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(E4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(F4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(G4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(D4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="K4">
+      <c r="K4" s="0">
         <f>'Lotes_Pipeline_sim1'!W3</f>
         <v/>
       </c>
-      <c r="L4">
+      <c r="L4" s="0">
         <f>'Lotes_Pipeline_sim1'!Z3</f>
         <v/>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>'Lotes_Pipeline_sim1'!AC3</f>
         <v/>
       </c>
-      <c r="N4">
+      <c r="N4" s="0">
         <f>'Lotes_Pipeline_sim1'!AF3</f>
         <v/>
       </c>
-      <c r="O4">
+      <c r="O4" s="0">
         <f>'Lotes_Pipeline_sim1'!AI3</f>
         <v/>
       </c>
-      <c r="P4">
+      <c r="P4" s="0">
         <f>'Lotes_Pipeline_sim1'!AL3</f>
         <v/>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="0">
         <f>'Lotes_Pipeline_sim1'!AO3</f>
         <v/>
       </c>
-      <c r="R4">
+      <c r="R4" s="0">
         <f>'Lotes_Pipeline_sim1'!AR3</f>
         <v/>
       </c>
-      <c r="S4">
+      <c r="S4" s="0">
         <f>IFERROR(ROUNDDOWN(H4*'Pipeline_sim1'!CE2/'Pipeline_sim1'!I2,0),0)</f>
         <v/>
       </c>
-      <c r="T4">
+      <c r="T4" s="0">
         <f>ROUNDDOWN(MIN(H4,S4,(M4)/0.7,(O4)/1,(R4)/13),0)</f>
         <v/>
       </c>
-      <c r="U4">
+      <c r="U4" s="0">
         <f>ROUNDDOWN(T4*'Pipeline_sim1'!AU2,0)</f>
         <v/>
       </c>
-      <c r="V4">
+      <c r="V4" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="W4">
+      <c r="W4" s="0">
         <f>K4-V4</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X4" s="0">
         <f>IFERROR(V4*U4/T4,0)</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y4" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="Z4" s="0">
         <f>L4-Y4</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA4" s="0">
         <f>IFERROR(Y4*U4/T4,0)</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB4" s="0">
         <f>MIN(M4,MAX(0,T4*0.7-(V4+Y4)))</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="0">
         <f>M4-AB4</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD4" s="0">
         <f>IFERROR(AB4*U4/T4,0)</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE4" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AF4">
+      <c r="AF4" s="0">
         <f>N4-AE4</f>
         <v/>
       </c>
-      <c r="AG4">
+      <c r="AG4" s="0">
         <f>IFERROR(AE4*U4/T4,0)</f>
         <v/>
       </c>
-      <c r="AH4">
+      <c r="AH4" s="0">
         <f>MIN(O4,MAX(0,T4*1-(AE4)))</f>
         <v/>
       </c>
-      <c r="AI4">
+      <c r="AI4" s="0">
         <f>O4-AH4</f>
         <v/>
       </c>
-      <c r="AJ4">
+      <c r="AJ4" s="0">
         <f>IFERROR(AH4*U4/T4,0)</f>
         <v/>
       </c>
-      <c r="AK4">
+      <c r="AK4" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AL4">
+      <c r="AL4" s="0">
         <f>P4-AK4</f>
         <v/>
       </c>
-      <c r="AM4">
+      <c r="AM4" s="0">
         <f>IFERROR(AK4*U4/T4,0)</f>
         <v/>
       </c>
-      <c r="AN4">
+      <c r="AN4" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AO4">
+      <c r="AO4" s="0">
         <f>Q4-AN4</f>
         <v/>
       </c>
-      <c r="AP4">
+      <c r="AP4" s="0">
         <f>IFERROR(AN4*U4/T4,0)</f>
         <v/>
       </c>
-      <c r="AQ4">
+      <c r="AQ4" s="0">
         <f>MIN(R4,MAX(0,T4*13-(AK4+AN4)))</f>
         <v/>
       </c>
-      <c r="AR4">
+      <c r="AR4" s="0">
         <f>R4-AQ4</f>
         <v/>
       </c>
-      <c r="AS4">
+      <c r="AS4" s="0">
         <f>IFERROR(AQ4*U4/T4,0)</f>
         <v/>
       </c>
-      <c r="AT4">
+      <c r="AT4" s="0">
         <f>IF(AND(C4="SEG-03",H4&gt;0),IF(J4&lt;4,0.65,IF(J4&gt;=7,1.4,1)),1)</f>
         <v/>
       </c>
-      <c r="AU4">
+      <c r="AU4" s="0">
         <f>I4*AT4</f>
         <v/>
       </c>
-      <c r="AV4">
+      <c r="AV4" s="0">
         <f>0+U4</f>
         <v/>
       </c>
-      <c r="AW4">
+      <c r="AW4" s="0">
         <f>MIN(AV4,MAX(0,'Mercados_Pipeline_sim1'!I4))</f>
         <v/>
       </c>
-      <c r="AX4">
+      <c r="AX4" s="0">
         <f>AW4*AU4</f>
         <v/>
       </c>
-      <c r="AY4">
+      <c r="AY4" s="0">
         <f>AV4-AW4</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>SEG-01</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>INF-08</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>INS-01</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>INS-04</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>INS-06</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(E5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(F5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(G5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(D5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="K5">
+      <c r="K5" s="0">
         <f>'Pipeline_sim1'!CG3</f>
         <v/>
       </c>
-      <c r="L5">
+      <c r="L5" s="0">
         <f>'Pipeline_sim1'!CI3</f>
         <v/>
       </c>
-      <c r="M5">
+      <c r="M5" s="0">
         <f>'Pipeline_sim1'!CK3</f>
         <v/>
       </c>
-      <c r="N5">
+      <c r="N5" s="0">
         <f>'Pipeline_sim1'!CM3</f>
         <v/>
       </c>
-      <c r="O5">
+      <c r="O5" s="0">
         <f>'Pipeline_sim1'!CO3</f>
         <v/>
       </c>
-      <c r="P5">
+      <c r="P5" s="0">
         <f>'Pipeline_sim1'!CQ3</f>
         <v/>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="0">
         <f>'Pipeline_sim1'!CS3</f>
         <v/>
       </c>
-      <c r="R5">
+      <c r="R5" s="0">
         <f>'Pipeline_sim1'!CU3</f>
         <v/>
       </c>
-      <c r="S5">
+      <c r="S5" s="0">
         <f>IFERROR(ROUNDDOWN(H5*'Pipeline_sim1'!CE3/'Pipeline_sim1'!I3,0),0)</f>
         <v/>
       </c>
-      <c r="T5">
+      <c r="T5" s="0">
         <f>ROUNDDOWN(MIN(H5,S5,(K5)/0.3,(N5)/1,(P5)/6),0)</f>
         <v/>
       </c>
-      <c r="U5">
+      <c r="U5" s="0">
         <f>ROUNDDOWN(T5*'Pipeline_sim1'!AU3,0)</f>
         <v/>
       </c>
-      <c r="V5">
+      <c r="V5" s="0">
         <f>MIN(K5,MAX(0,T5*0.3))</f>
         <v/>
       </c>
-      <c r="W5">
+      <c r="W5" s="0">
         <f>K5-V5</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X5" s="0">
         <f>IFERROR(V5*U5/T5,0)</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y5" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="0">
         <f>L5-Y5</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA5" s="0">
         <f>IFERROR(Y5*U5/T5,0)</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB5" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC5" s="0">
         <f>M5-AB5</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD5" s="0">
         <f>IFERROR(AB5*U5/T5,0)</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE5" s="0">
         <f>MIN(N5,MAX(0,T5*1))</f>
         <v/>
       </c>
-      <c r="AF5">
+      <c r="AF5" s="0">
         <f>N5-AE5</f>
         <v/>
       </c>
-      <c r="AG5">
+      <c r="AG5" s="0">
         <f>IFERROR(AE5*U5/T5,0)</f>
         <v/>
       </c>
-      <c r="AH5">
+      <c r="AH5" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AI5">
+      <c r="AI5" s="0">
         <f>O5-AH5</f>
         <v/>
       </c>
-      <c r="AJ5">
+      <c r="AJ5" s="0">
         <f>IFERROR(AH5*U5/T5,0)</f>
         <v/>
       </c>
-      <c r="AK5">
+      <c r="AK5" s="0">
         <f>MIN(P5,MAX(0,T5*6))</f>
         <v/>
       </c>
-      <c r="AL5">
+      <c r="AL5" s="0">
         <f>P5-AK5</f>
         <v/>
       </c>
-      <c r="AM5">
+      <c r="AM5" s="0">
         <f>IFERROR(AK5*U5/T5,0)</f>
         <v/>
       </c>
-      <c r="AN5">
+      <c r="AN5" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AO5">
+      <c r="AO5" s="0">
         <f>Q5-AN5</f>
         <v/>
       </c>
-      <c r="AP5">
+      <c r="AP5" s="0">
         <f>IFERROR(AN5*U5/T5,0)</f>
         <v/>
       </c>
-      <c r="AQ5">
+      <c r="AQ5" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AR5">
+      <c r="AR5" s="0">
         <f>R5-AQ5</f>
         <v/>
       </c>
-      <c r="AS5">
+      <c r="AS5" s="0">
         <f>IFERROR(AQ5*U5/T5,0)</f>
         <v/>
       </c>
-      <c r="AT5">
+      <c r="AT5" s="0">
         <f>IF(AND(C5="SEG-03",H5&gt;0),IF(J5&lt;4,0.65,IF(J5&gt;=7,1.4,1)),1)</f>
         <v/>
       </c>
-      <c r="AU5">
+      <c r="AU5" s="0">
         <f>I5*AT5</f>
         <v/>
       </c>
-      <c r="AV5">
+      <c r="AV5" s="0">
         <f>0+U5</f>
         <v/>
       </c>
-      <c r="AW5">
+      <c r="AW5" s="0">
         <f>MIN(AV5,MAX(0,'Mercados_Pipeline_sim1'!I5))</f>
         <v/>
       </c>
-      <c r="AX5">
+      <c r="AX5" s="0">
         <f>AW5*AU5</f>
         <v/>
       </c>
-      <c r="AY5">
+      <c r="AY5" s="0">
         <f>AV5-AW5</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>SEG-02</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>INF-09</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>INS-02</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>INS-04</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>INS-07</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(E6,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(F6,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(G6,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(D6,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="K6">
+      <c r="K6" s="0">
         <f>'Lotes_Pipeline_sim1'!W5</f>
         <v/>
       </c>
-      <c r="L6">
+      <c r="L6" s="0">
         <f>'Lotes_Pipeline_sim1'!Z5</f>
         <v/>
       </c>
-      <c r="M6">
+      <c r="M6" s="0">
         <f>'Lotes_Pipeline_sim1'!AC5</f>
         <v/>
       </c>
-      <c r="N6">
+      <c r="N6" s="0">
         <f>'Lotes_Pipeline_sim1'!AF5</f>
         <v/>
       </c>
-      <c r="O6">
+      <c r="O6" s="0">
         <f>'Lotes_Pipeline_sim1'!AI5</f>
         <v/>
       </c>
-      <c r="P6">
+      <c r="P6" s="0">
         <f>'Lotes_Pipeline_sim1'!AL5</f>
         <v/>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="0">
         <f>'Lotes_Pipeline_sim1'!AO5</f>
         <v/>
       </c>
-      <c r="R6">
+      <c r="R6" s="0">
         <f>'Lotes_Pipeline_sim1'!AR5</f>
         <v/>
       </c>
-      <c r="S6">
+      <c r="S6" s="0">
         <f>IFERROR(ROUNDDOWN(H6*'Pipeline_sim1'!CE3/'Pipeline_sim1'!I3,0),0)</f>
         <v/>
       </c>
-      <c r="T6">
+      <c r="T6" s="0">
         <f>ROUNDDOWN(MIN(H6,S6,(L6)/0.4,(N6)/1,(Q6)/7),0)</f>
         <v/>
       </c>
-      <c r="U6">
+      <c r="U6" s="0">
         <f>ROUNDDOWN(T6*'Pipeline_sim1'!AU3,0)</f>
         <v/>
       </c>
-      <c r="V6">
+      <c r="V6" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="W6">
+      <c r="W6" s="0">
         <f>K6-V6</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X6" s="0">
         <f>IFERROR(V6*U6/T6,0)</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y6" s="0">
         <f>MIN(L6,MAX(0,T6*0.4-(V6)))</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z6" s="0">
         <f>L6-Y6</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA6" s="0">
         <f>IFERROR(Y6*U6/T6,0)</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB6" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC6" s="0">
         <f>M6-AB6</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD6" s="0">
         <f>IFERROR(AB6*U6/T6,0)</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE6" s="0">
         <f>MIN(N6,MAX(0,T6*1))</f>
         <v/>
       </c>
-      <c r="AF6">
+      <c r="AF6" s="0">
         <f>N6-AE6</f>
         <v/>
       </c>
-      <c r="AG6">
+      <c r="AG6" s="0">
         <f>IFERROR(AE6*U6/T6,0)</f>
         <v/>
       </c>
-      <c r="AH6">
+      <c r="AH6" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AI6">
+      <c r="AI6" s="0">
         <f>O6-AH6</f>
         <v/>
       </c>
-      <c r="AJ6">
+      <c r="AJ6" s="0">
         <f>IFERROR(AH6*U6/T6,0)</f>
         <v/>
       </c>
-      <c r="AK6">
+      <c r="AK6" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AL6">
+      <c r="AL6" s="0">
         <f>P6-AK6</f>
         <v/>
       </c>
-      <c r="AM6">
+      <c r="AM6" s="0">
         <f>IFERROR(AK6*U6/T6,0)</f>
         <v/>
       </c>
-      <c r="AN6">
+      <c r="AN6" s="0">
         <f>MIN(Q6,MAX(0,T6*7-(AK6)))</f>
         <v/>
       </c>
-      <c r="AO6">
+      <c r="AO6" s="0">
         <f>Q6-AN6</f>
         <v/>
       </c>
-      <c r="AP6">
+      <c r="AP6" s="0">
         <f>IFERROR(AN6*U6/T6,0)</f>
         <v/>
       </c>
-      <c r="AQ6">
+      <c r="AQ6" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AR6">
+      <c r="AR6" s="0">
         <f>R6-AQ6</f>
         <v/>
       </c>
-      <c r="AS6">
+      <c r="AS6" s="0">
         <f>IFERROR(AQ6*U6/T6,0)</f>
         <v/>
       </c>
-      <c r="AT6">
+      <c r="AT6" s="0">
         <f>IF(AND(C6="SEG-03",H6&gt;0),IF(J6&lt;4,0.65,IF(J6&gt;=7,1.4,1)),1)</f>
         <v/>
       </c>
-      <c r="AU6">
+      <c r="AU6" s="0">
         <f>I6*AT6</f>
         <v/>
       </c>
-      <c r="AV6">
+      <c r="AV6" s="0">
         <f>0+U6</f>
         <v/>
       </c>
-      <c r="AW6">
+      <c r="AW6" s="0">
         <f>MIN(AV6,MAX(0,'Mercados_Pipeline_sim1'!I6))</f>
         <v/>
       </c>
-      <c r="AX6">
+      <c r="AX6" s="0">
         <f>AW6*AU6</f>
         <v/>
       </c>
-      <c r="AY6">
+      <c r="AY6" s="0">
         <f>AV6-AW6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>SEG-03</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>INF-10</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>INS-03</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>INS-05</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>INS-08</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(E7,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(F7,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(G7,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(D7,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="K7">
+      <c r="K7" s="0">
         <f>'Lotes_Pipeline_sim1'!W6</f>
         <v/>
       </c>
-      <c r="L7">
+      <c r="L7" s="0">
         <f>'Lotes_Pipeline_sim1'!Z6</f>
         <v/>
       </c>
-      <c r="M7">
+      <c r="M7" s="0">
         <f>'Lotes_Pipeline_sim1'!AC6</f>
         <v/>
       </c>
-      <c r="N7">
+      <c r="N7" s="0">
         <f>'Lotes_Pipeline_sim1'!AF6</f>
         <v/>
       </c>
-      <c r="O7">
+      <c r="O7" s="0">
         <f>'Lotes_Pipeline_sim1'!AI6</f>
         <v/>
       </c>
-      <c r="P7">
+      <c r="P7" s="0">
         <f>'Lotes_Pipeline_sim1'!AL6</f>
         <v/>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="0">
         <f>'Lotes_Pipeline_sim1'!AO6</f>
         <v/>
       </c>
-      <c r="R7">
+      <c r="R7" s="0">
         <f>'Lotes_Pipeline_sim1'!AR6</f>
         <v/>
       </c>
-      <c r="S7">
+      <c r="S7" s="0">
         <f>IFERROR(ROUNDDOWN(H7*'Pipeline_sim1'!CE3/'Pipeline_sim1'!I3,0),0)</f>
         <v/>
       </c>
-      <c r="T7">
+      <c r="T7" s="0">
         <f>ROUNDDOWN(MIN(H7,S7,(M7)/0.7,(O7)/1,(R7)/13),0)</f>
         <v/>
       </c>
-      <c r="U7">
+      <c r="U7" s="0">
         <f>ROUNDDOWN(T7*'Pipeline_sim1'!AU3,0)</f>
         <v/>
       </c>
-      <c r="V7">
+      <c r="V7" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="W7">
+      <c r="W7" s="0">
         <f>K7-V7</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X7" s="0">
         <f>IFERROR(V7*U7/T7,0)</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y7" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="0">
         <f>L7-Y7</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA7" s="0">
         <f>IFERROR(Y7*U7/T7,0)</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB7" s="0">
         <f>MIN(M7,MAX(0,T7*0.7-(V7+Y7)))</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC7" s="0">
         <f>M7-AB7</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD7" s="0">
         <f>IFERROR(AB7*U7/T7,0)</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE7" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AF7">
+      <c r="AF7" s="0">
         <f>N7-AE7</f>
         <v/>
       </c>
-      <c r="AG7">
+      <c r="AG7" s="0">
         <f>IFERROR(AE7*U7/T7,0)</f>
         <v/>
       </c>
-      <c r="AH7">
+      <c r="AH7" s="0">
         <f>MIN(O7,MAX(0,T7*1-(AE7)))</f>
         <v/>
       </c>
-      <c r="AI7">
+      <c r="AI7" s="0">
         <f>O7-AH7</f>
         <v/>
       </c>
-      <c r="AJ7">
+      <c r="AJ7" s="0">
         <f>IFERROR(AH7*U7/T7,0)</f>
         <v/>
       </c>
-      <c r="AK7">
+      <c r="AK7" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AL7">
+      <c r="AL7" s="0">
         <f>P7-AK7</f>
         <v/>
       </c>
-      <c r="AM7">
+      <c r="AM7" s="0">
         <f>IFERROR(AK7*U7/T7,0)</f>
         <v/>
       </c>
-      <c r="AN7">
+      <c r="AN7" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AO7">
+      <c r="AO7" s="0">
         <f>Q7-AN7</f>
         <v/>
       </c>
-      <c r="AP7">
+      <c r="AP7" s="0">
         <f>IFERROR(AN7*U7/T7,0)</f>
         <v/>
       </c>
-      <c r="AQ7">
+      <c r="AQ7" s="0">
         <f>MIN(R7,MAX(0,T7*13-(AK7+AN7)))</f>
         <v/>
       </c>
-      <c r="AR7">
+      <c r="AR7" s="0">
         <f>R7-AQ7</f>
         <v/>
       </c>
-      <c r="AS7">
+      <c r="AS7" s="0">
         <f>IFERROR(AQ7*U7/T7,0)</f>
         <v/>
       </c>
-      <c r="AT7">
+      <c r="AT7" s="0">
         <f>IF(AND(C7="SEG-03",H7&gt;0),IF(J7&lt;4,0.65,IF(J7&gt;=7,1.4,1)),1)</f>
         <v/>
       </c>
-      <c r="AU7">
+      <c r="AU7" s="0">
         <f>I7*AT7</f>
         <v/>
       </c>
-      <c r="AV7">
+      <c r="AV7" s="0">
         <f>0+U7</f>
         <v/>
       </c>
-      <c r="AW7">
+      <c r="AW7" s="0">
         <f>MIN(AV7,MAX(0,'Mercados_Pipeline_sim1'!I7))</f>
         <v/>
       </c>
-      <c r="AX7">
+      <c r="AX7" s="0">
         <f>AW7*AU7</f>
         <v/>
       </c>
-      <c r="AY7">
+      <c r="AY7" s="0">
         <f>AV7-AW7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>SEG-01</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>INF-08</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>INS-01</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>INS-04</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>INS-06</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="0" t="n">
         <v>43</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(E8,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(F8,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(G8,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(D8,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="K8">
+      <c r="K8" s="0">
         <f>'Pipeline_sim1'!CG4</f>
         <v/>
       </c>
-      <c r="L8">
+      <c r="L8" s="0">
         <f>'Pipeline_sim1'!CI4</f>
         <v/>
       </c>
-      <c r="M8">
+      <c r="M8" s="0">
         <f>'Pipeline_sim1'!CK4</f>
         <v/>
       </c>
-      <c r="N8">
+      <c r="N8" s="0">
         <f>'Pipeline_sim1'!CM4</f>
         <v/>
       </c>
-      <c r="O8">
+      <c r="O8" s="0">
         <f>'Pipeline_sim1'!CO4</f>
         <v/>
       </c>
-      <c r="P8">
+      <c r="P8" s="0">
         <f>'Pipeline_sim1'!CQ4</f>
         <v/>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="0">
         <f>'Pipeline_sim1'!CS4</f>
         <v/>
       </c>
-      <c r="R8">
+      <c r="R8" s="0">
         <f>'Pipeline_sim1'!CU4</f>
         <v/>
       </c>
-      <c r="S8">
+      <c r="S8" s="0">
         <f>IFERROR(ROUNDDOWN(H8*'Pipeline_sim1'!CE4/'Pipeline_sim1'!I4,0),0)</f>
         <v/>
       </c>
-      <c r="T8">
+      <c r="T8" s="0">
         <f>ROUNDDOWN(MIN(H8,S8,(K8)/0.3,(N8)/1,(P8)/6),0)</f>
         <v/>
       </c>
-      <c r="U8">
+      <c r="U8" s="0">
         <f>ROUNDDOWN(T8*'Pipeline_sim1'!AU4,0)</f>
         <v/>
       </c>
-      <c r="V8">
+      <c r="V8" s="0">
         <f>MIN(K8,MAX(0,T8*0.3))</f>
         <v/>
       </c>
-      <c r="W8">
+      <c r="W8" s="0">
         <f>K8-V8</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X8" s="0">
         <f>IFERROR(V8*U8/T8,0)</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y8" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="Z8" s="0">
         <f>L8-Y8</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA8" s="0">
         <f>IFERROR(Y8*U8/T8,0)</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB8" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC8" s="0">
         <f>M8-AB8</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD8" s="0">
         <f>IFERROR(AB8*U8/T8,0)</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE8" s="0">
         <f>MIN(N8,MAX(0,T8*1))</f>
         <v/>
       </c>
-      <c r="AF8">
+      <c r="AF8" s="0">
         <f>N8-AE8</f>
         <v/>
       </c>
-      <c r="AG8">
+      <c r="AG8" s="0">
         <f>IFERROR(AE8*U8/T8,0)</f>
         <v/>
       </c>
-      <c r="AH8">
+      <c r="AH8" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AI8">
+      <c r="AI8" s="0">
         <f>O8-AH8</f>
         <v/>
       </c>
-      <c r="AJ8">
+      <c r="AJ8" s="0">
         <f>IFERROR(AH8*U8/T8,0)</f>
         <v/>
       </c>
-      <c r="AK8">
+      <c r="AK8" s="0">
         <f>MIN(P8,MAX(0,T8*6))</f>
         <v/>
       </c>
-      <c r="AL8">
+      <c r="AL8" s="0">
         <f>P8-AK8</f>
         <v/>
       </c>
-      <c r="AM8">
+      <c r="AM8" s="0">
         <f>IFERROR(AK8*U8/T8,0)</f>
         <v/>
       </c>
-      <c r="AN8">
+      <c r="AN8" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AO8">
+      <c r="AO8" s="0">
         <f>Q8-AN8</f>
         <v/>
       </c>
-      <c r="AP8">
+      <c r="AP8" s="0">
         <f>IFERROR(AN8*U8/T8,0)</f>
         <v/>
       </c>
-      <c r="AQ8">
+      <c r="AQ8" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AR8">
+      <c r="AR8" s="0">
         <f>R8-AQ8</f>
         <v/>
       </c>
-      <c r="AS8">
+      <c r="AS8" s="0">
         <f>IFERROR(AQ8*U8/T8,0)</f>
         <v/>
       </c>
-      <c r="AT8">
+      <c r="AT8" s="0">
         <f>IF(AND(C8="SEG-03",H8&gt;0),IF(J8&lt;4,0.65,IF(J8&gt;=7,1.4,1)),1)</f>
         <v/>
       </c>
-      <c r="AU8">
+      <c r="AU8" s="0">
         <f>I8*AT8</f>
         <v/>
       </c>
-      <c r="AV8">
+      <c r="AV8" s="0">
         <f>0+U8</f>
         <v/>
       </c>
-      <c r="AW8">
+      <c r="AW8" s="0">
         <f>MIN(AV8,MAX(0,'Mercados_Pipeline_sim1'!I8))</f>
         <v/>
       </c>
-      <c r="AX8">
+      <c r="AX8" s="0">
         <f>AW8*AU8</f>
         <v/>
       </c>
-      <c r="AY8">
+      <c r="AY8" s="0">
         <f>AV8-AW8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>SEG-02</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>INF-09</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>INS-02</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="0" t="inlineStr">
         <is>
           <t>INS-04</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>INS-07</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(E9,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(F9,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(G9,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(D9,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="K9">
+      <c r="K9" s="0">
         <f>'Lotes_Pipeline_sim1'!W8</f>
         <v/>
       </c>
-      <c r="L9">
+      <c r="L9" s="0">
         <f>'Lotes_Pipeline_sim1'!Z8</f>
         <v/>
       </c>
-      <c r="M9">
+      <c r="M9" s="0">
         <f>'Lotes_Pipeline_sim1'!AC8</f>
         <v/>
       </c>
-      <c r="N9">
+      <c r="N9" s="0">
         <f>'Lotes_Pipeline_sim1'!AF8</f>
         <v/>
       </c>
-      <c r="O9">
+      <c r="O9" s="0">
         <f>'Lotes_Pipeline_sim1'!AI8</f>
         <v/>
       </c>
-      <c r="P9">
+      <c r="P9" s="0">
         <f>'Lotes_Pipeline_sim1'!AL8</f>
         <v/>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="0">
         <f>'Lotes_Pipeline_sim1'!AO8</f>
         <v/>
       </c>
-      <c r="R9">
+      <c r="R9" s="0">
         <f>'Lotes_Pipeline_sim1'!AR8</f>
         <v/>
       </c>
-      <c r="S9">
+      <c r="S9" s="0">
         <f>IFERROR(ROUNDDOWN(H9*'Pipeline_sim1'!CE4/'Pipeline_sim1'!I4,0),0)</f>
         <v/>
       </c>
-      <c r="T9">
+      <c r="T9" s="0">
         <f>ROUNDDOWN(MIN(H9,S9,(L9)/0.4,(N9)/1,(Q9)/7),0)</f>
         <v/>
       </c>
-      <c r="U9">
+      <c r="U9" s="0">
         <f>ROUNDDOWN(T9*'Pipeline_sim1'!AU4,0)</f>
         <v/>
       </c>
-      <c r="V9">
+      <c r="V9" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="W9">
+      <c r="W9" s="0">
         <f>K9-V9</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X9" s="0">
         <f>IFERROR(V9*U9/T9,0)</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y9" s="0">
         <f>MIN(L9,MAX(0,T9*0.4-(V9)))</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z9" s="0">
         <f>L9-Y9</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA9" s="0">
         <f>IFERROR(Y9*U9/T9,0)</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB9" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC9" s="0">
         <f>M9-AB9</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD9" s="0">
         <f>IFERROR(AB9*U9/T9,0)</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE9" s="0">
         <f>MIN(N9,MAX(0,T9*1))</f>
         <v/>
       </c>
-      <c r="AF9">
+      <c r="AF9" s="0">
         <f>N9-AE9</f>
         <v/>
       </c>
-      <c r="AG9">
+      <c r="AG9" s="0">
         <f>IFERROR(AE9*U9/T9,0)</f>
         <v/>
       </c>
-      <c r="AH9">
+      <c r="AH9" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AI9">
+      <c r="AI9" s="0">
         <f>O9-AH9</f>
         <v/>
       </c>
-      <c r="AJ9">
+      <c r="AJ9" s="0">
         <f>IFERROR(AH9*U9/T9,0)</f>
         <v/>
       </c>
-      <c r="AK9">
+      <c r="AK9" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AL9">
+      <c r="AL9" s="0">
         <f>P9-AK9</f>
         <v/>
       </c>
-      <c r="AM9">
+      <c r="AM9" s="0">
         <f>IFERROR(AK9*U9/T9,0)</f>
         <v/>
       </c>
-      <c r="AN9">
+      <c r="AN9" s="0">
         <f>MIN(Q9,MAX(0,T9*7-(AK9)))</f>
         <v/>
       </c>
-      <c r="AO9">
+      <c r="AO9" s="0">
         <f>Q9-AN9</f>
         <v/>
       </c>
-      <c r="AP9">
+      <c r="AP9" s="0">
         <f>IFERROR(AN9*U9/T9,0)</f>
         <v/>
       </c>
-      <c r="AQ9">
+      <c r="AQ9" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AR9">
+      <c r="AR9" s="0">
         <f>R9-AQ9</f>
         <v/>
       </c>
-      <c r="AS9">
+      <c r="AS9" s="0">
         <f>IFERROR(AQ9*U9/T9,0)</f>
         <v/>
       </c>
-      <c r="AT9">
+      <c r="AT9" s="0">
         <f>IF(AND(C9="SEG-03",H9&gt;0),IF(J9&lt;4,0.65,IF(J9&gt;=7,1.4,1)),1)</f>
         <v/>
       </c>
-      <c r="AU9">
+      <c r="AU9" s="0">
         <f>I9*AT9</f>
         <v/>
       </c>
-      <c r="AV9">
+      <c r="AV9" s="0">
         <f>0+U9</f>
         <v/>
       </c>
-      <c r="AW9">
+      <c r="AW9" s="0">
         <f>MIN(AV9,MAX(0,'Mercados_Pipeline_sim1'!I9))</f>
         <v/>
       </c>
-      <c r="AX9">
+      <c r="AX9" s="0">
         <f>AW9*AU9</f>
         <v/>
       </c>
-      <c r="AY9">
+      <c r="AY9" s="0">
         <f>AV9-AW9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>SEG-03</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>INF-10</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>INS-03</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>INS-05</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>INS-08</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(E10,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(F10,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(G10,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(D10,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="K10">
+      <c r="K10" s="0">
         <f>'Lotes_Pipeline_sim1'!W9</f>
         <v/>
       </c>
-      <c r="L10">
+      <c r="L10" s="0">
         <f>'Lotes_Pipeline_sim1'!Z9</f>
         <v/>
       </c>
-      <c r="M10">
+      <c r="M10" s="0">
         <f>'Lotes_Pipeline_sim1'!AC9</f>
         <v/>
       </c>
-      <c r="N10">
+      <c r="N10" s="0">
         <f>'Lotes_Pipeline_sim1'!AF9</f>
         <v/>
       </c>
-      <c r="O10">
+      <c r="O10" s="0">
         <f>'Lotes_Pipeline_sim1'!AI9</f>
         <v/>
       </c>
-      <c r="P10">
+      <c r="P10" s="0">
         <f>'Lotes_Pipeline_sim1'!AL9</f>
         <v/>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="0">
         <f>'Lotes_Pipeline_sim1'!AO9</f>
         <v/>
       </c>
-      <c r="R10">
+      <c r="R10" s="0">
         <f>'Lotes_Pipeline_sim1'!AR9</f>
         <v/>
       </c>
-      <c r="S10">
+      <c r="S10" s="0">
         <f>IFERROR(ROUNDDOWN(H10*'Pipeline_sim1'!CE4/'Pipeline_sim1'!I4,0),0)</f>
         <v/>
       </c>
-      <c r="T10">
+      <c r="T10" s="0">
         <f>ROUNDDOWN(MIN(H10,S10,(M10)/0.7,(O10)/1,(R10)/13),0)</f>
         <v/>
       </c>
-      <c r="U10">
+      <c r="U10" s="0">
         <f>ROUNDDOWN(T10*'Pipeline_sim1'!AU4,0)</f>
         <v/>
       </c>
-      <c r="V10">
+      <c r="V10" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="W10">
+      <c r="W10" s="0">
         <f>K10-V10</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X10" s="0">
         <f>IFERROR(V10*U10/T10,0)</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y10" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="Z10" s="0">
         <f>L10-Y10</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA10" s="0">
         <f>IFERROR(Y10*U10/T10,0)</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB10" s="0">
         <f>MIN(M10,MAX(0,T10*0.7-(V10+Y10)))</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC10" s="0">
         <f>M10-AB10</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD10" s="0">
         <f>IFERROR(AB10*U10/T10,0)</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE10" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AF10">
+      <c r="AF10" s="0">
         <f>N10-AE10</f>
         <v/>
       </c>
-      <c r="AG10">
+      <c r="AG10" s="0">
         <f>IFERROR(AE10*U10/T10,0)</f>
         <v/>
       </c>
-      <c r="AH10">
+      <c r="AH10" s="0">
         <f>MIN(O10,MAX(0,T10*1-(AE10)))</f>
         <v/>
       </c>
-      <c r="AI10">
+      <c r="AI10" s="0">
         <f>O10-AH10</f>
         <v/>
       </c>
-      <c r="AJ10">
+      <c r="AJ10" s="0">
         <f>IFERROR(AH10*U10/T10,0)</f>
         <v/>
       </c>
-      <c r="AK10">
+      <c r="AK10" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AL10">
+      <c r="AL10" s="0">
         <f>P10-AK10</f>
         <v/>
       </c>
-      <c r="AM10">
+      <c r="AM10" s="0">
         <f>IFERROR(AK10*U10/T10,0)</f>
         <v/>
       </c>
-      <c r="AN10">
+      <c r="AN10" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AO10">
+      <c r="AO10" s="0">
         <f>Q10-AN10</f>
         <v/>
       </c>
-      <c r="AP10">
+      <c r="AP10" s="0">
         <f>IFERROR(AN10*U10/T10,0)</f>
         <v/>
       </c>
-      <c r="AQ10">
+      <c r="AQ10" s="0">
         <f>MIN(R10,MAX(0,T10*13-(AK10+AN10)))</f>
         <v/>
       </c>
-      <c r="AR10">
+      <c r="AR10" s="0">
         <f>R10-AQ10</f>
         <v/>
       </c>
-      <c r="AS10">
+      <c r="AS10" s="0">
         <f>IFERROR(AQ10*U10/T10,0)</f>
         <v/>
       </c>
-      <c r="AT10">
+      <c r="AT10" s="0">
         <f>IF(AND(C10="SEG-03",H10&gt;0),IF(J10&lt;4,0.65,IF(J10&gt;=7,1.4,1)),1)</f>
         <v/>
       </c>
-      <c r="AU10">
+      <c r="AU10" s="0">
         <f>I10*AT10</f>
         <v/>
       </c>
-      <c r="AV10">
+      <c r="AV10" s="0">
         <f>0+U10</f>
         <v/>
       </c>
-      <c r="AW10">
+      <c r="AW10" s="0">
         <f>MIN(AV10,MAX(0,'Mercados_Pipeline_sim1'!I10))</f>
         <v/>
       </c>
-      <c r="AX10">
+      <c r="AX10" s="0">
         <f>AW10*AU10</f>
         <v/>
       </c>
-      <c r="AY10">
+      <c r="AY10" s="0">
         <f>AV10-AW10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>SEG-01</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>INF-08</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>INS-01</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>INS-04</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>INS-06</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="0" t="n">
         <v>41</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(E11,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(F11,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(G11,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(D11,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="K11">
+      <c r="K11" s="0">
         <f>'Pipeline_sim1'!CG5</f>
         <v/>
       </c>
-      <c r="L11">
+      <c r="L11" s="0">
         <f>'Pipeline_sim1'!CI5</f>
         <v/>
       </c>
-      <c r="M11">
+      <c r="M11" s="0">
         <f>'Pipeline_sim1'!CK5</f>
         <v/>
       </c>
-      <c r="N11">
+      <c r="N11" s="0">
         <f>'Pipeline_sim1'!CM5</f>
         <v/>
       </c>
-      <c r="O11">
+      <c r="O11" s="0">
         <f>'Pipeline_sim1'!CO5</f>
         <v/>
       </c>
-      <c r="P11">
+      <c r="P11" s="0">
         <f>'Pipeline_sim1'!CQ5</f>
         <v/>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="0">
         <f>'Pipeline_sim1'!CS5</f>
         <v/>
       </c>
-      <c r="R11">
+      <c r="R11" s="0">
         <f>'Pipeline_sim1'!CU5</f>
         <v/>
       </c>
-      <c r="S11">
+      <c r="S11" s="0">
         <f>IFERROR(ROUNDDOWN(H11*'Pipeline_sim1'!CE5/'Pipeline_sim1'!I5,0),0)</f>
         <v/>
       </c>
-      <c r="T11">
+      <c r="T11" s="0">
         <f>ROUNDDOWN(MIN(H11,S11,(K11)/0.3,(N11)/1,(P11)/6),0)</f>
         <v/>
       </c>
-      <c r="U11">
+      <c r="U11" s="0">
         <f>ROUNDDOWN(T11*'Pipeline_sim1'!AU5,0)</f>
         <v/>
       </c>
-      <c r="V11">
+      <c r="V11" s="0">
         <f>MIN(K11,MAX(0,T11*0.3))</f>
         <v/>
       </c>
-      <c r="W11">
+      <c r="W11" s="0">
         <f>K11-V11</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X11" s="0">
         <f>IFERROR(V11*U11/T11,0)</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y11" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z11" s="0">
         <f>L11-Y11</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA11" s="0">
         <f>IFERROR(Y11*U11/T11,0)</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB11" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC11" s="0">
         <f>M11-AB11</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD11" s="0">
         <f>IFERROR(AB11*U11/T11,0)</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE11" s="0">
         <f>MIN(N11,MAX(0,T11*1))</f>
         <v/>
       </c>
-      <c r="AF11">
+      <c r="AF11" s="0">
         <f>N11-AE11</f>
         <v/>
       </c>
-      <c r="AG11">
+      <c r="AG11" s="0">
         <f>IFERROR(AE11*U11/T11,0)</f>
         <v/>
       </c>
-      <c r="AH11">
+      <c r="AH11" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AI11">
+      <c r="AI11" s="0">
         <f>O11-AH11</f>
         <v/>
       </c>
-      <c r="AJ11">
+      <c r="AJ11" s="0">
         <f>IFERROR(AH11*U11/T11,0)</f>
         <v/>
       </c>
-      <c r="AK11">
+      <c r="AK11" s="0">
         <f>MIN(P11,MAX(0,T11*6))</f>
         <v/>
       </c>
-      <c r="AL11">
+      <c r="AL11" s="0">
         <f>P11-AK11</f>
         <v/>
       </c>
-      <c r="AM11">
+      <c r="AM11" s="0">
         <f>IFERROR(AK11*U11/T11,0)</f>
         <v/>
       </c>
-      <c r="AN11">
+      <c r="AN11" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AO11">
+      <c r="AO11" s="0">
         <f>Q11-AN11</f>
         <v/>
       </c>
-      <c r="AP11">
+      <c r="AP11" s="0">
         <f>IFERROR(AN11*U11/T11,0)</f>
         <v/>
       </c>
-      <c r="AQ11">
+      <c r="AQ11" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AR11">
+      <c r="AR11" s="0">
         <f>R11-AQ11</f>
         <v/>
       </c>
-      <c r="AS11">
+      <c r="AS11" s="0">
         <f>IFERROR(AQ11*U11/T11,0)</f>
         <v/>
       </c>
-      <c r="AT11">
+      <c r="AT11" s="0">
         <f>IF(AND(C11="SEG-03",H11&gt;0),IF(J11&lt;4,0.65,IF(J11&gt;=7,1.4,1)),1)</f>
         <v/>
       </c>
-      <c r="AU11">
+      <c r="AU11" s="0">
         <f>I11*AT11</f>
         <v/>
       </c>
-      <c r="AV11">
+      <c r="AV11" s="0">
         <f>0+U11</f>
         <v/>
       </c>
-      <c r="AW11">
+      <c r="AW11" s="0">
         <f>MIN(AV11,MAX(0,'Mercados_Pipeline_sim1'!I11))</f>
         <v/>
       </c>
-      <c r="AX11">
+      <c r="AX11" s="0">
         <f>AW11*AU11</f>
         <v/>
       </c>
-      <c r="AY11">
+      <c r="AY11" s="0">
         <f>AV11-AW11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>SEG-02</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>INF-09</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>INS-02</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>INS-04</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>INS-07</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(E12,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(F12,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(G12,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(D12,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="K12">
+      <c r="K12" s="0">
         <f>'Lotes_Pipeline_sim1'!W11</f>
         <v/>
       </c>
-      <c r="L12">
+      <c r="L12" s="0">
         <f>'Lotes_Pipeline_sim1'!Z11</f>
         <v/>
       </c>
-      <c r="M12">
+      <c r="M12" s="0">
         <f>'Lotes_Pipeline_sim1'!AC11</f>
         <v/>
       </c>
-      <c r="N12">
+      <c r="N12" s="0">
         <f>'Lotes_Pipeline_sim1'!AF11</f>
         <v/>
       </c>
-      <c r="O12">
+      <c r="O12" s="0">
         <f>'Lotes_Pipeline_sim1'!AI11</f>
         <v/>
       </c>
-      <c r="P12">
+      <c r="P12" s="0">
         <f>'Lotes_Pipeline_sim1'!AL11</f>
         <v/>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="0">
         <f>'Lotes_Pipeline_sim1'!AO11</f>
         <v/>
       </c>
-      <c r="R12">
+      <c r="R12" s="0">
         <f>'Lotes_Pipeline_sim1'!AR11</f>
         <v/>
       </c>
-      <c r="S12">
+      <c r="S12" s="0">
         <f>IFERROR(ROUNDDOWN(H12*'Pipeline_sim1'!CE5/'Pipeline_sim1'!I5,0),0)</f>
         <v/>
       </c>
-      <c r="T12">
+      <c r="T12" s="0">
         <f>ROUNDDOWN(MIN(H12,S12,(L12)/0.4,(N12)/1,(Q12)/7),0)</f>
         <v/>
       </c>
-      <c r="U12">
+      <c r="U12" s="0">
         <f>ROUNDDOWN(T12*'Pipeline_sim1'!AU5,0)</f>
         <v/>
       </c>
-      <c r="V12">
+      <c r="V12" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="W12">
+      <c r="W12" s="0">
         <f>K12-V12</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X12" s="0">
         <f>IFERROR(V12*U12/T12,0)</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y12" s="0">
         <f>MIN(L12,MAX(0,T12*0.4-(V12)))</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z12" s="0">
         <f>L12-Y12</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA12" s="0">
         <f>IFERROR(Y12*U12/T12,0)</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB12" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC12" s="0">
         <f>M12-AB12</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD12" s="0">
         <f>IFERROR(AB12*U12/T12,0)</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE12" s="0">
         <f>MIN(N12,MAX(0,T12*1))</f>
         <v/>
       </c>
-      <c r="AF12">
+      <c r="AF12" s="0">
         <f>N12-AE12</f>
         <v/>
       </c>
-      <c r="AG12">
+      <c r="AG12" s="0">
         <f>IFERROR(AE12*U12/T12,0)</f>
         <v/>
       </c>
-      <c r="AH12">
+      <c r="AH12" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AI12">
+      <c r="AI12" s="0">
         <f>O12-AH12</f>
         <v/>
       </c>
-      <c r="AJ12">
+      <c r="AJ12" s="0">
         <f>IFERROR(AH12*U12/T12,0)</f>
         <v/>
       </c>
-      <c r="AK12">
+      <c r="AK12" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AL12">
+      <c r="AL12" s="0">
         <f>P12-AK12</f>
         <v/>
       </c>
-      <c r="AM12">
+      <c r="AM12" s="0">
         <f>IFERROR(AK12*U12/T12,0)</f>
         <v/>
       </c>
-      <c r="AN12">
+      <c r="AN12" s="0">
         <f>MIN(Q12,MAX(0,T12*7-(AK12)))</f>
         <v/>
       </c>
-      <c r="AO12">
+      <c r="AO12" s="0">
         <f>Q12-AN12</f>
         <v/>
       </c>
-      <c r="AP12">
+      <c r="AP12" s="0">
         <f>IFERROR(AN12*U12/T12,0)</f>
         <v/>
       </c>
-      <c r="AQ12">
+      <c r="AQ12" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AR12">
+      <c r="AR12" s="0">
         <f>R12-AQ12</f>
         <v/>
       </c>
-      <c r="AS12">
+      <c r="AS12" s="0">
         <f>IFERROR(AQ12*U12/T12,0)</f>
         <v/>
       </c>
-      <c r="AT12">
+      <c r="AT12" s="0">
         <f>IF(AND(C12="SEG-03",H12&gt;0),IF(J12&lt;4,0.65,IF(J12&gt;=7,1.4,1)),1)</f>
         <v/>
       </c>
-      <c r="AU12">
+      <c r="AU12" s="0">
         <f>I12*AT12</f>
         <v/>
       </c>
-      <c r="AV12">
+      <c r="AV12" s="0">
         <f>0+U12</f>
         <v/>
       </c>
-      <c r="AW12">
+      <c r="AW12" s="0">
         <f>MIN(AV12,MAX(0,'Mercados_Pipeline_sim1'!I12))</f>
         <v/>
       </c>
-      <c r="AX12">
+      <c r="AX12" s="0">
         <f>AW12*AU12</f>
         <v/>
       </c>
-      <c r="AY12">
+      <c r="AY12" s="0">
         <f>AV12-AW12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>SEG-03</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>INF-10</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>INS-03</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>INS-05</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>INS-08</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(E13,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(F13,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(G13,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$H$2:$H$69,MATCH(D13,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="K13">
+      <c r="K13" s="0">
         <f>'Lotes_Pipeline_sim1'!W12</f>
         <v/>
       </c>
-      <c r="L13">
+      <c r="L13" s="0">
         <f>'Lotes_Pipeline_sim1'!Z12</f>
         <v/>
       </c>
-      <c r="M13">
+      <c r="M13" s="0">
         <f>'Lotes_Pipeline_sim1'!AC12</f>
         <v/>
       </c>
-      <c r="N13">
+      <c r="N13" s="0">
         <f>'Lotes_Pipeline_sim1'!AF12</f>
         <v/>
       </c>
-      <c r="O13">
+      <c r="O13" s="0">
         <f>'Lotes_Pipeline_sim1'!AI12</f>
         <v/>
       </c>
-      <c r="P13">
+      <c r="P13" s="0">
         <f>'Lotes_Pipeline_sim1'!AL12</f>
         <v/>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="0">
         <f>'Lotes_Pipeline_sim1'!AO12</f>
         <v/>
       </c>
-      <c r="R13">
+      <c r="R13" s="0">
         <f>'Lotes_Pipeline_sim1'!AR12</f>
         <v/>
       </c>
-      <c r="S13">
+      <c r="S13" s="0">
         <f>IFERROR(ROUNDDOWN(H13*'Pipeline_sim1'!CE5/'Pipeline_sim1'!I5,0),0)</f>
         <v/>
       </c>
-      <c r="T13">
+      <c r="T13" s="0">
         <f>ROUNDDOWN(MIN(H13,S13,(M13)/0.7,(O13)/1,(R13)/13),0)</f>
         <v/>
       </c>
-      <c r="U13">
+      <c r="U13" s="0">
         <f>ROUNDDOWN(T13*'Pipeline_sim1'!AU5,0)</f>
         <v/>
       </c>
-      <c r="V13">
+      <c r="V13" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="W13">
+      <c r="W13" s="0">
         <f>K13-V13</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X13" s="0">
         <f>IFERROR(V13*U13/T13,0)</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y13" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="Z13" s="0">
         <f>L13-Y13</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA13" s="0">
         <f>IFERROR(Y13*U13/T13,0)</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB13" s="0">
         <f>MIN(M13,MAX(0,T13*0.7-(V13+Y13)))</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC13" s="0">
         <f>M13-AB13</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD13" s="0">
         <f>IFERROR(AB13*U13/T13,0)</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE13" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AF13">
+      <c r="AF13" s="0">
         <f>N13-AE13</f>
         <v/>
       </c>
-      <c r="AG13">
+      <c r="AG13" s="0">
         <f>IFERROR(AE13*U13/T13,0)</f>
         <v/>
       </c>
-      <c r="AH13">
+      <c r="AH13" s="0">
         <f>MIN(O13,MAX(0,T13*1-(AE13)))</f>
         <v/>
       </c>
-      <c r="AI13">
+      <c r="AI13" s="0">
         <f>O13-AH13</f>
         <v/>
       </c>
-      <c r="AJ13">
+      <c r="AJ13" s="0">
         <f>IFERROR(AH13*U13/T13,0)</f>
         <v/>
       </c>
-      <c r="AK13">
+      <c r="AK13" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AL13">
+      <c r="AL13" s="0">
         <f>P13-AK13</f>
         <v/>
       </c>
-      <c r="AM13">
+      <c r="AM13" s="0">
         <f>IFERROR(AK13*U13/T13,0)</f>
         <v/>
       </c>
-      <c r="AN13">
+      <c r="AN13" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="AO13">
+      <c r="AO13" s="0">
         <f>Q13-AN13</f>
         <v/>
       </c>
-      <c r="AP13">
+      <c r="AP13" s="0">
         <f>IFERROR(AN13*U13/T13,0)</f>
         <v/>
       </c>
-      <c r="AQ13">
+      <c r="AQ13" s="0">
         <f>MIN(R13,MAX(0,T13*13-(AK13+AN13)))</f>
         <v/>
       </c>
-      <c r="AR13">
+      <c r="AR13" s="0">
         <f>R13-AQ13</f>
         <v/>
       </c>
-      <c r="AS13">
+      <c r="AS13" s="0">
         <f>IFERROR(AQ13*U13/T13,0)</f>
         <v/>
       </c>
-      <c r="AT13">
+      <c r="AT13" s="0">
         <f>IF(AND(C13="SEG-03",H13&gt;0),IF(J13&lt;4,0.65,IF(J13&gt;=7,1.4,1)),1)</f>
         <v/>
       </c>
-      <c r="AU13">
+      <c r="AU13" s="0">
         <f>I13*AT13</f>
         <v/>
       </c>
-      <c r="AV13">
+      <c r="AV13" s="0">
         <f>0+U13</f>
         <v/>
       </c>
-      <c r="AW13">
+      <c r="AW13" s="0">
         <f>MIN(AV13,MAX(0,'Mercados_Pipeline_sim1'!I13))</f>
         <v/>
       </c>
-      <c r="AX13">
+      <c r="AX13" s="0">
         <f>AW13*AU13</f>
         <v/>
       </c>
-      <c r="AY13">
+      <c r="AY13" s="0">
         <f>AV13-AW13</f>
         <v/>
       </c>
@@ -14082,793 +15086,793 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>ciclo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>empresa</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>segmento</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>activo</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>reputacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>calidad</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="0" t="inlineStr">
         <is>
           <t>demandaAjustada</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="0" t="inlineStr">
         <is>
           <t>asignado</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="0" t="inlineStr">
         <is>
           <t>puntajePrecio</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t>puntajeTotal</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="0" t="inlineStr">
         <is>
           <t>reputacionEscalada</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>porcentaje</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>SEG-01</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>1|SEG-01</t>
         </is>
       </c>
-      <c r="E2">
+      <c r="E2" s="0">
         <f>TRUE()</f>
         <v/>
       </c>
-      <c r="F2">
+      <c r="F2" s="0">
         <f>IFERROR(('Lotes_Pipeline_sim1'!I2*'Lotes_Pipeline_sim1'!H2)/('Lotes_Pipeline_sim1'!H2),0)</f>
         <v/>
       </c>
-      <c r="G2">
+      <c r="G2" s="0">
         <f>'Pipeline_sim1'!DY2</f>
         <v/>
       </c>
-      <c r="H2">
+      <c r="H2" s="0">
         <f>IFERROR(ROUND(G2/SUMIFS($G$2:$G$13,$D$2:$D$13,D2,$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
-      <c r="I2">
+      <c r="I2" s="0">
         <f>MAX(0,ROUNDDOWN(J2*'Pipeline_sim1'!AN2*1.12,0))</f>
         <v/>
       </c>
-      <c r="J2">
+      <c r="J2" s="0">
         <f>IFERROR(ROUND(L2/SUMIF($D$2:$D$13,D2,$L$2:$L$13)*7000*0.5,0),0)</f>
         <v/>
       </c>
-      <c r="K2">
+      <c r="K2" s="0">
         <f>IFERROR(100*(_xlfn.MAXIFS($F$2:$F$13,$D$2:$D$13,D2,$E$2:$E$13,TRUE())-F2)/(_xlfn.MAXIFS($F$2:$F$13,$D$2:$D$13,D2,$E$2:$E$13,TRUE())-_xlfn.MINIFS($F$2:$F$13,$D$2:$D$13,D2,$E$2:$E$13,TRUE())),100)</f>
         <v/>
       </c>
-      <c r="L2">
+      <c r="L2" s="0">
         <f>IF(E2,0.7*K2+0.2*G2*10+0.1*H2,0)</f>
         <v/>
       </c>
-      <c r="M2">
+      <c r="M2" s="0">
         <f>G2*10</f>
         <v/>
       </c>
-      <c r="N2">
+      <c r="N2" s="0">
         <f>IFERROR(L2/SUMIF($D$2:$D$13,D2,$L$2:$L$13),0)</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>SEG-02</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>1|SEG-02</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="E3" s="0">
         <f>TRUE()</f>
         <v/>
       </c>
-      <c r="F3">
+      <c r="F3" s="0">
         <f>IFERROR(('Lotes_Pipeline_sim1'!I3*'Lotes_Pipeline_sim1'!H3)/('Lotes_Pipeline_sim1'!H3),0)</f>
         <v/>
       </c>
-      <c r="G3">
+      <c r="G3" s="0">
         <f>'Pipeline_sim1'!DY2</f>
         <v/>
       </c>
-      <c r="H3">
+      <c r="H3" s="0">
         <f>IFERROR(ROUND(G3/SUMIFS($G$2:$G$13,$D$2:$D$13,D3,$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
-      <c r="I3">
+      <c r="I3" s="0">
         <f>MAX(0,ROUNDDOWN(J3*'Pipeline_sim1'!AN2*1.12,0))</f>
         <v/>
       </c>
-      <c r="J3">
+      <c r="J3" s="0">
         <f>IFERROR(ROUND(L3/SUMIF($D$2:$D$13,D3,$L$2:$L$13)*5000*0.7,0),0)</f>
         <v/>
       </c>
-      <c r="K3">
+      <c r="K3" s="0">
         <f>100-ABS(F3-100)/100*100</f>
         <v/>
       </c>
-      <c r="L3">
+      <c r="L3" s="0">
         <f>IF(E3,0.4*K3+0.35*G3*10+0.25*H3,0)</f>
         <v/>
       </c>
-      <c r="M3">
+      <c r="M3" s="0">
         <f>G3*10</f>
         <v/>
       </c>
-      <c r="N3">
+      <c r="N3" s="0">
         <f>IFERROR(L3/SUMIF($D$2:$D$13,D3,$L$2:$L$13),0)</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>SEG-03</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>1|SEG-03</t>
         </is>
       </c>
-      <c r="E4">
+      <c r="E4" s="0">
         <f>TRUE()</f>
         <v/>
       </c>
-      <c r="F4">
+      <c r="F4" s="0">
         <f>IFERROR(('Lotes_Pipeline_sim1'!I4*'Lotes_Pipeline_sim1'!H4)/('Lotes_Pipeline_sim1'!H4),0)</f>
         <v/>
       </c>
-      <c r="G4">
+      <c r="G4" s="0">
         <f>'Pipeline_sim1'!DY2</f>
         <v/>
       </c>
-      <c r="H4">
+      <c r="H4" s="0">
         <f>IFERROR(ROUND(G4/SUMIFS($G$2:$G$13,$D$2:$D$13,D4,$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
-      <c r="I4">
+      <c r="I4" s="0">
         <f>MAX(0,ROUNDDOWN(J4*'Pipeline_sim1'!AN2*1.12,0))</f>
         <v/>
       </c>
-      <c r="J4">
+      <c r="J4" s="0">
         <f>IFERROR(ROUND(L4/SUMIF($D$2:$D$13,D4,$L$2:$L$13)*2000*0.4,0),0)</f>
         <v/>
       </c>
-      <c r="K4">
+      <c r="K4" s="0">
         <f>100-ABS(F4-250)/250*100</f>
         <v/>
       </c>
-      <c r="L4">
+      <c r="L4" s="0">
         <f>IF(E4,0.1*K4+0.5*G4*10+0.4*H4,0)</f>
         <v/>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>G4*10</f>
         <v/>
       </c>
-      <c r="N4">
+      <c r="N4" s="0">
         <f>IFERROR(L4/SUMIF($D$2:$D$13,D4,$L$2:$L$13),0)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>SEG-01</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>1|SEG-01</t>
         </is>
       </c>
-      <c r="E5">
+      <c r="E5" s="0">
         <f>TRUE()</f>
         <v/>
       </c>
-      <c r="F5">
+      <c r="F5" s="0">
         <f>IFERROR(('Lotes_Pipeline_sim1'!I5*'Lotes_Pipeline_sim1'!H5)/('Lotes_Pipeline_sim1'!H5),0)</f>
         <v/>
       </c>
-      <c r="G5">
+      <c r="G5" s="0">
         <f>'Pipeline_sim1'!DY3</f>
         <v/>
       </c>
-      <c r="H5">
+      <c r="H5" s="0">
         <f>IFERROR(ROUND(G5/SUMIFS($G$2:$G$13,$D$2:$D$13,D5,$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
-      <c r="I5">
+      <c r="I5" s="0">
         <f>MAX(0,ROUNDDOWN(J5*'Pipeline_sim1'!AN3*1.12,0))</f>
         <v/>
       </c>
-      <c r="J5">
+      <c r="J5" s="0">
         <f>IFERROR(ROUND(L5/SUMIF($D$2:$D$13,D5,$L$2:$L$13)*7000*0.5,0),0)</f>
         <v/>
       </c>
-      <c r="K5">
+      <c r="K5" s="0">
         <f>IFERROR(100*(_xlfn.MAXIFS($F$2:$F$13,$D$2:$D$13,D5,$E$2:$E$13,TRUE())-F5)/(_xlfn.MAXIFS($F$2:$F$13,$D$2:$D$13,D5,$E$2:$E$13,TRUE())-_xlfn.MINIFS($F$2:$F$13,$D$2:$D$13,D5,$E$2:$E$13,TRUE())),100)</f>
         <v/>
       </c>
-      <c r="L5">
+      <c r="L5" s="0">
         <f>IF(E5,0.7*K5+0.2*G5*10+0.1*H5,0)</f>
         <v/>
       </c>
-      <c r="M5">
+      <c r="M5" s="0">
         <f>G5*10</f>
         <v/>
       </c>
-      <c r="N5">
+      <c r="N5" s="0">
         <f>IFERROR(L5/SUMIF($D$2:$D$13,D5,$L$2:$L$13),0)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>SEG-02</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>1|SEG-02</t>
         </is>
       </c>
-      <c r="E6">
+      <c r="E6" s="0">
         <f>TRUE()</f>
         <v/>
       </c>
-      <c r="F6">
+      <c r="F6" s="0">
         <f>IFERROR(('Lotes_Pipeline_sim1'!I6*'Lotes_Pipeline_sim1'!H6)/('Lotes_Pipeline_sim1'!H6),0)</f>
         <v/>
       </c>
-      <c r="G6">
+      <c r="G6" s="0">
         <f>'Pipeline_sim1'!DY3</f>
         <v/>
       </c>
-      <c r="H6">
+      <c r="H6" s="0">
         <f>IFERROR(ROUND(G6/SUMIFS($G$2:$G$13,$D$2:$D$13,D6,$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
-      <c r="I6">
+      <c r="I6" s="0">
         <f>MAX(0,ROUNDDOWN(J6*'Pipeline_sim1'!AN3*1.12,0))</f>
         <v/>
       </c>
-      <c r="J6">
+      <c r="J6" s="0">
         <f>IFERROR(ROUND(L6/SUMIF($D$2:$D$13,D6,$L$2:$L$13)*5000*0.7,0),0)</f>
         <v/>
       </c>
-      <c r="K6">
+      <c r="K6" s="0">
         <f>100-ABS(F6-100)/100*100</f>
         <v/>
       </c>
-      <c r="L6">
+      <c r="L6" s="0">
         <f>IF(E6,0.4*K6+0.35*G6*10+0.25*H6,0)</f>
         <v/>
       </c>
-      <c r="M6">
+      <c r="M6" s="0">
         <f>G6*10</f>
         <v/>
       </c>
-      <c r="N6">
+      <c r="N6" s="0">
         <f>IFERROR(L6/SUMIF($D$2:$D$13,D6,$L$2:$L$13),0)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>SEG-03</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>1|SEG-03</t>
         </is>
       </c>
-      <c r="E7">
+      <c r="E7" s="0">
         <f>TRUE()</f>
         <v/>
       </c>
-      <c r="F7">
+      <c r="F7" s="0">
         <f>IFERROR(('Lotes_Pipeline_sim1'!I7*'Lotes_Pipeline_sim1'!H7)/('Lotes_Pipeline_sim1'!H7),0)</f>
         <v/>
       </c>
-      <c r="G7">
+      <c r="G7" s="0">
         <f>'Pipeline_sim1'!DY3</f>
         <v/>
       </c>
-      <c r="H7">
+      <c r="H7" s="0">
         <f>IFERROR(ROUND(G7/SUMIFS($G$2:$G$13,$D$2:$D$13,D7,$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
-      <c r="I7">
+      <c r="I7" s="0">
         <f>MAX(0,ROUNDDOWN(J7*'Pipeline_sim1'!AN3*1.12,0))</f>
         <v/>
       </c>
-      <c r="J7">
+      <c r="J7" s="0">
         <f>IFERROR(ROUND(L7/SUMIF($D$2:$D$13,D7,$L$2:$L$13)*2000*0.4,0),0)</f>
         <v/>
       </c>
-      <c r="K7">
+      <c r="K7" s="0">
         <f>100-ABS(F7-250)/250*100</f>
         <v/>
       </c>
-      <c r="L7">
+      <c r="L7" s="0">
         <f>IF(E7,0.1*K7+0.5*G7*10+0.4*H7,0)</f>
         <v/>
       </c>
-      <c r="M7">
+      <c r="M7" s="0">
         <f>G7*10</f>
         <v/>
       </c>
-      <c r="N7">
+      <c r="N7" s="0">
         <f>IFERROR(L7/SUMIF($D$2:$D$13,D7,$L$2:$L$13),0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>SEG-01</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>1|SEG-01</t>
         </is>
       </c>
-      <c r="E8">
+      <c r="E8" s="0">
         <f>TRUE()</f>
         <v/>
       </c>
-      <c r="F8">
+      <c r="F8" s="0">
         <f>IFERROR(('Lotes_Pipeline_sim1'!I8*'Lotes_Pipeline_sim1'!H8)/('Lotes_Pipeline_sim1'!H8),0)</f>
         <v/>
       </c>
-      <c r="G8">
+      <c r="G8" s="0">
         <f>'Pipeline_sim1'!DY4</f>
         <v/>
       </c>
-      <c r="H8">
+      <c r="H8" s="0">
         <f>IFERROR(ROUND(G8/SUMIFS($G$2:$G$13,$D$2:$D$13,D8,$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
-      <c r="I8">
+      <c r="I8" s="0">
         <f>MAX(0,ROUNDDOWN(J8*'Pipeline_sim1'!AN4*1.12,0))</f>
         <v/>
       </c>
-      <c r="J8">
+      <c r="J8" s="0">
         <f>IFERROR(ROUND(L8/SUMIF($D$2:$D$13,D8,$L$2:$L$13)*7000*0.5,0),0)</f>
         <v/>
       </c>
-      <c r="K8">
+      <c r="K8" s="0">
         <f>IFERROR(100*(_xlfn.MAXIFS($F$2:$F$13,$D$2:$D$13,D8,$E$2:$E$13,TRUE())-F8)/(_xlfn.MAXIFS($F$2:$F$13,$D$2:$D$13,D8,$E$2:$E$13,TRUE())-_xlfn.MINIFS($F$2:$F$13,$D$2:$D$13,D8,$E$2:$E$13,TRUE())),100)</f>
         <v/>
       </c>
-      <c r="L8">
+      <c r="L8" s="0">
         <f>IF(E8,0.7*K8+0.2*G8*10+0.1*H8,0)</f>
         <v/>
       </c>
-      <c r="M8">
+      <c r="M8" s="0">
         <f>G8*10</f>
         <v/>
       </c>
-      <c r="N8">
+      <c r="N8" s="0">
         <f>IFERROR(L8/SUMIF($D$2:$D$13,D8,$L$2:$L$13),0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>SEG-02</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>1|SEG-02</t>
         </is>
       </c>
-      <c r="E9">
+      <c r="E9" s="0">
         <f>TRUE()</f>
         <v/>
       </c>
-      <c r="F9">
+      <c r="F9" s="0">
         <f>IFERROR(('Lotes_Pipeline_sim1'!I9*'Lotes_Pipeline_sim1'!H9)/('Lotes_Pipeline_sim1'!H9),0)</f>
         <v/>
       </c>
-      <c r="G9">
+      <c r="G9" s="0">
         <f>'Pipeline_sim1'!DY4</f>
         <v/>
       </c>
-      <c r="H9">
+      <c r="H9" s="0">
         <f>IFERROR(ROUND(G9/SUMIFS($G$2:$G$13,$D$2:$D$13,D9,$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
-      <c r="I9">
+      <c r="I9" s="0">
         <f>MAX(0,ROUNDDOWN(J9*'Pipeline_sim1'!AN4*1.12,0))</f>
         <v/>
       </c>
-      <c r="J9">
+      <c r="J9" s="0">
         <f>IFERROR(ROUND(L9/SUMIF($D$2:$D$13,D9,$L$2:$L$13)*5000*0.7,0),0)</f>
         <v/>
       </c>
-      <c r="K9">
+      <c r="K9" s="0">
         <f>100-ABS(F9-100)/100*100</f>
         <v/>
       </c>
-      <c r="L9">
+      <c r="L9" s="0">
         <f>IF(E9,0.4*K9+0.35*G9*10+0.25*H9,0)</f>
         <v/>
       </c>
-      <c r="M9">
+      <c r="M9" s="0">
         <f>G9*10</f>
         <v/>
       </c>
-      <c r="N9">
+      <c r="N9" s="0">
         <f>IFERROR(L9/SUMIF($D$2:$D$13,D9,$L$2:$L$13),0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>SEG-03</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>1|SEG-03</t>
         </is>
       </c>
-      <c r="E10">
+      <c r="E10" s="0">
         <f>TRUE()</f>
         <v/>
       </c>
-      <c r="F10">
+      <c r="F10" s="0">
         <f>IFERROR(('Lotes_Pipeline_sim1'!I10*'Lotes_Pipeline_sim1'!H10)/('Lotes_Pipeline_sim1'!H10),0)</f>
         <v/>
       </c>
-      <c r="G10">
+      <c r="G10" s="0">
         <f>'Pipeline_sim1'!DY4</f>
         <v/>
       </c>
-      <c r="H10">
+      <c r="H10" s="0">
         <f>IFERROR(ROUND(G10/SUMIFS($G$2:$G$13,$D$2:$D$13,D10,$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
-      <c r="I10">
+      <c r="I10" s="0">
         <f>MAX(0,ROUNDDOWN(J10*'Pipeline_sim1'!AN4*1.12,0))</f>
         <v/>
       </c>
-      <c r="J10">
+      <c r="J10" s="0">
         <f>IFERROR(ROUND(L10/SUMIF($D$2:$D$13,D10,$L$2:$L$13)*2000*0.4,0),0)</f>
         <v/>
       </c>
-      <c r="K10">
+      <c r="K10" s="0">
         <f>100-ABS(F10-250)/250*100</f>
         <v/>
       </c>
-      <c r="L10">
+      <c r="L10" s="0">
         <f>IF(E10,0.1*K10+0.5*G10*10+0.4*H10,0)</f>
         <v/>
       </c>
-      <c r="M10">
+      <c r="M10" s="0">
         <f>G10*10</f>
         <v/>
       </c>
-      <c r="N10">
+      <c r="N10" s="0">
         <f>IFERROR(L10/SUMIF($D$2:$D$13,D10,$L$2:$L$13),0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>SEG-01</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>1|SEG-01</t>
         </is>
       </c>
-      <c r="E11">
+      <c r="E11" s="0">
         <f>TRUE()</f>
         <v/>
       </c>
-      <c r="F11">
+      <c r="F11" s="0">
         <f>IFERROR(('Lotes_Pipeline_sim1'!I11*'Lotes_Pipeline_sim1'!H11)/('Lotes_Pipeline_sim1'!H11),0)</f>
         <v/>
       </c>
-      <c r="G11">
+      <c r="G11" s="0">
         <f>'Pipeline_sim1'!DY5</f>
         <v/>
       </c>
-      <c r="H11">
+      <c r="H11" s="0">
         <f>IFERROR(ROUND(G11/SUMIFS($G$2:$G$13,$D$2:$D$13,D11,$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
-      <c r="I11">
+      <c r="I11" s="0">
         <f>MAX(0,ROUNDDOWN(J11*'Pipeline_sim1'!AN5*1.12,0))</f>
         <v/>
       </c>
-      <c r="J11">
+      <c r="J11" s="0">
         <f>IFERROR(ROUND(L11/SUMIF($D$2:$D$13,D11,$L$2:$L$13)*7000*0.5,0),0)</f>
         <v/>
       </c>
-      <c r="K11">
+      <c r="K11" s="0">
         <f>IFERROR(100*(_xlfn.MAXIFS($F$2:$F$13,$D$2:$D$13,D11,$E$2:$E$13,TRUE())-F11)/(_xlfn.MAXIFS($F$2:$F$13,$D$2:$D$13,D11,$E$2:$E$13,TRUE())-_xlfn.MINIFS($F$2:$F$13,$D$2:$D$13,D11,$E$2:$E$13,TRUE())),100)</f>
         <v/>
       </c>
-      <c r="L11">
+      <c r="L11" s="0">
         <f>IF(E11,0.7*K11+0.2*G11*10+0.1*H11,0)</f>
         <v/>
       </c>
-      <c r="M11">
+      <c r="M11" s="0">
         <f>G11*10</f>
         <v/>
       </c>
-      <c r="N11">
+      <c r="N11" s="0">
         <f>IFERROR(L11/SUMIF($D$2:$D$13,D11,$L$2:$L$13),0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>SEG-02</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>1|SEG-02</t>
         </is>
       </c>
-      <c r="E12">
+      <c r="E12" s="0">
         <f>TRUE()</f>
         <v/>
       </c>
-      <c r="F12">
+      <c r="F12" s="0">
         <f>IFERROR(('Lotes_Pipeline_sim1'!I12*'Lotes_Pipeline_sim1'!H12)/('Lotes_Pipeline_sim1'!H12),0)</f>
         <v/>
       </c>
-      <c r="G12">
+      <c r="G12" s="0">
         <f>'Pipeline_sim1'!DY5</f>
         <v/>
       </c>
-      <c r="H12">
+      <c r="H12" s="0">
         <f>IFERROR(ROUND(G12/SUMIFS($G$2:$G$13,$D$2:$D$13,D12,$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
-      <c r="I12">
+      <c r="I12" s="0">
         <f>MAX(0,ROUNDDOWN(J12*'Pipeline_sim1'!AN5*1.12,0))</f>
         <v/>
       </c>
-      <c r="J12">
+      <c r="J12" s="0">
         <f>IFERROR(ROUND(L12/SUMIF($D$2:$D$13,D12,$L$2:$L$13)*5000*0.7,0),0)</f>
         <v/>
       </c>
-      <c r="K12">
+      <c r="K12" s="0">
         <f>100-ABS(F12-100)/100*100</f>
         <v/>
       </c>
-      <c r="L12">
+      <c r="L12" s="0">
         <f>IF(E12,0.4*K12+0.35*G12*10+0.25*H12,0)</f>
         <v/>
       </c>
-      <c r="M12">
+      <c r="M12" s="0">
         <f>G12*10</f>
         <v/>
       </c>
-      <c r="N12">
+      <c r="N12" s="0">
         <f>IFERROR(L12/SUMIF($D$2:$D$13,D12,$L$2:$L$13),0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>SEG-03</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>1|SEG-03</t>
         </is>
       </c>
-      <c r="E13">
+      <c r="E13" s="0">
         <f>TRUE()</f>
         <v/>
       </c>
-      <c r="F13">
+      <c r="F13" s="0">
         <f>IFERROR(('Lotes_Pipeline_sim1'!I13*'Lotes_Pipeline_sim1'!H13)/('Lotes_Pipeline_sim1'!H13),0)</f>
         <v/>
       </c>
-      <c r="G13">
+      <c r="G13" s="0">
         <f>'Pipeline_sim1'!DY5</f>
         <v/>
       </c>
-      <c r="H13">
+      <c r="H13" s="0">
         <f>IFERROR(ROUND(G13/SUMIFS($G$2:$G$13,$D$2:$D$13,D13,$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
-      <c r="I13">
+      <c r="I13" s="0">
         <f>MAX(0,ROUNDDOWN(J13*'Pipeline_sim1'!AN5*1.12,0))</f>
         <v/>
       </c>
-      <c r="J13">
+      <c r="J13" s="0">
         <f>IFERROR(ROUND(L13/SUMIF($D$2:$D$13,D13,$L$2:$L$13)*2000*0.4,0),0)</f>
         <v/>
       </c>
-      <c r="K13">
+      <c r="K13" s="0">
         <f>100-ABS(F13-250)/250*100</f>
         <v/>
       </c>
-      <c r="L13">
+      <c r="L13" s="0">
         <f>IF(E13,0.1*K13+0.5*G13*10+0.4*H13,0)</f>
         <v/>
       </c>
-      <c r="M13">
+      <c r="M13" s="0">
         <f>G13*10</f>
         <v/>
       </c>
-      <c r="N13">
+      <c r="N13" s="0">
         <f>IFERROR(L13/SUMIF($D$2:$D$13,D13,$L$2:$L$13),0)</f>
         <v/>
       </c>

--- a/tests/oracle/ORACULO_sim1.xlsx
+++ b/tests/oracle/ORACULO_sim1.xlsx
@@ -5386,242 +5386,242 @@
           <t>CONS-08</t>
         </is>
       </c>
-      <c r="FA1" t="inlineStr">
+      <c r="FA1" s="0" t="inlineStr">
         <is>
           <t>capitalInicial</t>
         </is>
       </c>
-      <c r="FB1" t="inlineStr">
+      <c r="FB1" s="0" t="inlineStr">
         <is>
           <t>compraActivos</t>
         </is>
       </c>
-      <c r="FC1" t="inlineStr">
+      <c r="FC1" s="0" t="inlineStr">
         <is>
           <t>adquisicionNeta</t>
         </is>
       </c>
-      <c r="FD1" t="inlineStr">
+      <c r="FD1" s="0" t="inlineStr">
         <is>
           <t>valorCompradoNeto</t>
         </is>
       </c>
-      <c r="FE1" t="inlineStr">
+      <c r="FE1" s="0" t="inlineStr">
         <is>
           <t>valorInventarioNeto</t>
         </is>
       </c>
-      <c r="FF1" t="inlineStr">
+      <c r="FF1" s="0" t="inlineStr">
         <is>
           <t>cajaInicial</t>
         </is>
       </c>
-      <c r="FG1" t="inlineStr">
+      <c r="FG1" s="0" t="inlineStr">
         <is>
           <t>tasaNuevoPrestamo</t>
         </is>
       </c>
-      <c r="FH1" t="inlineStr">
+      <c r="FH1" s="0" t="inlineStr">
         <is>
           <t>interesMensual</t>
         </is>
       </c>
-      <c r="FI1" t="inlineStr">
+      <c r="FI1" s="0" t="inlineStr">
         <is>
           <t>tasaMensual</t>
         </is>
       </c>
-      <c r="FJ1" t="inlineStr">
+      <c r="FJ1" s="0" t="inlineStr">
         <is>
           <t>intereses</t>
         </is>
       </c>
-      <c r="FK1" t="inlineStr">
+      <c r="FK1" s="0" t="inlineStr">
         <is>
           <t>pagosOperacion</t>
         </is>
       </c>
-      <c r="FL1" t="inlineStr">
+      <c r="FL1" s="0" t="inlineStr">
         <is>
           <t>cajaFinal</t>
         </is>
       </c>
-      <c r="FM1" t="inlineStr">
+      <c r="FM1" s="0" t="inlineStr">
         <is>
           <t>depreciacionAcumulada</t>
         </is>
       </c>
-      <c r="FN1" t="inlineStr">
+      <c r="FN1" s="0" t="inlineStr">
         <is>
           <t>activosCosto</t>
         </is>
       </c>
-      <c r="FO1" t="inlineStr">
+      <c r="FO1" s="0" t="inlineStr">
         <is>
           <t>activosFijos</t>
         </is>
       </c>
-      <c r="FP1" t="inlineStr">
+      <c r="FP1" s="0" t="inlineStr">
         <is>
           <t>financial.estadoResultados.ingresos</t>
         </is>
       </c>
-      <c r="FQ1" t="inlineStr">
+      <c r="FQ1" s="0" t="inlineStr">
         <is>
           <t>financial.estadoResultados.ventasNetas</t>
         </is>
       </c>
-      <c r="FR1" t="inlineStr">
+      <c r="FR1" s="0" t="inlineStr">
         <is>
           <t>financial.estadoResultados.costos</t>
         </is>
       </c>
-      <c r="FS1" t="inlineStr">
+      <c r="FS1" s="0" t="inlineStr">
         <is>
           <t>financial.estadoResultados.utilidad</t>
         </is>
       </c>
-      <c r="FT1" t="inlineStr">
+      <c r="FT1" s="0" t="inlineStr">
         <is>
           <t>financial.estadoResultados.depreciacion</t>
         </is>
       </c>
-      <c r="FU1" t="inlineStr">
+      <c r="FU1" s="0" t="inlineStr">
         <is>
           <t>financial.estadoResultados.intereses</t>
         </is>
       </c>
-      <c r="FV1" t="inlineStr">
+      <c r="FV1" s="0" t="inlineStr">
         <is>
           <t>financial.estadoResultados.costosProduccion</t>
         </is>
       </c>
-      <c r="FW1" t="inlineStr">
+      <c r="FW1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceCaja.cajaInicial</t>
         </is>
       </c>
-      <c r="FX1" t="inlineStr">
+      <c r="FX1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceCaja.entradas</t>
         </is>
       </c>
-      <c r="FY1" t="inlineStr">
+      <c r="FY1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceCaja.salidas</t>
         </is>
       </c>
-      <c r="FZ1" t="inlineStr">
+      <c r="FZ1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceCaja.cajaFinal</t>
         </is>
       </c>
-      <c r="GA1" t="inlineStr">
+      <c r="GA1" s="0" t="inlineStr">
         <is>
           <t>financial.flujoCaja.cajaInicial</t>
         </is>
       </c>
-      <c r="GB1" t="inlineStr">
+      <c r="GB1" s="0" t="inlineStr">
         <is>
           <t>financial.flujoCaja.cobrosVentas</t>
         </is>
       </c>
-      <c r="GC1" t="inlineStr">
+      <c r="GC1" s="0" t="inlineStr">
         <is>
           <t>financial.flujoCaja.pagosOperacion</t>
         </is>
       </c>
-      <c r="GD1" t="inlineStr">
+      <c r="GD1" s="0" t="inlineStr">
         <is>
           <t>financial.flujoCaja.compraActivos</t>
         </is>
       </c>
-      <c r="GE1" t="inlineStr">
+      <c r="GE1" s="0" t="inlineStr">
         <is>
           <t>financial.flujoCaja.financiamiento</t>
         </is>
       </c>
-      <c r="GF1" t="inlineStr">
+      <c r="GF1" s="0" t="inlineStr">
         <is>
           <t>financial.flujoCaja.operacion</t>
         </is>
       </c>
-      <c r="GG1" t="inlineStr">
+      <c r="GG1" s="0" t="inlineStr">
         <is>
           <t>financial.flujoCaja.inversion</t>
         </is>
       </c>
-      <c r="GH1" t="inlineStr">
+      <c r="GH1" s="0" t="inlineStr">
         <is>
           <t>financial.flujoCaja.flujoNeto</t>
         </is>
       </c>
-      <c r="GI1" t="inlineStr">
+      <c r="GI1" s="0" t="inlineStr">
         <is>
           <t>financial.flujoCaja.cajaFinal</t>
         </is>
       </c>
-      <c r="GJ1" t="inlineStr">
+      <c r="GJ1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.efectivo</t>
         </is>
       </c>
-      <c r="GK1" t="inlineStr">
+      <c r="GK1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.activosFijos</t>
         </is>
       </c>
-      <c r="GL1" t="inlineStr">
+      <c r="GL1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.inventarioMP</t>
         </is>
       </c>
-      <c r="GM1" t="inlineStr">
+      <c r="GM1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.activos</t>
         </is>
       </c>
-      <c r="GN1" t="inlineStr">
+      <c r="GN1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.deuda</t>
         </is>
       </c>
-      <c r="GO1" t="inlineStr">
+      <c r="GO1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.patrimonio</t>
         </is>
       </c>
-      <c r="GP1" t="inlineStr">
+      <c r="GP1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.pasivoPatrimonio</t>
         </is>
       </c>
-      <c r="GQ1" t="inlineStr">
+      <c r="GQ1" s="0" t="inlineStr">
         <is>
           <t>financial.financiamiento.montoPrestamo</t>
         </is>
       </c>
-      <c r="GR1" t="inlineStr">
+      <c r="GR1" s="0" t="inlineStr">
         <is>
           <t>financial.financiamiento.tasaTEA</t>
         </is>
       </c>
-      <c r="GS1" t="inlineStr">
+      <c r="GS1" s="0" t="inlineStr">
         <is>
           <t>financial.financiamiento.deudaPrincipal</t>
         </is>
       </c>
-      <c r="GT1" t="inlineStr">
+      <c r="GT1" s="0" t="inlineStr">
         <is>
           <t>financial.financiamiento.tasaAdicionalProximoPrestamo</t>
         </is>
       </c>
-      <c r="GU1" t="inlineStr">
+      <c r="GU1" s="0" t="inlineStr">
         <is>
           <t>financial.financiamiento.tasaMensual</t>
         </is>
       </c>
-      <c r="GV1" t="inlineStr">
+      <c r="GV1" s="0" t="inlineStr">
         <is>
           <t>financial.financiamiento.intereses</t>
         </is>
@@ -6218,194 +6218,194 @@
         <f>AND(K2=0,AF2&lt;5)</f>
         <v/>
       </c>
-      <c r="FA2" t="n">
+      <c r="FA2" s="0" t="n">
         <v>1000000</v>
       </c>
-      <c r="FB2">
+      <c r="FB2" s="0">
         <f>1*2500*(1+0.03+0.02)+1*3500*(1+0.03+0.02)+1*1200*(1+0.03+0.02)+1*300*(1+0+0.01)</f>
         <v/>
       </c>
-      <c r="FC2">
+      <c r="FC2" s="0">
         <f>1*2500+1*3500+1*1200+1*300</f>
         <v/>
       </c>
-      <c r="FD2">
+      <c r="FD2" s="0">
         <f>(CF2*25+CH2*45+CJ2*80+CL2*4+CN2*9+CP2*2+CR2*4+CT2*7)*0.8924</f>
         <v/>
       </c>
-      <c r="FE2">
+      <c r="FE2" s="0">
         <f>(DC2*25+DE2*45+DG2*80+DJ2*4+DL2*9+DO2*2+DQ2*4+DS2*7)*0.8924</f>
         <v/>
       </c>
-      <c r="FF2">
+      <c r="FF2" s="0">
         <f>FA2</f>
         <v/>
       </c>
-      <c r="FG2">
+      <c r="FG2" s="0">
         <f>(1+AR2/100)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="FH2">
+      <c r="FH2" s="0">
         <f>0*0+AP2*FG2</f>
         <v/>
       </c>
-      <c r="FI2">
+      <c r="FI2" s="0">
         <f>IFERROR(FH2/(0+AP2),0)</f>
         <v/>
       </c>
-      <c r="FJ2">
+      <c r="FJ2" s="0">
         <f>FH2*1</f>
         <v/>
       </c>
-      <c r="FK2">
+      <c r="FK2" s="0">
         <f>EQ2-DW2-DU2+FD2+FJ2</f>
         <v/>
       </c>
-      <c r="FL2">
+      <c r="FL2" s="0">
         <f>FF2+EJ2+AP2-FK2-FB2</f>
         <v/>
       </c>
-      <c r="FM2">
+      <c r="FM2" s="0">
         <f>0+DW2</f>
         <v/>
       </c>
-      <c r="FN2">
+      <c r="FN2" s="0">
         <f>0+FC2</f>
         <v/>
       </c>
-      <c r="FO2">
+      <c r="FO2" s="0">
         <f>FN2-FM2</f>
         <v/>
       </c>
-      <c r="FP2">
+      <c r="FP2" s="0">
         <f>EJ2</f>
         <v/>
       </c>
-      <c r="FQ2">
+      <c r="FQ2" s="0">
         <f>EJ2</f>
         <v/>
       </c>
-      <c r="FR2">
+      <c r="FR2" s="0">
         <f>EQ2+FJ2</f>
         <v/>
       </c>
-      <c r="FS2">
+      <c r="FS2" s="0">
         <f>ER2-FJ2</f>
         <v/>
       </c>
-      <c r="FT2">
+      <c r="FT2" s="0">
         <f>DW2</f>
         <v/>
       </c>
-      <c r="FU2">
+      <c r="FU2" s="0">
         <f>FJ2</f>
         <v/>
       </c>
-      <c r="FV2">
+      <c r="FV2" s="0">
         <f>EQ2</f>
         <v/>
       </c>
-      <c r="FW2">
+      <c r="FW2" s="0">
         <f>FF2</f>
         <v/>
       </c>
-      <c r="FX2">
+      <c r="FX2" s="0">
         <f>EJ2+AP2</f>
         <v/>
       </c>
-      <c r="FY2">
+      <c r="FY2" s="0">
         <f>FK2+FB2</f>
         <v/>
       </c>
-      <c r="FZ2">
+      <c r="FZ2" s="0">
         <f>FL2</f>
         <v/>
       </c>
-      <c r="GA2">
+      <c r="GA2" s="0">
         <f>FF2</f>
         <v/>
       </c>
-      <c r="GB2">
+      <c r="GB2" s="0">
         <f>EJ2</f>
         <v/>
       </c>
-      <c r="GC2">
+      <c r="GC2" s="0">
         <f>FK2</f>
         <v/>
       </c>
-      <c r="GD2">
+      <c r="GD2" s="0">
         <f>FB2</f>
         <v/>
       </c>
-      <c r="GE2">
+      <c r="GE2" s="0">
         <f>AP2</f>
         <v/>
       </c>
-      <c r="GF2">
+      <c r="GF2" s="0">
         <f>EJ2-FK2</f>
         <v/>
       </c>
-      <c r="GG2">
+      <c r="GG2" s="0">
         <f>-FB2</f>
         <v/>
       </c>
-      <c r="GH2">
+      <c r="GH2" s="0">
         <f>FL2-FF2</f>
         <v/>
       </c>
-      <c r="GI2">
+      <c r="GI2" s="0">
         <f>FL2</f>
         <v/>
       </c>
-      <c r="GJ2">
+      <c r="GJ2" s="0">
         <f>FL2</f>
         <v/>
       </c>
-      <c r="GK2">
+      <c r="GK2" s="0">
         <f>FO2</f>
         <v/>
       </c>
-      <c r="GL2">
+      <c r="GL2" s="0">
         <f>FE2</f>
         <v/>
       </c>
-      <c r="GM2">
+      <c r="GM2" s="0">
         <f>FL2+FO2+FE2</f>
         <v/>
       </c>
-      <c r="GN2">
+      <c r="GN2" s="0">
         <f>AS2</f>
         <v/>
       </c>
-      <c r="GO2">
+      <c r="GO2" s="0">
         <f>FL2+FO2+FE2-AS2</f>
         <v/>
       </c>
-      <c r="GP2">
+      <c r="GP2" s="0">
         <f>FL2+FO2+FE2</f>
         <v/>
       </c>
-      <c r="GQ2">
+      <c r="GQ2" s="0">
         <f>AP2</f>
         <v/>
       </c>
-      <c r="GR2">
+      <c r="GR2" s="0">
         <f>AR2</f>
         <v/>
       </c>
-      <c r="GS2">
+      <c r="GS2" s="0">
         <f>AS2</f>
         <v/>
       </c>
-      <c r="GT2">
+      <c r="GT2" s="0">
         <f>AT2</f>
         <v/>
       </c>
-      <c r="GU2">
+      <c r="GU2" s="0">
         <f>FI2</f>
         <v/>
       </c>
-      <c r="GV2">
+      <c r="GV2" s="0">
         <f>FJ2</f>
         <v/>
       </c>
@@ -7001,194 +7001,194 @@
         <f>AND(K3=0,AF3&lt;5)</f>
         <v/>
       </c>
-      <c r="FA3" t="n">
+      <c r="FA3" s="0" t="n">
         <v>1000000</v>
       </c>
-      <c r="FB3">
+      <c r="FB3" s="0">
         <f>1*2500*(1+0.03+0.02)+1*3500*(1+0.03+0.02)+1*1200*(1+0.03+0.02)+1*300*(1+0+0.01)</f>
         <v/>
       </c>
-      <c r="FC3">
+      <c r="FC3" s="0">
         <f>1*2500+1*3500+1*1200+1*300</f>
         <v/>
       </c>
-      <c r="FD3">
+      <c r="FD3" s="0">
         <f>(CF3*25+CH3*45+CJ3*80+CL3*4+CN3*9+CP3*2+CR3*4+CT3*7)*0.8924</f>
         <v/>
       </c>
-      <c r="FE3">
+      <c r="FE3" s="0">
         <f>(DC3*25+DE3*45+DG3*80+DJ3*4+DL3*9+DO3*2+DQ3*4+DS3*7)*0.8924</f>
         <v/>
       </c>
-      <c r="FF3">
+      <c r="FF3" s="0">
         <f>FA3</f>
         <v/>
       </c>
-      <c r="FG3">
+      <c r="FG3" s="0">
         <f>(1+AR3/100)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="FH3">
+      <c r="FH3" s="0">
         <f>0*0+AP3*FG3</f>
         <v/>
       </c>
-      <c r="FI3">
+      <c r="FI3" s="0">
         <f>IFERROR(FH3/(0+AP3),0)</f>
         <v/>
       </c>
-      <c r="FJ3">
+      <c r="FJ3" s="0">
         <f>FH3*1</f>
         <v/>
       </c>
-      <c r="FK3">
+      <c r="FK3" s="0">
         <f>EQ3-DW3-DU3+FD3+FJ3</f>
         <v/>
       </c>
-      <c r="FL3">
+      <c r="FL3" s="0">
         <f>FF3+EJ3+AP3-FK3-FB3</f>
         <v/>
       </c>
-      <c r="FM3">
+      <c r="FM3" s="0">
         <f>0+DW3</f>
         <v/>
       </c>
-      <c r="FN3">
+      <c r="FN3" s="0">
         <f>0+FC3</f>
         <v/>
       </c>
-      <c r="FO3">
+      <c r="FO3" s="0">
         <f>FN3-FM3</f>
         <v/>
       </c>
-      <c r="FP3">
+      <c r="FP3" s="0">
         <f>EJ3</f>
         <v/>
       </c>
-      <c r="FQ3">
+      <c r="FQ3" s="0">
         <f>EJ3</f>
         <v/>
       </c>
-      <c r="FR3">
+      <c r="FR3" s="0">
         <f>EQ3+FJ3</f>
         <v/>
       </c>
-      <c r="FS3">
+      <c r="FS3" s="0">
         <f>ER3-FJ3</f>
         <v/>
       </c>
-      <c r="FT3">
+      <c r="FT3" s="0">
         <f>DW3</f>
         <v/>
       </c>
-      <c r="FU3">
+      <c r="FU3" s="0">
         <f>FJ3</f>
         <v/>
       </c>
-      <c r="FV3">
+      <c r="FV3" s="0">
         <f>EQ3</f>
         <v/>
       </c>
-      <c r="FW3">
+      <c r="FW3" s="0">
         <f>FF3</f>
         <v/>
       </c>
-      <c r="FX3">
+      <c r="FX3" s="0">
         <f>EJ3+AP3</f>
         <v/>
       </c>
-      <c r="FY3">
+      <c r="FY3" s="0">
         <f>FK3+FB3</f>
         <v/>
       </c>
-      <c r="FZ3">
+      <c r="FZ3" s="0">
         <f>FL3</f>
         <v/>
       </c>
-      <c r="GA3">
+      <c r="GA3" s="0">
         <f>FF3</f>
         <v/>
       </c>
-      <c r="GB3">
+      <c r="GB3" s="0">
         <f>EJ3</f>
         <v/>
       </c>
-      <c r="GC3">
+      <c r="GC3" s="0">
         <f>FK3</f>
         <v/>
       </c>
-      <c r="GD3">
+      <c r="GD3" s="0">
         <f>FB3</f>
         <v/>
       </c>
-      <c r="GE3">
+      <c r="GE3" s="0">
         <f>AP3</f>
         <v/>
       </c>
-      <c r="GF3">
+      <c r="GF3" s="0">
         <f>EJ3-FK3</f>
         <v/>
       </c>
-      <c r="GG3">
+      <c r="GG3" s="0">
         <f>-FB3</f>
         <v/>
       </c>
-      <c r="GH3">
+      <c r="GH3" s="0">
         <f>FL3-FF3</f>
         <v/>
       </c>
-      <c r="GI3">
+      <c r="GI3" s="0">
         <f>FL3</f>
         <v/>
       </c>
-      <c r="GJ3">
+      <c r="GJ3" s="0">
         <f>FL3</f>
         <v/>
       </c>
-      <c r="GK3">
+      <c r="GK3" s="0">
         <f>FO3</f>
         <v/>
       </c>
-      <c r="GL3">
+      <c r="GL3" s="0">
         <f>FE3</f>
         <v/>
       </c>
-      <c r="GM3">
+      <c r="GM3" s="0">
         <f>FL3+FO3+FE3</f>
         <v/>
       </c>
-      <c r="GN3">
+      <c r="GN3" s="0">
         <f>AS3</f>
         <v/>
       </c>
-      <c r="GO3">
+      <c r="GO3" s="0">
         <f>FL3+FO3+FE3-AS3</f>
         <v/>
       </c>
-      <c r="GP3">
+      <c r="GP3" s="0">
         <f>FL3+FO3+FE3</f>
         <v/>
       </c>
-      <c r="GQ3">
+      <c r="GQ3" s="0">
         <f>AP3</f>
         <v/>
       </c>
-      <c r="GR3">
+      <c r="GR3" s="0">
         <f>AR3</f>
         <v/>
       </c>
-      <c r="GS3">
+      <c r="GS3" s="0">
         <f>AS3</f>
         <v/>
       </c>
-      <c r="GT3">
+      <c r="GT3" s="0">
         <f>AT3</f>
         <v/>
       </c>
-      <c r="GU3">
+      <c r="GU3" s="0">
         <f>FI3</f>
         <v/>
       </c>
-      <c r="GV3">
+      <c r="GV3" s="0">
         <f>FJ3</f>
         <v/>
       </c>
@@ -7784,194 +7784,194 @@
         <f>AND(K4=0,AF4&lt;5)</f>
         <v/>
       </c>
-      <c r="FA4" t="n">
+      <c r="FA4" s="0" t="n">
         <v>1000000</v>
       </c>
-      <c r="FB4">
+      <c r="FB4" s="0">
         <f>1*2500*(1+0.03+0.02)+1*3500*(1+0.03+0.02)+1*1200*(1+0.03+0.02)+1*300*(1+0+0.01)</f>
         <v/>
       </c>
-      <c r="FC4">
+      <c r="FC4" s="0">
         <f>1*2500+1*3500+1*1200+1*300</f>
         <v/>
       </c>
-      <c r="FD4">
+      <c r="FD4" s="0">
         <f>(CF4*25+CH4*45+CJ4*80+CL4*4+CN4*9+CP4*2+CR4*4+CT4*7)*0.8924</f>
         <v/>
       </c>
-      <c r="FE4">
+      <c r="FE4" s="0">
         <f>(DC4*25+DE4*45+DG4*80+DJ4*4+DL4*9+DO4*2+DQ4*4+DS4*7)*0.8924</f>
         <v/>
       </c>
-      <c r="FF4">
+      <c r="FF4" s="0">
         <f>FA4</f>
         <v/>
       </c>
-      <c r="FG4">
+      <c r="FG4" s="0">
         <f>(1+AR4/100)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="FH4">
+      <c r="FH4" s="0">
         <f>0*0+AP4*FG4</f>
         <v/>
       </c>
-      <c r="FI4">
+      <c r="FI4" s="0">
         <f>IFERROR(FH4/(0+AP4),0)</f>
         <v/>
       </c>
-      <c r="FJ4">
+      <c r="FJ4" s="0">
         <f>FH4*1</f>
         <v/>
       </c>
-      <c r="FK4">
+      <c r="FK4" s="0">
         <f>EQ4-DW4-DU4+FD4+FJ4</f>
         <v/>
       </c>
-      <c r="FL4">
+      <c r="FL4" s="0">
         <f>FF4+EJ4+AP4-FK4-FB4</f>
         <v/>
       </c>
-      <c r="FM4">
+      <c r="FM4" s="0">
         <f>0+DW4</f>
         <v/>
       </c>
-      <c r="FN4">
+      <c r="FN4" s="0">
         <f>0+FC4</f>
         <v/>
       </c>
-      <c r="FO4">
+      <c r="FO4" s="0">
         <f>FN4-FM4</f>
         <v/>
       </c>
-      <c r="FP4">
+      <c r="FP4" s="0">
         <f>EJ4</f>
         <v/>
       </c>
-      <c r="FQ4">
+      <c r="FQ4" s="0">
         <f>EJ4</f>
         <v/>
       </c>
-      <c r="FR4">
+      <c r="FR4" s="0">
         <f>EQ4+FJ4</f>
         <v/>
       </c>
-      <c r="FS4">
+      <c r="FS4" s="0">
         <f>ER4-FJ4</f>
         <v/>
       </c>
-      <c r="FT4">
+      <c r="FT4" s="0">
         <f>DW4</f>
         <v/>
       </c>
-      <c r="FU4">
+      <c r="FU4" s="0">
         <f>FJ4</f>
         <v/>
       </c>
-      <c r="FV4">
+      <c r="FV4" s="0">
         <f>EQ4</f>
         <v/>
       </c>
-      <c r="FW4">
+      <c r="FW4" s="0">
         <f>FF4</f>
         <v/>
       </c>
-      <c r="FX4">
+      <c r="FX4" s="0">
         <f>EJ4+AP4</f>
         <v/>
       </c>
-      <c r="FY4">
+      <c r="FY4" s="0">
         <f>FK4+FB4</f>
         <v/>
       </c>
-      <c r="FZ4">
+      <c r="FZ4" s="0">
         <f>FL4</f>
         <v/>
       </c>
-      <c r="GA4">
+      <c r="GA4" s="0">
         <f>FF4</f>
         <v/>
       </c>
-      <c r="GB4">
+      <c r="GB4" s="0">
         <f>EJ4</f>
         <v/>
       </c>
-      <c r="GC4">
+      <c r="GC4" s="0">
         <f>FK4</f>
         <v/>
       </c>
-      <c r="GD4">
+      <c r="GD4" s="0">
         <f>FB4</f>
         <v/>
       </c>
-      <c r="GE4">
+      <c r="GE4" s="0">
         <f>AP4</f>
         <v/>
       </c>
-      <c r="GF4">
+      <c r="GF4" s="0">
         <f>EJ4-FK4</f>
         <v/>
       </c>
-      <c r="GG4">
+      <c r="GG4" s="0">
         <f>-FB4</f>
         <v/>
       </c>
-      <c r="GH4">
+      <c r="GH4" s="0">
         <f>FL4-FF4</f>
         <v/>
       </c>
-      <c r="GI4">
+      <c r="GI4" s="0">
         <f>FL4</f>
         <v/>
       </c>
-      <c r="GJ4">
+      <c r="GJ4" s="0">
         <f>FL4</f>
         <v/>
       </c>
-      <c r="GK4">
+      <c r="GK4" s="0">
         <f>FO4</f>
         <v/>
       </c>
-      <c r="GL4">
+      <c r="GL4" s="0">
         <f>FE4</f>
         <v/>
       </c>
-      <c r="GM4">
+      <c r="GM4" s="0">
         <f>FL4+FO4+FE4</f>
         <v/>
       </c>
-      <c r="GN4">
+      <c r="GN4" s="0">
         <f>AS4</f>
         <v/>
       </c>
-      <c r="GO4">
+      <c r="GO4" s="0">
         <f>FL4+FO4+FE4-AS4</f>
         <v/>
       </c>
-      <c r="GP4">
+      <c r="GP4" s="0">
         <f>FL4+FO4+FE4</f>
         <v/>
       </c>
-      <c r="GQ4">
+      <c r="GQ4" s="0">
         <f>AP4</f>
         <v/>
       </c>
-      <c r="GR4">
+      <c r="GR4" s="0">
         <f>AR4</f>
         <v/>
       </c>
-      <c r="GS4">
+      <c r="GS4" s="0">
         <f>AS4</f>
         <v/>
       </c>
-      <c r="GT4">
+      <c r="GT4" s="0">
         <f>AT4</f>
         <v/>
       </c>
-      <c r="GU4">
+      <c r="GU4" s="0">
         <f>FI4</f>
         <v/>
       </c>
-      <c r="GV4">
+      <c r="GV4" s="0">
         <f>FJ4</f>
         <v/>
       </c>
@@ -8567,194 +8567,194 @@
         <f>AND(K5=0,AF5&lt;5)</f>
         <v/>
       </c>
-      <c r="FA5" t="n">
+      <c r="FA5" s="0" t="n">
         <v>1000000</v>
       </c>
-      <c r="FB5">
+      <c r="FB5" s="0">
         <f>1*2500*(1+0.03+0.02)+1*3500*(1+0.03+0.02)+1*1200*(1+0.03+0.02)+1*300*(1+0+0.01)</f>
         <v/>
       </c>
-      <c r="FC5">
+      <c r="FC5" s="0">
         <f>1*2500+1*3500+1*1200+1*300</f>
         <v/>
       </c>
-      <c r="FD5">
+      <c r="FD5" s="0">
         <f>(CF5*25+CH5*45+CJ5*80+CL5*4+CN5*9+CP5*2+CR5*4+CT5*7)*0.8924</f>
         <v/>
       </c>
-      <c r="FE5">
+      <c r="FE5" s="0">
         <f>(DC5*25+DE5*45+DG5*80+DJ5*4+DL5*9+DO5*2+DQ5*4+DS5*7)*0.8924</f>
         <v/>
       </c>
-      <c r="FF5">
+      <c r="FF5" s="0">
         <f>FA5</f>
         <v/>
       </c>
-      <c r="FG5">
+      <c r="FG5" s="0">
         <f>(1+AR5/100)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="FH5">
+      <c r="FH5" s="0">
         <f>0*0+AP5*FG5</f>
         <v/>
       </c>
-      <c r="FI5">
+      <c r="FI5" s="0">
         <f>IFERROR(FH5/(0+AP5),0)</f>
         <v/>
       </c>
-      <c r="FJ5">
+      <c r="FJ5" s="0">
         <f>FH5*1</f>
         <v/>
       </c>
-      <c r="FK5">
+      <c r="FK5" s="0">
         <f>EQ5-DW5-DU5+FD5+FJ5</f>
         <v/>
       </c>
-      <c r="FL5">
+      <c r="FL5" s="0">
         <f>FF5+EJ5+AP5-FK5-FB5</f>
         <v/>
       </c>
-      <c r="FM5">
+      <c r="FM5" s="0">
         <f>0+DW5</f>
         <v/>
       </c>
-      <c r="FN5">
+      <c r="FN5" s="0">
         <f>0+FC5</f>
         <v/>
       </c>
-      <c r="FO5">
+      <c r="FO5" s="0">
         <f>FN5-FM5</f>
         <v/>
       </c>
-      <c r="FP5">
+      <c r="FP5" s="0">
         <f>EJ5</f>
         <v/>
       </c>
-      <c r="FQ5">
+      <c r="FQ5" s="0">
         <f>EJ5</f>
         <v/>
       </c>
-      <c r="FR5">
+      <c r="FR5" s="0">
         <f>EQ5+FJ5</f>
         <v/>
       </c>
-      <c r="FS5">
+      <c r="FS5" s="0">
         <f>ER5-FJ5</f>
         <v/>
       </c>
-      <c r="FT5">
+      <c r="FT5" s="0">
         <f>DW5</f>
         <v/>
       </c>
-      <c r="FU5">
+      <c r="FU5" s="0">
         <f>FJ5</f>
         <v/>
       </c>
-      <c r="FV5">
+      <c r="FV5" s="0">
         <f>EQ5</f>
         <v/>
       </c>
-      <c r="FW5">
+      <c r="FW5" s="0">
         <f>FF5</f>
         <v/>
       </c>
-      <c r="FX5">
+      <c r="FX5" s="0">
         <f>EJ5+AP5</f>
         <v/>
       </c>
-      <c r="FY5">
+      <c r="FY5" s="0">
         <f>FK5+FB5</f>
         <v/>
       </c>
-      <c r="FZ5">
+      <c r="FZ5" s="0">
         <f>FL5</f>
         <v/>
       </c>
-      <c r="GA5">
+      <c r="GA5" s="0">
         <f>FF5</f>
         <v/>
       </c>
-      <c r="GB5">
+      <c r="GB5" s="0">
         <f>EJ5</f>
         <v/>
       </c>
-      <c r="GC5">
+      <c r="GC5" s="0">
         <f>FK5</f>
         <v/>
       </c>
-      <c r="GD5">
+      <c r="GD5" s="0">
         <f>FB5</f>
         <v/>
       </c>
-      <c r="GE5">
+      <c r="GE5" s="0">
         <f>AP5</f>
         <v/>
       </c>
-      <c r="GF5">
+      <c r="GF5" s="0">
         <f>EJ5-FK5</f>
         <v/>
       </c>
-      <c r="GG5">
+      <c r="GG5" s="0">
         <f>-FB5</f>
         <v/>
       </c>
-      <c r="GH5">
+      <c r="GH5" s="0">
         <f>FL5-FF5</f>
         <v/>
       </c>
-      <c r="GI5">
+      <c r="GI5" s="0">
         <f>FL5</f>
         <v/>
       </c>
-      <c r="GJ5">
+      <c r="GJ5" s="0">
         <f>FL5</f>
         <v/>
       </c>
-      <c r="GK5">
+      <c r="GK5" s="0">
         <f>FO5</f>
         <v/>
       </c>
-      <c r="GL5">
+      <c r="GL5" s="0">
         <f>FE5</f>
         <v/>
       </c>
-      <c r="GM5">
+      <c r="GM5" s="0">
         <f>FL5+FO5+FE5</f>
         <v/>
       </c>
-      <c r="GN5">
+      <c r="GN5" s="0">
         <f>AS5</f>
         <v/>
       </c>
-      <c r="GO5">
+      <c r="GO5" s="0">
         <f>FL5+FO5+FE5-AS5</f>
         <v/>
       </c>
-      <c r="GP5">
+      <c r="GP5" s="0">
         <f>FL5+FO5+FE5</f>
         <v/>
       </c>
-      <c r="GQ5">
+      <c r="GQ5" s="0">
         <f>AP5</f>
         <v/>
       </c>
-      <c r="GR5">
+      <c r="GR5" s="0">
         <f>AR5</f>
         <v/>
       </c>
-      <c r="GS5">
+      <c r="GS5" s="0">
         <f>AS5</f>
         <v/>
       </c>
-      <c r="GT5">
+      <c r="GT5" s="0">
         <f>AT5</f>
         <v/>
       </c>
-      <c r="GU5">
+      <c r="GU5" s="0">
         <f>FI5</f>
         <v/>
       </c>
-      <c r="GV5">
+      <c r="GV5" s="0">
         <f>FJ5</f>
         <v/>
       </c>

--- a/tests/oracle/ORACULO_sim1.xlsx
+++ b/tests/oracle/ORACULO_sim1.xlsx
@@ -4444,7 +4444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GV5"/>
+  <dimension ref="A1:GW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="184" min="1" max="1"/>
@@ -4603,6 +4603,7 @@
     <col width="20" customWidth="1" style="184" min="154" max="154"/>
     <col width="20" customWidth="1" style="184" min="155" max="155"/>
     <col width="20" customWidth="1" style="184" min="156" max="156"/>
+    <col width="20" customWidth="1" style="184" min="157" max="157"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5338,290 +5339,295 @@
       </c>
       <c r="EQ1" s="0" t="inlineStr">
         <is>
+          <t>costoAnalista</t>
+        </is>
+      </c>
+      <c r="ER1" s="0" t="inlineStr">
+        <is>
           <t>costosTotales</t>
         </is>
       </c>
-      <c r="ER1" s="0" t="inlineStr">
+      <c r="ES1" s="0" t="inlineStr">
         <is>
           <t>utilidad</t>
         </is>
       </c>
-      <c r="ES1" s="0" t="inlineStr">
+      <c r="ET1" s="0" t="inlineStr">
         <is>
           <t>CONS-01</t>
         </is>
       </c>
-      <c r="ET1" s="0" t="inlineStr">
+      <c r="EU1" s="0" t="inlineStr">
         <is>
           <t>CONS-02</t>
         </is>
       </c>
-      <c r="EU1" s="0" t="inlineStr">
+      <c r="EV1" s="0" t="inlineStr">
         <is>
           <t>CONS-03</t>
         </is>
       </c>
-      <c r="EV1" s="0" t="inlineStr">
+      <c r="EW1" s="0" t="inlineStr">
         <is>
           <t>CONS-04</t>
         </is>
       </c>
-      <c r="EW1" s="0" t="inlineStr">
+      <c r="EX1" s="0" t="inlineStr">
         <is>
           <t>CONS-05</t>
         </is>
       </c>
-      <c r="EX1" s="0" t="inlineStr">
+      <c r="EY1" s="0" t="inlineStr">
         <is>
           <t>CONS-06</t>
         </is>
       </c>
-      <c r="EY1" s="0" t="inlineStr">
+      <c r="EZ1" s="0" t="inlineStr">
         <is>
           <t>CONS-07</t>
         </is>
       </c>
-      <c r="EZ1" s="0" t="inlineStr">
+      <c r="FA1" s="0" t="inlineStr">
         <is>
           <t>CONS-08</t>
         </is>
       </c>
-      <c r="FA1" s="0" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>capitalInicial</t>
         </is>
       </c>
-      <c r="FB1" s="0" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>compraActivos</t>
         </is>
       </c>
-      <c r="FC1" s="0" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>adquisicionNeta</t>
         </is>
       </c>
-      <c r="FD1" s="0" t="inlineStr">
+      <c r="FE1" t="inlineStr">
         <is>
           <t>valorCompradoNeto</t>
         </is>
       </c>
-      <c r="FE1" s="0" t="inlineStr">
+      <c r="FF1" t="inlineStr">
         <is>
           <t>valorInventarioNeto</t>
         </is>
       </c>
-      <c r="FF1" s="0" t="inlineStr">
+      <c r="FG1" t="inlineStr">
         <is>
           <t>cajaInicial</t>
         </is>
       </c>
-      <c r="FG1" s="0" t="inlineStr">
+      <c r="FH1" t="inlineStr">
         <is>
           <t>tasaNuevoPrestamo</t>
         </is>
       </c>
-      <c r="FH1" s="0" t="inlineStr">
+      <c r="FI1" t="inlineStr">
         <is>
           <t>interesMensual</t>
         </is>
       </c>
-      <c r="FI1" s="0" t="inlineStr">
+      <c r="FJ1" t="inlineStr">
         <is>
           <t>tasaMensual</t>
         </is>
       </c>
-      <c r="FJ1" s="0" t="inlineStr">
+      <c r="FK1" t="inlineStr">
         <is>
           <t>intereses</t>
         </is>
       </c>
-      <c r="FK1" s="0" t="inlineStr">
+      <c r="FL1" t="inlineStr">
         <is>
           <t>pagosOperacion</t>
         </is>
       </c>
-      <c r="FL1" s="0" t="inlineStr">
+      <c r="FM1" t="inlineStr">
         <is>
           <t>cajaFinal</t>
         </is>
       </c>
-      <c r="FM1" s="0" t="inlineStr">
+      <c r="FN1" t="inlineStr">
         <is>
           <t>depreciacionAcumulada</t>
         </is>
       </c>
-      <c r="FN1" s="0" t="inlineStr">
+      <c r="FO1" t="inlineStr">
         <is>
           <t>activosCosto</t>
         </is>
       </c>
-      <c r="FO1" s="0" t="inlineStr">
+      <c r="FP1" t="inlineStr">
         <is>
           <t>activosFijos</t>
         </is>
       </c>
-      <c r="FP1" s="0" t="inlineStr">
+      <c r="FQ1" t="inlineStr">
         <is>
           <t>financial.estadoResultados.ingresos</t>
         </is>
       </c>
-      <c r="FQ1" s="0" t="inlineStr">
+      <c r="FR1" t="inlineStr">
         <is>
           <t>financial.estadoResultados.ventasNetas</t>
         </is>
       </c>
-      <c r="FR1" s="0" t="inlineStr">
+      <c r="FS1" t="inlineStr">
         <is>
           <t>financial.estadoResultados.costos</t>
         </is>
       </c>
-      <c r="FS1" s="0" t="inlineStr">
+      <c r="FT1" t="inlineStr">
         <is>
           <t>financial.estadoResultados.utilidad</t>
         </is>
       </c>
-      <c r="FT1" s="0" t="inlineStr">
+      <c r="FU1" t="inlineStr">
         <is>
           <t>financial.estadoResultados.depreciacion</t>
         </is>
       </c>
-      <c r="FU1" s="0" t="inlineStr">
+      <c r="FV1" t="inlineStr">
         <is>
           <t>financial.estadoResultados.intereses</t>
         </is>
       </c>
-      <c r="FV1" s="0" t="inlineStr">
+      <c r="FW1" t="inlineStr">
         <is>
           <t>financial.estadoResultados.costosProduccion</t>
         </is>
       </c>
-      <c r="FW1" s="0" t="inlineStr">
+      <c r="FX1" t="inlineStr">
         <is>
           <t>financial.balanceCaja.cajaInicial</t>
         </is>
       </c>
-      <c r="FX1" s="0" t="inlineStr">
+      <c r="FY1" t="inlineStr">
         <is>
           <t>financial.balanceCaja.entradas</t>
         </is>
       </c>
-      <c r="FY1" s="0" t="inlineStr">
+      <c r="FZ1" t="inlineStr">
         <is>
           <t>financial.balanceCaja.salidas</t>
         </is>
       </c>
-      <c r="FZ1" s="0" t="inlineStr">
+      <c r="GA1" t="inlineStr">
         <is>
           <t>financial.balanceCaja.cajaFinal</t>
         </is>
       </c>
-      <c r="GA1" s="0" t="inlineStr">
+      <c r="GB1" t="inlineStr">
         <is>
           <t>financial.flujoCaja.cajaInicial</t>
         </is>
       </c>
-      <c r="GB1" s="0" t="inlineStr">
+      <c r="GC1" t="inlineStr">
         <is>
           <t>financial.flujoCaja.cobrosVentas</t>
         </is>
       </c>
-      <c r="GC1" s="0" t="inlineStr">
+      <c r="GD1" t="inlineStr">
         <is>
           <t>financial.flujoCaja.pagosOperacion</t>
         </is>
       </c>
-      <c r="GD1" s="0" t="inlineStr">
+      <c r="GE1" t="inlineStr">
         <is>
           <t>financial.flujoCaja.compraActivos</t>
         </is>
       </c>
-      <c r="GE1" s="0" t="inlineStr">
+      <c r="GF1" t="inlineStr">
         <is>
           <t>financial.flujoCaja.financiamiento</t>
         </is>
       </c>
-      <c r="GF1" s="0" t="inlineStr">
+      <c r="GG1" t="inlineStr">
         <is>
           <t>financial.flujoCaja.operacion</t>
         </is>
       </c>
-      <c r="GG1" s="0" t="inlineStr">
+      <c r="GH1" t="inlineStr">
         <is>
           <t>financial.flujoCaja.inversion</t>
         </is>
       </c>
-      <c r="GH1" s="0" t="inlineStr">
+      <c r="GI1" t="inlineStr">
         <is>
           <t>financial.flujoCaja.flujoNeto</t>
         </is>
       </c>
-      <c r="GI1" s="0" t="inlineStr">
+      <c r="GJ1" t="inlineStr">
         <is>
           <t>financial.flujoCaja.cajaFinal</t>
         </is>
       </c>
-      <c r="GJ1" s="0" t="inlineStr">
+      <c r="GK1" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.efectivo</t>
         </is>
       </c>
-      <c r="GK1" s="0" t="inlineStr">
+      <c r="GL1" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.activosFijos</t>
         </is>
       </c>
-      <c r="GL1" s="0" t="inlineStr">
+      <c r="GM1" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.inventarioMP</t>
         </is>
       </c>
-      <c r="GM1" s="0" t="inlineStr">
+      <c r="GN1" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.activos</t>
         </is>
       </c>
-      <c r="GN1" s="0" t="inlineStr">
+      <c r="GO1" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.deuda</t>
         </is>
       </c>
-      <c r="GO1" s="0" t="inlineStr">
+      <c r="GP1" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.patrimonio</t>
         </is>
       </c>
-      <c r="GP1" s="0" t="inlineStr">
+      <c r="GQ1" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.pasivoPatrimonio</t>
         </is>
       </c>
-      <c r="GQ1" s="0" t="inlineStr">
+      <c r="GR1" t="inlineStr">
         <is>
           <t>financial.financiamiento.montoPrestamo</t>
         </is>
       </c>
-      <c r="GR1" s="0" t="inlineStr">
+      <c r="GS1" t="inlineStr">
         <is>
           <t>financial.financiamiento.tasaTEA</t>
         </is>
       </c>
-      <c r="GS1" s="0" t="inlineStr">
+      <c r="GT1" t="inlineStr">
         <is>
           <t>financial.financiamiento.deudaPrincipal</t>
         </is>
       </c>
-      <c r="GT1" s="0" t="inlineStr">
+      <c r="GU1" t="inlineStr">
         <is>
           <t>financial.financiamiento.tasaAdicionalProximoPrestamo</t>
         </is>
       </c>
-      <c r="GU1" s="0" t="inlineStr">
+      <c r="GV1" t="inlineStr">
         <is>
           <t>financial.financiamiento.tasaMensual</t>
         </is>
       </c>
-      <c r="GV1" s="0" t="inlineStr">
+      <c r="GW1" t="inlineStr">
         <is>
           <t>financial.financiamiento.intereses</t>
         </is>
@@ -5676,7 +5682,7 @@
         <v>1</v>
       </c>
       <c r="L2" s="0" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="M2" s="0" t="inlineStr">
         <is>
@@ -5730,43 +5736,35 @@
       </c>
       <c r="W2" s="0" t="inlineStr">
         <is>
-          <t>INS-09B</t>
+          <t>INV-01B</t>
         </is>
       </c>
       <c r="X2" s="0" t="inlineStr">
         <is>
-          <t>INS-10A</t>
+          <t>COM-06B</t>
         </is>
       </c>
       <c r="Y2" s="0" t="inlineStr">
         <is>
-          <t>INS-11B</t>
-        </is>
-      </c>
-      <c r="Z2" s="0" t="inlineStr">
-        <is>
-          <t>INV-01B</t>
-        </is>
-      </c>
-      <c r="AA2" s="0" t="inlineStr">
-        <is>
           <t>INV-02B</t>
         </is>
       </c>
+      <c r="Z2" s="0" t="inlineStr"/>
+      <c r="AA2" s="0" t="inlineStr"/>
       <c r="AB2" s="0" t="inlineStr"/>
       <c r="AC2" s="0" t="inlineStr"/>
       <c r="AD2" s="0" t="inlineStr"/>
       <c r="AE2" s="0" t="inlineStr"/>
       <c r="AF2" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(N2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(O2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(P2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Q2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(R2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(S2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(T2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(U2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(V2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(W2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(X2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Y2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Z2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(AA2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
+        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(N2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(O2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(P2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Q2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(R2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(S2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(T2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(U2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(V2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(W2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(X2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Y2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
       <c r="AG2" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(N2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(O2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(P2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Q2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(R2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(S2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(T2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(U2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(V2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(W2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(X2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Y2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Z2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(AA2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
+        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(N2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(O2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(P2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Q2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(R2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(S2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(T2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(U2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(V2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(W2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(X2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Y2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
       <c r="AH2" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(N2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(O2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(P2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Q2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(R2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(S2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(T2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(U2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(V2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(W2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(X2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Y2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Z2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(AA2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
+        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(N2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(O2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(P2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Q2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(R2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(S2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(T2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(U2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(V2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(W2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(X2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Y2,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
       <c r="AI2" s="0">
@@ -6093,7 +6091,7 @@
         <v/>
       </c>
       <c r="DU2" s="0">
-        <f>(DB2*25+DD2*45+DF2*80+DI2*4+DK2*9+DN2*2+DP2*4+DR2*7)*0.8924</f>
+        <f>(DB2*25+DD2*45+DF2*80+DI2*4+DK2*9+DN2*2+DP2*4+DR2*7)*0.92</f>
         <v/>
       </c>
       <c r="DV2" s="0">
@@ -6167,246 +6165,249 @@
         <v/>
       </c>
       <c r="EN2" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)*EI2</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="EO2" s="0">
-        <f>(IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("COM-01C",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("INV-01B",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("INV-02B",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0))*1</f>
+        <f>(IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("COM-01C",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("INV-01B",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0))*1</f>
         <v/>
       </c>
       <c r="EP2" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="EQ2" s="0">
-        <f>DT2+DU2+DV2+DW2+L2+EL2+EM2+EN2+EO2+EP2</f>
-        <v/>
+      <c r="EQ2" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="ER2" s="0">
-        <f>EJ2-EQ2</f>
+        <f>DT2+DU2+DV2+DW2+L2+EL2+EM2+EN2+EO2+EP2+EQ2</f>
         <v/>
       </c>
       <c r="ES2" s="0">
+        <f>EJ2-ER2</f>
+        <v/>
+      </c>
+      <c r="ET2" s="0">
         <f>OR(AND('Lotes_Pipeline_sim1'!C2="SEG-03",'Lotes_Pipeline_sim1'!H2&gt;0,'Lotes_Pipeline_sim1'!J2&lt;4),AND('Lotes_Pipeline_sim1'!C3="SEG-03",'Lotes_Pipeline_sim1'!H3&gt;0,'Lotes_Pipeline_sim1'!J3&lt;4),AND('Lotes_Pipeline_sim1'!C4="SEG-03",'Lotes_Pipeline_sim1'!H4&gt;0,'Lotes_Pipeline_sim1'!J4&lt;4))</f>
         <v/>
       </c>
-      <c r="ET2" s="0">
+      <c r="EU2" s="0">
         <f>OR(AND('Lotes_Pipeline_sim1'!C2="SEG-03",'Lotes_Pipeline_sim1'!H2&gt;0,'Lotes_Pipeline_sim1'!J2&gt;=7),AND('Lotes_Pipeline_sim1'!C3="SEG-03",'Lotes_Pipeline_sim1'!H3&gt;0,'Lotes_Pipeline_sim1'!J3&gt;=7),AND('Lotes_Pipeline_sim1'!C4="SEG-03",'Lotes_Pipeline_sim1'!H4&gt;0,'Lotes_Pipeline_sim1'!J4&gt;=7))</f>
         <v/>
       </c>
-      <c r="EU2" s="0">
+      <c r="EV2" s="0">
         <f>AF2&lt;4</f>
         <v/>
       </c>
-      <c r="EV2" s="0">
+      <c r="EW2" s="0">
         <f>AM2&gt;=2</f>
         <v/>
       </c>
-      <c r="EW2" s="0">
+      <c r="EX2" s="0">
         <f>AH2&lt;3</f>
         <v/>
       </c>
-      <c r="EX2" s="0">
+      <c r="EY2" s="0">
         <f>I2&gt;CE2</f>
         <v/>
       </c>
-      <c r="EY2" s="0">
+      <c r="EZ2" s="0">
         <f>CZ2&gt;EI2</f>
         <v/>
       </c>
-      <c r="EZ2" s="0">
+      <c r="FA2" s="0">
         <f>AND(K2=0,AF2&lt;5)</f>
         <v/>
       </c>
-      <c r="FA2" s="0" t="n">
+      <c r="FB2" t="n">
         <v>1000000</v>
       </c>
-      <c r="FB2" s="0">
+      <c r="FC2">
         <f>1*2500*(1+0.03+0.02)+1*3500*(1+0.03+0.02)+1*1200*(1+0.03+0.02)+1*300*(1+0+0.01)</f>
         <v/>
       </c>
-      <c r="FC2" s="0">
+      <c r="FD2">
         <f>1*2500+1*3500+1*1200+1*300</f>
         <v/>
       </c>
-      <c r="FD2" s="0">
-        <f>(CF2*25+CH2*45+CJ2*80+CL2*4+CN2*9+CP2*2+CR2*4+CT2*7)*0.8924</f>
-        <v/>
-      </c>
-      <c r="FE2" s="0">
-        <f>(DC2*25+DE2*45+DG2*80+DJ2*4+DL2*9+DO2*2+DQ2*4+DS2*7)*0.8924</f>
-        <v/>
-      </c>
-      <c r="FF2" s="0">
-        <f>FA2</f>
-        <v/>
-      </c>
-      <c r="FG2" s="0">
+      <c r="FE2">
+        <f>(CF2*25+CH2*45+CJ2*80+CL2*4+CN2*9+CP2*2+CR2*4+CT2*7)*0.92</f>
+        <v/>
+      </c>
+      <c r="FF2">
+        <f>(DC2*25+DE2*45+DG2*80+DJ2*4+DL2*9+DO2*2+DQ2*4+DS2*7)*0.92</f>
+        <v/>
+      </c>
+      <c r="FG2">
+        <f>FB2</f>
+        <v/>
+      </c>
+      <c r="FH2">
         <f>(1+AR2/100)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="FH2" s="0">
-        <f>0*0+AP2*FG2</f>
-        <v/>
-      </c>
-      <c r="FI2" s="0">
-        <f>IFERROR(FH2/(0+AP2),0)</f>
-        <v/>
-      </c>
-      <c r="FJ2" s="0">
-        <f>FH2*1</f>
-        <v/>
-      </c>
-      <c r="FK2" s="0">
-        <f>EQ2-DW2-DU2+FD2+FJ2</f>
-        <v/>
-      </c>
-      <c r="FL2" s="0">
-        <f>FF2+EJ2+AP2-FK2-FB2</f>
-        <v/>
-      </c>
-      <c r="FM2" s="0">
+      <c r="FI2">
+        <f>0*0+AP2*FH2</f>
+        <v/>
+      </c>
+      <c r="FJ2">
+        <f>IFERROR(FI2/(0+AP2),0)</f>
+        <v/>
+      </c>
+      <c r="FK2">
+        <f>FI2*1</f>
+        <v/>
+      </c>
+      <c r="FL2">
+        <f>ER2-DW2-DU2+FE2+FK2</f>
+        <v/>
+      </c>
+      <c r="FM2">
+        <f>FG2+EJ2+AP2-FL2-FC2</f>
+        <v/>
+      </c>
+      <c r="FN2">
         <f>0+DW2</f>
         <v/>
       </c>
-      <c r="FN2" s="0">
-        <f>0+FC2</f>
-        <v/>
-      </c>
-      <c r="FO2" s="0">
-        <f>FN2-FM2</f>
-        <v/>
-      </c>
-      <c r="FP2" s="0">
+      <c r="FO2">
+        <f>0+FD2</f>
+        <v/>
+      </c>
+      <c r="FP2">
+        <f>FO2-FN2</f>
+        <v/>
+      </c>
+      <c r="FQ2">
         <f>EJ2</f>
         <v/>
       </c>
-      <c r="FQ2" s="0">
+      <c r="FR2">
         <f>EJ2</f>
         <v/>
       </c>
-      <c r="FR2" s="0">
-        <f>EQ2+FJ2</f>
-        <v/>
-      </c>
-      <c r="FS2" s="0">
-        <f>ER2-FJ2</f>
-        <v/>
-      </c>
-      <c r="FT2" s="0">
+      <c r="FS2">
+        <f>ER2+FK2</f>
+        <v/>
+      </c>
+      <c r="FT2">
+        <f>ES2-FK2</f>
+        <v/>
+      </c>
+      <c r="FU2">
         <f>DW2</f>
         <v/>
       </c>
-      <c r="FU2" s="0">
+      <c r="FV2">
+        <f>FK2</f>
+        <v/>
+      </c>
+      <c r="FW2">
+        <f>ER2</f>
+        <v/>
+      </c>
+      <c r="FX2">
+        <f>FG2</f>
+        <v/>
+      </c>
+      <c r="FY2">
+        <f>EJ2+AP2</f>
+        <v/>
+      </c>
+      <c r="FZ2">
+        <f>FL2+FC2</f>
+        <v/>
+      </c>
+      <c r="GA2">
+        <f>FM2</f>
+        <v/>
+      </c>
+      <c r="GB2">
+        <f>FG2</f>
+        <v/>
+      </c>
+      <c r="GC2">
+        <f>EJ2</f>
+        <v/>
+      </c>
+      <c r="GD2">
+        <f>FL2</f>
+        <v/>
+      </c>
+      <c r="GE2">
+        <f>FC2</f>
+        <v/>
+      </c>
+      <c r="GF2">
+        <f>AP2</f>
+        <v/>
+      </c>
+      <c r="GG2">
+        <f>EJ2-FL2</f>
+        <v/>
+      </c>
+      <c r="GH2">
+        <f>-FC2</f>
+        <v/>
+      </c>
+      <c r="GI2">
+        <f>FM2-FG2</f>
+        <v/>
+      </c>
+      <c r="GJ2">
+        <f>FM2</f>
+        <v/>
+      </c>
+      <c r="GK2">
+        <f>FM2</f>
+        <v/>
+      </c>
+      <c r="GL2">
+        <f>FP2</f>
+        <v/>
+      </c>
+      <c r="GM2">
+        <f>FF2</f>
+        <v/>
+      </c>
+      <c r="GN2">
+        <f>FM2+FP2+FF2</f>
+        <v/>
+      </c>
+      <c r="GO2">
+        <f>AS2</f>
+        <v/>
+      </c>
+      <c r="GP2">
+        <f>FM2+FP2+FF2-AS2</f>
+        <v/>
+      </c>
+      <c r="GQ2">
+        <f>FM2+FP2+FF2</f>
+        <v/>
+      </c>
+      <c r="GR2">
+        <f>AP2</f>
+        <v/>
+      </c>
+      <c r="GS2">
+        <f>AR2</f>
+        <v/>
+      </c>
+      <c r="GT2">
+        <f>AS2</f>
+        <v/>
+      </c>
+      <c r="GU2">
+        <f>AT2</f>
+        <v/>
+      </c>
+      <c r="GV2">
         <f>FJ2</f>
         <v/>
       </c>
-      <c r="FV2" s="0">
-        <f>EQ2</f>
-        <v/>
-      </c>
-      <c r="FW2" s="0">
-        <f>FF2</f>
-        <v/>
-      </c>
-      <c r="FX2" s="0">
-        <f>EJ2+AP2</f>
-        <v/>
-      </c>
-      <c r="FY2" s="0">
-        <f>FK2+FB2</f>
-        <v/>
-      </c>
-      <c r="FZ2" s="0">
-        <f>FL2</f>
-        <v/>
-      </c>
-      <c r="GA2" s="0">
-        <f>FF2</f>
-        <v/>
-      </c>
-      <c r="GB2" s="0">
-        <f>EJ2</f>
-        <v/>
-      </c>
-      <c r="GC2" s="0">
+      <c r="GW2">
         <f>FK2</f>
-        <v/>
-      </c>
-      <c r="GD2" s="0">
-        <f>FB2</f>
-        <v/>
-      </c>
-      <c r="GE2" s="0">
-        <f>AP2</f>
-        <v/>
-      </c>
-      <c r="GF2" s="0">
-        <f>EJ2-FK2</f>
-        <v/>
-      </c>
-      <c r="GG2" s="0">
-        <f>-FB2</f>
-        <v/>
-      </c>
-      <c r="GH2" s="0">
-        <f>FL2-FF2</f>
-        <v/>
-      </c>
-      <c r="GI2" s="0">
-        <f>FL2</f>
-        <v/>
-      </c>
-      <c r="GJ2" s="0">
-        <f>FL2</f>
-        <v/>
-      </c>
-      <c r="GK2" s="0">
-        <f>FO2</f>
-        <v/>
-      </c>
-      <c r="GL2" s="0">
-        <f>FE2</f>
-        <v/>
-      </c>
-      <c r="GM2" s="0">
-        <f>FL2+FO2+FE2</f>
-        <v/>
-      </c>
-      <c r="GN2" s="0">
-        <f>AS2</f>
-        <v/>
-      </c>
-      <c r="GO2" s="0">
-        <f>FL2+FO2+FE2-AS2</f>
-        <v/>
-      </c>
-      <c r="GP2" s="0">
-        <f>FL2+FO2+FE2</f>
-        <v/>
-      </c>
-      <c r="GQ2" s="0">
-        <f>AP2</f>
-        <v/>
-      </c>
-      <c r="GR2" s="0">
-        <f>AR2</f>
-        <v/>
-      </c>
-      <c r="GS2" s="0">
-        <f>AS2</f>
-        <v/>
-      </c>
-      <c r="GT2" s="0">
-        <f>AT2</f>
-        <v/>
-      </c>
-      <c r="GU2" s="0">
-        <f>FI2</f>
-        <v/>
-      </c>
-      <c r="GV2" s="0">
-        <f>FJ2</f>
         <v/>
       </c>
     </row>
@@ -6459,7 +6460,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="0" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="M3" s="0" t="inlineStr">
         <is>
@@ -6513,43 +6514,35 @@
       </c>
       <c r="W3" s="0" t="inlineStr">
         <is>
-          <t>INS-09B</t>
+          <t>INV-01B</t>
         </is>
       </c>
       <c r="X3" s="0" t="inlineStr">
         <is>
-          <t>INS-10A</t>
+          <t>COM-06B</t>
         </is>
       </c>
       <c r="Y3" s="0" t="inlineStr">
         <is>
-          <t>INS-11B</t>
-        </is>
-      </c>
-      <c r="Z3" s="0" t="inlineStr">
-        <is>
-          <t>INV-01B</t>
-        </is>
-      </c>
-      <c r="AA3" s="0" t="inlineStr">
-        <is>
           <t>INV-02B</t>
         </is>
       </c>
+      <c r="Z3" s="0" t="inlineStr"/>
+      <c r="AA3" s="0" t="inlineStr"/>
       <c r="AB3" s="0" t="inlineStr"/>
       <c r="AC3" s="0" t="inlineStr"/>
       <c r="AD3" s="0" t="inlineStr"/>
       <c r="AE3" s="0" t="inlineStr"/>
       <c r="AF3" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(N3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(O3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(P3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Q3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(R3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(S3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(T3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(U3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(V3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(W3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(X3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Y3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Z3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(AA3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
+        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(N3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(O3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(P3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Q3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(R3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(S3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(T3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(U3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(V3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(W3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(X3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Y3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
       <c r="AG3" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(N3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(O3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(P3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Q3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(R3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(S3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(T3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(U3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(V3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(W3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(X3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Y3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Z3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(AA3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
+        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(N3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(O3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(P3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Q3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(R3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(S3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(T3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(U3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(V3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(W3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(X3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Y3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
       <c r="AH3" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(N3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(O3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(P3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Q3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(R3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(S3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(T3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(U3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(V3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(W3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(X3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Y3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Z3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(AA3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
+        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(N3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(O3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(P3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Q3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(R3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(S3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(T3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(U3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(V3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(W3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(X3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Y3,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
       <c r="AI3" s="0">
@@ -6876,7 +6869,7 @@
         <v/>
       </c>
       <c r="DU3" s="0">
-        <f>(DB3*25+DD3*45+DF3*80+DI3*4+DK3*9+DN3*2+DP3*4+DR3*7)*0.8924</f>
+        <f>(DB3*25+DD3*45+DF3*80+DI3*4+DK3*9+DN3*2+DP3*4+DR3*7)*0.92</f>
         <v/>
       </c>
       <c r="DV3" s="0">
@@ -6950,246 +6943,249 @@
         <v/>
       </c>
       <c r="EN3" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)*EI3</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="EO3" s="0">
-        <f>(IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("COM-01C",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("INV-01B",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("INV-02B",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0))*1</f>
+        <f>(IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("COM-01C",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("INV-01B",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0))*1</f>
         <v/>
       </c>
       <c r="EP3" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="EQ3" s="0">
-        <f>DT3+DU3+DV3+DW3+L3+EL3+EM3+EN3+EO3+EP3</f>
-        <v/>
+      <c r="EQ3" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="ER3" s="0">
-        <f>EJ3-EQ3</f>
+        <f>DT3+DU3+DV3+DW3+L3+EL3+EM3+EN3+EO3+EP3+EQ3</f>
         <v/>
       </c>
       <c r="ES3" s="0">
+        <f>EJ3-ER3</f>
+        <v/>
+      </c>
+      <c r="ET3" s="0">
         <f>OR(AND('Lotes_Pipeline_sim1'!C5="SEG-03",'Lotes_Pipeline_sim1'!H5&gt;0,'Lotes_Pipeline_sim1'!J5&lt;4),AND('Lotes_Pipeline_sim1'!C6="SEG-03",'Lotes_Pipeline_sim1'!H6&gt;0,'Lotes_Pipeline_sim1'!J6&lt;4),AND('Lotes_Pipeline_sim1'!C7="SEG-03",'Lotes_Pipeline_sim1'!H7&gt;0,'Lotes_Pipeline_sim1'!J7&lt;4))</f>
         <v/>
       </c>
-      <c r="ET3" s="0">
+      <c r="EU3" s="0">
         <f>OR(AND('Lotes_Pipeline_sim1'!C5="SEG-03",'Lotes_Pipeline_sim1'!H5&gt;0,'Lotes_Pipeline_sim1'!J5&gt;=7),AND('Lotes_Pipeline_sim1'!C6="SEG-03",'Lotes_Pipeline_sim1'!H6&gt;0,'Lotes_Pipeline_sim1'!J6&gt;=7),AND('Lotes_Pipeline_sim1'!C7="SEG-03",'Lotes_Pipeline_sim1'!H7&gt;0,'Lotes_Pipeline_sim1'!J7&gt;=7))</f>
         <v/>
       </c>
-      <c r="EU3" s="0">
+      <c r="EV3" s="0">
         <f>AF3&lt;4</f>
         <v/>
       </c>
-      <c r="EV3" s="0">
+      <c r="EW3" s="0">
         <f>AM3&gt;=2</f>
         <v/>
       </c>
-      <c r="EW3" s="0">
+      <c r="EX3" s="0">
         <f>AH3&lt;3</f>
         <v/>
       </c>
-      <c r="EX3" s="0">
+      <c r="EY3" s="0">
         <f>I3&gt;CE3</f>
         <v/>
       </c>
-      <c r="EY3" s="0">
+      <c r="EZ3" s="0">
         <f>CZ3&gt;EI3</f>
         <v/>
       </c>
-      <c r="EZ3" s="0">
+      <c r="FA3" s="0">
         <f>AND(K3=0,AF3&lt;5)</f>
         <v/>
       </c>
-      <c r="FA3" s="0" t="n">
+      <c r="FB3" t="n">
         <v>1000000</v>
       </c>
-      <c r="FB3" s="0">
+      <c r="FC3">
         <f>1*2500*(1+0.03+0.02)+1*3500*(1+0.03+0.02)+1*1200*(1+0.03+0.02)+1*300*(1+0+0.01)</f>
         <v/>
       </c>
-      <c r="FC3" s="0">
+      <c r="FD3">
         <f>1*2500+1*3500+1*1200+1*300</f>
         <v/>
       </c>
-      <c r="FD3" s="0">
-        <f>(CF3*25+CH3*45+CJ3*80+CL3*4+CN3*9+CP3*2+CR3*4+CT3*7)*0.8924</f>
-        <v/>
-      </c>
-      <c r="FE3" s="0">
-        <f>(DC3*25+DE3*45+DG3*80+DJ3*4+DL3*9+DO3*2+DQ3*4+DS3*7)*0.8924</f>
-        <v/>
-      </c>
-      <c r="FF3" s="0">
-        <f>FA3</f>
-        <v/>
-      </c>
-      <c r="FG3" s="0">
+      <c r="FE3">
+        <f>(CF3*25+CH3*45+CJ3*80+CL3*4+CN3*9+CP3*2+CR3*4+CT3*7)*0.92</f>
+        <v/>
+      </c>
+      <c r="FF3">
+        <f>(DC3*25+DE3*45+DG3*80+DJ3*4+DL3*9+DO3*2+DQ3*4+DS3*7)*0.92</f>
+        <v/>
+      </c>
+      <c r="FG3">
+        <f>FB3</f>
+        <v/>
+      </c>
+      <c r="FH3">
         <f>(1+AR3/100)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="FH3" s="0">
-        <f>0*0+AP3*FG3</f>
-        <v/>
-      </c>
-      <c r="FI3" s="0">
-        <f>IFERROR(FH3/(0+AP3),0)</f>
-        <v/>
-      </c>
-      <c r="FJ3" s="0">
-        <f>FH3*1</f>
-        <v/>
-      </c>
-      <c r="FK3" s="0">
-        <f>EQ3-DW3-DU3+FD3+FJ3</f>
-        <v/>
-      </c>
-      <c r="FL3" s="0">
-        <f>FF3+EJ3+AP3-FK3-FB3</f>
-        <v/>
-      </c>
-      <c r="FM3" s="0">
+      <c r="FI3">
+        <f>0*0+AP3*FH3</f>
+        <v/>
+      </c>
+      <c r="FJ3">
+        <f>IFERROR(FI3/(0+AP3),0)</f>
+        <v/>
+      </c>
+      <c r="FK3">
+        <f>FI3*1</f>
+        <v/>
+      </c>
+      <c r="FL3">
+        <f>ER3-DW3-DU3+FE3+FK3</f>
+        <v/>
+      </c>
+      <c r="FM3">
+        <f>FG3+EJ3+AP3-FL3-FC3</f>
+        <v/>
+      </c>
+      <c r="FN3">
         <f>0+DW3</f>
         <v/>
       </c>
-      <c r="FN3" s="0">
-        <f>0+FC3</f>
-        <v/>
-      </c>
-      <c r="FO3" s="0">
-        <f>FN3-FM3</f>
-        <v/>
-      </c>
-      <c r="FP3" s="0">
+      <c r="FO3">
+        <f>0+FD3</f>
+        <v/>
+      </c>
+      <c r="FP3">
+        <f>FO3-FN3</f>
+        <v/>
+      </c>
+      <c r="FQ3">
         <f>EJ3</f>
         <v/>
       </c>
-      <c r="FQ3" s="0">
+      <c r="FR3">
         <f>EJ3</f>
         <v/>
       </c>
-      <c r="FR3" s="0">
-        <f>EQ3+FJ3</f>
-        <v/>
-      </c>
-      <c r="FS3" s="0">
-        <f>ER3-FJ3</f>
-        <v/>
-      </c>
-      <c r="FT3" s="0">
+      <c r="FS3">
+        <f>ER3+FK3</f>
+        <v/>
+      </c>
+      <c r="FT3">
+        <f>ES3-FK3</f>
+        <v/>
+      </c>
+      <c r="FU3">
         <f>DW3</f>
         <v/>
       </c>
-      <c r="FU3" s="0">
+      <c r="FV3">
+        <f>FK3</f>
+        <v/>
+      </c>
+      <c r="FW3">
+        <f>ER3</f>
+        <v/>
+      </c>
+      <c r="FX3">
+        <f>FG3</f>
+        <v/>
+      </c>
+      <c r="FY3">
+        <f>EJ3+AP3</f>
+        <v/>
+      </c>
+      <c r="FZ3">
+        <f>FL3+FC3</f>
+        <v/>
+      </c>
+      <c r="GA3">
+        <f>FM3</f>
+        <v/>
+      </c>
+      <c r="GB3">
+        <f>FG3</f>
+        <v/>
+      </c>
+      <c r="GC3">
+        <f>EJ3</f>
+        <v/>
+      </c>
+      <c r="GD3">
+        <f>FL3</f>
+        <v/>
+      </c>
+      <c r="GE3">
+        <f>FC3</f>
+        <v/>
+      </c>
+      <c r="GF3">
+        <f>AP3</f>
+        <v/>
+      </c>
+      <c r="GG3">
+        <f>EJ3-FL3</f>
+        <v/>
+      </c>
+      <c r="GH3">
+        <f>-FC3</f>
+        <v/>
+      </c>
+      <c r="GI3">
+        <f>FM3-FG3</f>
+        <v/>
+      </c>
+      <c r="GJ3">
+        <f>FM3</f>
+        <v/>
+      </c>
+      <c r="GK3">
+        <f>FM3</f>
+        <v/>
+      </c>
+      <c r="GL3">
+        <f>FP3</f>
+        <v/>
+      </c>
+      <c r="GM3">
+        <f>FF3</f>
+        <v/>
+      </c>
+      <c r="GN3">
+        <f>FM3+FP3+FF3</f>
+        <v/>
+      </c>
+      <c r="GO3">
+        <f>AS3</f>
+        <v/>
+      </c>
+      <c r="GP3">
+        <f>FM3+FP3+FF3-AS3</f>
+        <v/>
+      </c>
+      <c r="GQ3">
+        <f>FM3+FP3+FF3</f>
+        <v/>
+      </c>
+      <c r="GR3">
+        <f>AP3</f>
+        <v/>
+      </c>
+      <c r="GS3">
+        <f>AR3</f>
+        <v/>
+      </c>
+      <c r="GT3">
+        <f>AS3</f>
+        <v/>
+      </c>
+      <c r="GU3">
+        <f>AT3</f>
+        <v/>
+      </c>
+      <c r="GV3">
         <f>FJ3</f>
         <v/>
       </c>
-      <c r="FV3" s="0">
-        <f>EQ3</f>
-        <v/>
-      </c>
-      <c r="FW3" s="0">
-        <f>FF3</f>
-        <v/>
-      </c>
-      <c r="FX3" s="0">
-        <f>EJ3+AP3</f>
-        <v/>
-      </c>
-      <c r="FY3" s="0">
-        <f>FK3+FB3</f>
-        <v/>
-      </c>
-      <c r="FZ3" s="0">
-        <f>FL3</f>
-        <v/>
-      </c>
-      <c r="GA3" s="0">
-        <f>FF3</f>
-        <v/>
-      </c>
-      <c r="GB3" s="0">
-        <f>EJ3</f>
-        <v/>
-      </c>
-      <c r="GC3" s="0">
+      <c r="GW3">
         <f>FK3</f>
-        <v/>
-      </c>
-      <c r="GD3" s="0">
-        <f>FB3</f>
-        <v/>
-      </c>
-      <c r="GE3" s="0">
-        <f>AP3</f>
-        <v/>
-      </c>
-      <c r="GF3" s="0">
-        <f>EJ3-FK3</f>
-        <v/>
-      </c>
-      <c r="GG3" s="0">
-        <f>-FB3</f>
-        <v/>
-      </c>
-      <c r="GH3" s="0">
-        <f>FL3-FF3</f>
-        <v/>
-      </c>
-      <c r="GI3" s="0">
-        <f>FL3</f>
-        <v/>
-      </c>
-      <c r="GJ3" s="0">
-        <f>FL3</f>
-        <v/>
-      </c>
-      <c r="GK3" s="0">
-        <f>FO3</f>
-        <v/>
-      </c>
-      <c r="GL3" s="0">
-        <f>FE3</f>
-        <v/>
-      </c>
-      <c r="GM3" s="0">
-        <f>FL3+FO3+FE3</f>
-        <v/>
-      </c>
-      <c r="GN3" s="0">
-        <f>AS3</f>
-        <v/>
-      </c>
-      <c r="GO3" s="0">
-        <f>FL3+FO3+FE3-AS3</f>
-        <v/>
-      </c>
-      <c r="GP3" s="0">
-        <f>FL3+FO3+FE3</f>
-        <v/>
-      </c>
-      <c r="GQ3" s="0">
-        <f>AP3</f>
-        <v/>
-      </c>
-      <c r="GR3" s="0">
-        <f>AR3</f>
-        <v/>
-      </c>
-      <c r="GS3" s="0">
-        <f>AS3</f>
-        <v/>
-      </c>
-      <c r="GT3" s="0">
-        <f>AT3</f>
-        <v/>
-      </c>
-      <c r="GU3" s="0">
-        <f>FI3</f>
-        <v/>
-      </c>
-      <c r="GV3" s="0">
-        <f>FJ3</f>
         <v/>
       </c>
     </row>
@@ -7242,7 +7238,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="0" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="M4" s="0" t="inlineStr">
         <is>
@@ -7296,43 +7292,35 @@
       </c>
       <c r="W4" s="0" t="inlineStr">
         <is>
-          <t>INS-09B</t>
+          <t>INV-01B</t>
         </is>
       </c>
       <c r="X4" s="0" t="inlineStr">
         <is>
-          <t>INS-10A</t>
+          <t>COM-06B</t>
         </is>
       </c>
       <c r="Y4" s="0" t="inlineStr">
         <is>
-          <t>INS-11B</t>
-        </is>
-      </c>
-      <c r="Z4" s="0" t="inlineStr">
-        <is>
-          <t>INV-01B</t>
-        </is>
-      </c>
-      <c r="AA4" s="0" t="inlineStr">
-        <is>
           <t>INV-02B</t>
         </is>
       </c>
+      <c r="Z4" s="0" t="inlineStr"/>
+      <c r="AA4" s="0" t="inlineStr"/>
       <c r="AB4" s="0" t="inlineStr"/>
       <c r="AC4" s="0" t="inlineStr"/>
       <c r="AD4" s="0" t="inlineStr"/>
       <c r="AE4" s="0" t="inlineStr"/>
       <c r="AF4" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(N4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(O4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(P4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Q4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(R4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(S4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(T4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(U4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(V4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(W4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(X4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Y4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Z4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(AA4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
+        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(N4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(O4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(P4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Q4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(R4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(S4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(T4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(U4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(V4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(W4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(X4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Y4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
       <c r="AG4" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(N4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(O4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(P4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Q4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(R4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(S4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(T4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(U4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(V4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(W4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(X4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Y4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Z4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(AA4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
+        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(N4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(O4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(P4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Q4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(R4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(S4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(T4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(U4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(V4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(W4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(X4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Y4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
       <c r="AH4" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(N4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(O4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(P4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Q4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(R4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(S4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(T4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(U4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(V4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(W4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(X4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Y4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Z4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(AA4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
+        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(N4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(O4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(P4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Q4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(R4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(S4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(T4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(U4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(V4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(W4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(X4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Y4,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
       <c r="AI4" s="0">
@@ -7659,7 +7647,7 @@
         <v/>
       </c>
       <c r="DU4" s="0">
-        <f>(DB4*25+DD4*45+DF4*80+DI4*4+DK4*9+DN4*2+DP4*4+DR4*7)*0.8924</f>
+        <f>(DB4*25+DD4*45+DF4*80+DI4*4+DK4*9+DN4*2+DP4*4+DR4*7)*0.92</f>
         <v/>
       </c>
       <c r="DV4" s="0">
@@ -7733,246 +7721,249 @@
         <v/>
       </c>
       <c r="EN4" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)*EI4</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="EO4" s="0">
-        <f>(IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("COM-01C",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("INV-01B",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("INV-02B",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0))*1</f>
+        <f>(IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("COM-01C",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("INV-01B",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0))*1</f>
         <v/>
       </c>
       <c r="EP4" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="EQ4" s="0">
-        <f>DT4+DU4+DV4+DW4+L4+EL4+EM4+EN4+EO4+EP4</f>
-        <v/>
+      <c r="EQ4" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="ER4" s="0">
-        <f>EJ4-EQ4</f>
+        <f>DT4+DU4+DV4+DW4+L4+EL4+EM4+EN4+EO4+EP4+EQ4</f>
         <v/>
       </c>
       <c r="ES4" s="0">
+        <f>EJ4-ER4</f>
+        <v/>
+      </c>
+      <c r="ET4" s="0">
         <f>OR(AND('Lotes_Pipeline_sim1'!C8="SEG-03",'Lotes_Pipeline_sim1'!H8&gt;0,'Lotes_Pipeline_sim1'!J8&lt;4),AND('Lotes_Pipeline_sim1'!C9="SEG-03",'Lotes_Pipeline_sim1'!H9&gt;0,'Lotes_Pipeline_sim1'!J9&lt;4),AND('Lotes_Pipeline_sim1'!C10="SEG-03",'Lotes_Pipeline_sim1'!H10&gt;0,'Lotes_Pipeline_sim1'!J10&lt;4))</f>
         <v/>
       </c>
-      <c r="ET4" s="0">
+      <c r="EU4" s="0">
         <f>OR(AND('Lotes_Pipeline_sim1'!C8="SEG-03",'Lotes_Pipeline_sim1'!H8&gt;0,'Lotes_Pipeline_sim1'!J8&gt;=7),AND('Lotes_Pipeline_sim1'!C9="SEG-03",'Lotes_Pipeline_sim1'!H9&gt;0,'Lotes_Pipeline_sim1'!J9&gt;=7),AND('Lotes_Pipeline_sim1'!C10="SEG-03",'Lotes_Pipeline_sim1'!H10&gt;0,'Lotes_Pipeline_sim1'!J10&gt;=7))</f>
         <v/>
       </c>
-      <c r="EU4" s="0">
+      <c r="EV4" s="0">
         <f>AF4&lt;4</f>
         <v/>
       </c>
-      <c r="EV4" s="0">
+      <c r="EW4" s="0">
         <f>AM4&gt;=2</f>
         <v/>
       </c>
-      <c r="EW4" s="0">
+      <c r="EX4" s="0">
         <f>AH4&lt;3</f>
         <v/>
       </c>
-      <c r="EX4" s="0">
+      <c r="EY4" s="0">
         <f>I4&gt;CE4</f>
         <v/>
       </c>
-      <c r="EY4" s="0">
+      <c r="EZ4" s="0">
         <f>CZ4&gt;EI4</f>
         <v/>
       </c>
-      <c r="EZ4" s="0">
+      <c r="FA4" s="0">
         <f>AND(K4=0,AF4&lt;5)</f>
         <v/>
       </c>
-      <c r="FA4" s="0" t="n">
+      <c r="FB4" t="n">
         <v>1000000</v>
       </c>
-      <c r="FB4" s="0">
+      <c r="FC4">
         <f>1*2500*(1+0.03+0.02)+1*3500*(1+0.03+0.02)+1*1200*(1+0.03+0.02)+1*300*(1+0+0.01)</f>
         <v/>
       </c>
-      <c r="FC4" s="0">
+      <c r="FD4">
         <f>1*2500+1*3500+1*1200+1*300</f>
         <v/>
       </c>
-      <c r="FD4" s="0">
-        <f>(CF4*25+CH4*45+CJ4*80+CL4*4+CN4*9+CP4*2+CR4*4+CT4*7)*0.8924</f>
-        <v/>
-      </c>
-      <c r="FE4" s="0">
-        <f>(DC4*25+DE4*45+DG4*80+DJ4*4+DL4*9+DO4*2+DQ4*4+DS4*7)*0.8924</f>
-        <v/>
-      </c>
-      <c r="FF4" s="0">
-        <f>FA4</f>
-        <v/>
-      </c>
-      <c r="FG4" s="0">
+      <c r="FE4">
+        <f>(CF4*25+CH4*45+CJ4*80+CL4*4+CN4*9+CP4*2+CR4*4+CT4*7)*0.92</f>
+        <v/>
+      </c>
+      <c r="FF4">
+        <f>(DC4*25+DE4*45+DG4*80+DJ4*4+DL4*9+DO4*2+DQ4*4+DS4*7)*0.92</f>
+        <v/>
+      </c>
+      <c r="FG4">
+        <f>FB4</f>
+        <v/>
+      </c>
+      <c r="FH4">
         <f>(1+AR4/100)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="FH4" s="0">
-        <f>0*0+AP4*FG4</f>
-        <v/>
-      </c>
-      <c r="FI4" s="0">
-        <f>IFERROR(FH4/(0+AP4),0)</f>
-        <v/>
-      </c>
-      <c r="FJ4" s="0">
-        <f>FH4*1</f>
-        <v/>
-      </c>
-      <c r="FK4" s="0">
-        <f>EQ4-DW4-DU4+FD4+FJ4</f>
-        <v/>
-      </c>
-      <c r="FL4" s="0">
-        <f>FF4+EJ4+AP4-FK4-FB4</f>
-        <v/>
-      </c>
-      <c r="FM4" s="0">
+      <c r="FI4">
+        <f>0*0+AP4*FH4</f>
+        <v/>
+      </c>
+      <c r="FJ4">
+        <f>IFERROR(FI4/(0+AP4),0)</f>
+        <v/>
+      </c>
+      <c r="FK4">
+        <f>FI4*1</f>
+        <v/>
+      </c>
+      <c r="FL4">
+        <f>ER4-DW4-DU4+FE4+FK4</f>
+        <v/>
+      </c>
+      <c r="FM4">
+        <f>FG4+EJ4+AP4-FL4-FC4</f>
+        <v/>
+      </c>
+      <c r="FN4">
         <f>0+DW4</f>
         <v/>
       </c>
-      <c r="FN4" s="0">
-        <f>0+FC4</f>
-        <v/>
-      </c>
-      <c r="FO4" s="0">
-        <f>FN4-FM4</f>
-        <v/>
-      </c>
-      <c r="FP4" s="0">
+      <c r="FO4">
+        <f>0+FD4</f>
+        <v/>
+      </c>
+      <c r="FP4">
+        <f>FO4-FN4</f>
+        <v/>
+      </c>
+      <c r="FQ4">
         <f>EJ4</f>
         <v/>
       </c>
-      <c r="FQ4" s="0">
+      <c r="FR4">
         <f>EJ4</f>
         <v/>
       </c>
-      <c r="FR4" s="0">
-        <f>EQ4+FJ4</f>
-        <v/>
-      </c>
-      <c r="FS4" s="0">
-        <f>ER4-FJ4</f>
-        <v/>
-      </c>
-      <c r="FT4" s="0">
+      <c r="FS4">
+        <f>ER4+FK4</f>
+        <v/>
+      </c>
+      <c r="FT4">
+        <f>ES4-FK4</f>
+        <v/>
+      </c>
+      <c r="FU4">
         <f>DW4</f>
         <v/>
       </c>
-      <c r="FU4" s="0">
+      <c r="FV4">
+        <f>FK4</f>
+        <v/>
+      </c>
+      <c r="FW4">
+        <f>ER4</f>
+        <v/>
+      </c>
+      <c r="FX4">
+        <f>FG4</f>
+        <v/>
+      </c>
+      <c r="FY4">
+        <f>EJ4+AP4</f>
+        <v/>
+      </c>
+      <c r="FZ4">
+        <f>FL4+FC4</f>
+        <v/>
+      </c>
+      <c r="GA4">
+        <f>FM4</f>
+        <v/>
+      </c>
+      <c r="GB4">
+        <f>FG4</f>
+        <v/>
+      </c>
+      <c r="GC4">
+        <f>EJ4</f>
+        <v/>
+      </c>
+      <c r="GD4">
+        <f>FL4</f>
+        <v/>
+      </c>
+      <c r="GE4">
+        <f>FC4</f>
+        <v/>
+      </c>
+      <c r="GF4">
+        <f>AP4</f>
+        <v/>
+      </c>
+      <c r="GG4">
+        <f>EJ4-FL4</f>
+        <v/>
+      </c>
+      <c r="GH4">
+        <f>-FC4</f>
+        <v/>
+      </c>
+      <c r="GI4">
+        <f>FM4-FG4</f>
+        <v/>
+      </c>
+      <c r="GJ4">
+        <f>FM4</f>
+        <v/>
+      </c>
+      <c r="GK4">
+        <f>FM4</f>
+        <v/>
+      </c>
+      <c r="GL4">
+        <f>FP4</f>
+        <v/>
+      </c>
+      <c r="GM4">
+        <f>FF4</f>
+        <v/>
+      </c>
+      <c r="GN4">
+        <f>FM4+FP4+FF4</f>
+        <v/>
+      </c>
+      <c r="GO4">
+        <f>AS4</f>
+        <v/>
+      </c>
+      <c r="GP4">
+        <f>FM4+FP4+FF4-AS4</f>
+        <v/>
+      </c>
+      <c r="GQ4">
+        <f>FM4+FP4+FF4</f>
+        <v/>
+      </c>
+      <c r="GR4">
+        <f>AP4</f>
+        <v/>
+      </c>
+      <c r="GS4">
+        <f>AR4</f>
+        <v/>
+      </c>
+      <c r="GT4">
+        <f>AS4</f>
+        <v/>
+      </c>
+      <c r="GU4">
+        <f>AT4</f>
+        <v/>
+      </c>
+      <c r="GV4">
         <f>FJ4</f>
         <v/>
       </c>
-      <c r="FV4" s="0">
-        <f>EQ4</f>
-        <v/>
-      </c>
-      <c r="FW4" s="0">
-        <f>FF4</f>
-        <v/>
-      </c>
-      <c r="FX4" s="0">
-        <f>EJ4+AP4</f>
-        <v/>
-      </c>
-      <c r="FY4" s="0">
-        <f>FK4+FB4</f>
-        <v/>
-      </c>
-      <c r="FZ4" s="0">
-        <f>FL4</f>
-        <v/>
-      </c>
-      <c r="GA4" s="0">
-        <f>FF4</f>
-        <v/>
-      </c>
-      <c r="GB4" s="0">
-        <f>EJ4</f>
-        <v/>
-      </c>
-      <c r="GC4" s="0">
+      <c r="GW4">
         <f>FK4</f>
-        <v/>
-      </c>
-      <c r="GD4" s="0">
-        <f>FB4</f>
-        <v/>
-      </c>
-      <c r="GE4" s="0">
-        <f>AP4</f>
-        <v/>
-      </c>
-      <c r="GF4" s="0">
-        <f>EJ4-FK4</f>
-        <v/>
-      </c>
-      <c r="GG4" s="0">
-        <f>-FB4</f>
-        <v/>
-      </c>
-      <c r="GH4" s="0">
-        <f>FL4-FF4</f>
-        <v/>
-      </c>
-      <c r="GI4" s="0">
-        <f>FL4</f>
-        <v/>
-      </c>
-      <c r="GJ4" s="0">
-        <f>FL4</f>
-        <v/>
-      </c>
-      <c r="GK4" s="0">
-        <f>FO4</f>
-        <v/>
-      </c>
-      <c r="GL4" s="0">
-        <f>FE4</f>
-        <v/>
-      </c>
-      <c r="GM4" s="0">
-        <f>FL4+FO4+FE4</f>
-        <v/>
-      </c>
-      <c r="GN4" s="0">
-        <f>AS4</f>
-        <v/>
-      </c>
-      <c r="GO4" s="0">
-        <f>FL4+FO4+FE4-AS4</f>
-        <v/>
-      </c>
-      <c r="GP4" s="0">
-        <f>FL4+FO4+FE4</f>
-        <v/>
-      </c>
-      <c r="GQ4" s="0">
-        <f>AP4</f>
-        <v/>
-      </c>
-      <c r="GR4" s="0">
-        <f>AR4</f>
-        <v/>
-      </c>
-      <c r="GS4" s="0">
-        <f>AS4</f>
-        <v/>
-      </c>
-      <c r="GT4" s="0">
-        <f>AT4</f>
-        <v/>
-      </c>
-      <c r="GU4" s="0">
-        <f>FI4</f>
-        <v/>
-      </c>
-      <c r="GV4" s="0">
-        <f>FJ4</f>
         <v/>
       </c>
     </row>
@@ -8025,7 +8016,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="0" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="M5" s="0" t="inlineStr">
         <is>
@@ -8079,43 +8070,35 @@
       </c>
       <c r="W5" s="0" t="inlineStr">
         <is>
-          <t>INS-09B</t>
+          <t>INV-01B</t>
         </is>
       </c>
       <c r="X5" s="0" t="inlineStr">
         <is>
-          <t>INS-10A</t>
+          <t>COM-06B</t>
         </is>
       </c>
       <c r="Y5" s="0" t="inlineStr">
         <is>
-          <t>INS-11B</t>
-        </is>
-      </c>
-      <c r="Z5" s="0" t="inlineStr">
-        <is>
-          <t>INV-01B</t>
-        </is>
-      </c>
-      <c r="AA5" s="0" t="inlineStr">
-        <is>
           <t>INV-02B</t>
         </is>
       </c>
+      <c r="Z5" s="0" t="inlineStr"/>
+      <c r="AA5" s="0" t="inlineStr"/>
       <c r="AB5" s="0" t="inlineStr"/>
       <c r="AC5" s="0" t="inlineStr"/>
       <c r="AD5" s="0" t="inlineStr"/>
       <c r="AE5" s="0" t="inlineStr"/>
       <c r="AF5" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(N5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(O5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(P5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Q5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(R5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(S5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(T5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(U5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(V5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(W5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(X5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Y5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Z5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(AA5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
+        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(N5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(O5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(P5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Q5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(R5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(S5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(T5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(U5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(V5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(W5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(X5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$I$2:$I$69,MATCH(Y5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
       <c r="AG5" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(N5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(O5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(P5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Q5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(R5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(S5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(T5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(U5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(V5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(W5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(X5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Y5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Z5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(AA5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
+        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(N5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(O5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(P5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Q5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(R5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(S5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(T5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(U5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(V5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(W5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(X5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$J$2:$J$69,MATCH(Y5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
       <c r="AH5" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(N5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(O5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(P5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Q5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(R5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(S5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(T5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(U5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(V5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(W5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(X5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Y5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Z5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(AA5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
+        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(N5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(O5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(P5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Q5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(R5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(S5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(T5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(U5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(V5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(W5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(X5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$K$2:$K$69,MATCH(Y5,'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
       <c r="AI5" s="0">
@@ -8442,7 +8425,7 @@
         <v/>
       </c>
       <c r="DU5" s="0">
-        <f>(DB5*25+DD5*45+DF5*80+DI5*4+DK5*9+DN5*2+DP5*4+DR5*7)*0.8924</f>
+        <f>(DB5*25+DD5*45+DF5*80+DI5*4+DK5*9+DN5*2+DP5*4+DR5*7)*0.92</f>
         <v/>
       </c>
       <c r="DV5" s="0">
@@ -8516,246 +8499,249 @@
         <v/>
       </c>
       <c r="EN5" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)*EI5</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="EO5" s="0">
-        <f>(IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("COM-01C",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("INV-01B",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("INV-02B",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0))*1</f>
+        <f>(IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("COM-01C",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_sim1'!$G$2:$G$69,MATCH("INV-01B",'Catalogo_Numerico_sim1'!$A$2:$A$69,0)),0))*1</f>
         <v/>
       </c>
       <c r="EP5" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="EQ5" s="0">
-        <f>DT5+DU5+DV5+DW5+L5+EL5+EM5+EN5+EO5+EP5</f>
-        <v/>
+      <c r="EQ5" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="ER5" s="0">
-        <f>EJ5-EQ5</f>
+        <f>DT5+DU5+DV5+DW5+L5+EL5+EM5+EN5+EO5+EP5+EQ5</f>
         <v/>
       </c>
       <c r="ES5" s="0">
+        <f>EJ5-ER5</f>
+        <v/>
+      </c>
+      <c r="ET5" s="0">
         <f>OR(AND('Lotes_Pipeline_sim1'!C11="SEG-03",'Lotes_Pipeline_sim1'!H11&gt;0,'Lotes_Pipeline_sim1'!J11&lt;4),AND('Lotes_Pipeline_sim1'!C12="SEG-03",'Lotes_Pipeline_sim1'!H12&gt;0,'Lotes_Pipeline_sim1'!J12&lt;4),AND('Lotes_Pipeline_sim1'!C13="SEG-03",'Lotes_Pipeline_sim1'!H13&gt;0,'Lotes_Pipeline_sim1'!J13&lt;4))</f>
         <v/>
       </c>
-      <c r="ET5" s="0">
+      <c r="EU5" s="0">
         <f>OR(AND('Lotes_Pipeline_sim1'!C11="SEG-03",'Lotes_Pipeline_sim1'!H11&gt;0,'Lotes_Pipeline_sim1'!J11&gt;=7),AND('Lotes_Pipeline_sim1'!C12="SEG-03",'Lotes_Pipeline_sim1'!H12&gt;0,'Lotes_Pipeline_sim1'!J12&gt;=7),AND('Lotes_Pipeline_sim1'!C13="SEG-03",'Lotes_Pipeline_sim1'!H13&gt;0,'Lotes_Pipeline_sim1'!J13&gt;=7))</f>
         <v/>
       </c>
-      <c r="EU5" s="0">
+      <c r="EV5" s="0">
         <f>AF5&lt;4</f>
         <v/>
       </c>
-      <c r="EV5" s="0">
+      <c r="EW5" s="0">
         <f>AM5&gt;=2</f>
         <v/>
       </c>
-      <c r="EW5" s="0">
+      <c r="EX5" s="0">
         <f>AH5&lt;3</f>
         <v/>
       </c>
-      <c r="EX5" s="0">
+      <c r="EY5" s="0">
         <f>I5&gt;CE5</f>
         <v/>
       </c>
-      <c r="EY5" s="0">
+      <c r="EZ5" s="0">
         <f>CZ5&gt;EI5</f>
         <v/>
       </c>
-      <c r="EZ5" s="0">
+      <c r="FA5" s="0">
         <f>AND(K5=0,AF5&lt;5)</f>
         <v/>
       </c>
-      <c r="FA5" s="0" t="n">
+      <c r="FB5" t="n">
         <v>1000000</v>
       </c>
-      <c r="FB5" s="0">
+      <c r="FC5">
         <f>1*2500*(1+0.03+0.02)+1*3500*(1+0.03+0.02)+1*1200*(1+0.03+0.02)+1*300*(1+0+0.01)</f>
         <v/>
       </c>
-      <c r="FC5" s="0">
+      <c r="FD5">
         <f>1*2500+1*3500+1*1200+1*300</f>
         <v/>
       </c>
-      <c r="FD5" s="0">
-        <f>(CF5*25+CH5*45+CJ5*80+CL5*4+CN5*9+CP5*2+CR5*4+CT5*7)*0.8924</f>
-        <v/>
-      </c>
-      <c r="FE5" s="0">
-        <f>(DC5*25+DE5*45+DG5*80+DJ5*4+DL5*9+DO5*2+DQ5*4+DS5*7)*0.8924</f>
-        <v/>
-      </c>
-      <c r="FF5" s="0">
-        <f>FA5</f>
-        <v/>
-      </c>
-      <c r="FG5" s="0">
+      <c r="FE5">
+        <f>(CF5*25+CH5*45+CJ5*80+CL5*4+CN5*9+CP5*2+CR5*4+CT5*7)*0.92</f>
+        <v/>
+      </c>
+      <c r="FF5">
+        <f>(DC5*25+DE5*45+DG5*80+DJ5*4+DL5*9+DO5*2+DQ5*4+DS5*7)*0.92</f>
+        <v/>
+      </c>
+      <c r="FG5">
+        <f>FB5</f>
+        <v/>
+      </c>
+      <c r="FH5">
         <f>(1+AR5/100)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="FH5" s="0">
-        <f>0*0+AP5*FG5</f>
-        <v/>
-      </c>
-      <c r="FI5" s="0">
-        <f>IFERROR(FH5/(0+AP5),0)</f>
-        <v/>
-      </c>
-      <c r="FJ5" s="0">
-        <f>FH5*1</f>
-        <v/>
-      </c>
-      <c r="FK5" s="0">
-        <f>EQ5-DW5-DU5+FD5+FJ5</f>
-        <v/>
-      </c>
-      <c r="FL5" s="0">
-        <f>FF5+EJ5+AP5-FK5-FB5</f>
-        <v/>
-      </c>
-      <c r="FM5" s="0">
+      <c r="FI5">
+        <f>0*0+AP5*FH5</f>
+        <v/>
+      </c>
+      <c r="FJ5">
+        <f>IFERROR(FI5/(0+AP5),0)</f>
+        <v/>
+      </c>
+      <c r="FK5">
+        <f>FI5*1</f>
+        <v/>
+      </c>
+      <c r="FL5">
+        <f>ER5-DW5-DU5+FE5+FK5</f>
+        <v/>
+      </c>
+      <c r="FM5">
+        <f>FG5+EJ5+AP5-FL5-FC5</f>
+        <v/>
+      </c>
+      <c r="FN5">
         <f>0+DW5</f>
         <v/>
       </c>
-      <c r="FN5" s="0">
-        <f>0+FC5</f>
-        <v/>
-      </c>
-      <c r="FO5" s="0">
-        <f>FN5-FM5</f>
-        <v/>
-      </c>
-      <c r="FP5" s="0">
+      <c r="FO5">
+        <f>0+FD5</f>
+        <v/>
+      </c>
+      <c r="FP5">
+        <f>FO5-FN5</f>
+        <v/>
+      </c>
+      <c r="FQ5">
         <f>EJ5</f>
         <v/>
       </c>
-      <c r="FQ5" s="0">
+      <c r="FR5">
         <f>EJ5</f>
         <v/>
       </c>
-      <c r="FR5" s="0">
-        <f>EQ5+FJ5</f>
-        <v/>
-      </c>
-      <c r="FS5" s="0">
-        <f>ER5-FJ5</f>
-        <v/>
-      </c>
-      <c r="FT5" s="0">
+      <c r="FS5">
+        <f>ER5+FK5</f>
+        <v/>
+      </c>
+      <c r="FT5">
+        <f>ES5-FK5</f>
+        <v/>
+      </c>
+      <c r="FU5">
         <f>DW5</f>
         <v/>
       </c>
-      <c r="FU5" s="0">
+      <c r="FV5">
+        <f>FK5</f>
+        <v/>
+      </c>
+      <c r="FW5">
+        <f>ER5</f>
+        <v/>
+      </c>
+      <c r="FX5">
+        <f>FG5</f>
+        <v/>
+      </c>
+      <c r="FY5">
+        <f>EJ5+AP5</f>
+        <v/>
+      </c>
+      <c r="FZ5">
+        <f>FL5+FC5</f>
+        <v/>
+      </c>
+      <c r="GA5">
+        <f>FM5</f>
+        <v/>
+      </c>
+      <c r="GB5">
+        <f>FG5</f>
+        <v/>
+      </c>
+      <c r="GC5">
+        <f>EJ5</f>
+        <v/>
+      </c>
+      <c r="GD5">
+        <f>FL5</f>
+        <v/>
+      </c>
+      <c r="GE5">
+        <f>FC5</f>
+        <v/>
+      </c>
+      <c r="GF5">
+        <f>AP5</f>
+        <v/>
+      </c>
+      <c r="GG5">
+        <f>EJ5-FL5</f>
+        <v/>
+      </c>
+      <c r="GH5">
+        <f>-FC5</f>
+        <v/>
+      </c>
+      <c r="GI5">
+        <f>FM5-FG5</f>
+        <v/>
+      </c>
+      <c r="GJ5">
+        <f>FM5</f>
+        <v/>
+      </c>
+      <c r="GK5">
+        <f>FM5</f>
+        <v/>
+      </c>
+      <c r="GL5">
+        <f>FP5</f>
+        <v/>
+      </c>
+      <c r="GM5">
+        <f>FF5</f>
+        <v/>
+      </c>
+      <c r="GN5">
+        <f>FM5+FP5+FF5</f>
+        <v/>
+      </c>
+      <c r="GO5">
+        <f>AS5</f>
+        <v/>
+      </c>
+      <c r="GP5">
+        <f>FM5+FP5+FF5-AS5</f>
+        <v/>
+      </c>
+      <c r="GQ5">
+        <f>FM5+FP5+FF5</f>
+        <v/>
+      </c>
+      <c r="GR5">
+        <f>AP5</f>
+        <v/>
+      </c>
+      <c r="GS5">
+        <f>AR5</f>
+        <v/>
+      </c>
+      <c r="GT5">
+        <f>AS5</f>
+        <v/>
+      </c>
+      <c r="GU5">
+        <f>AT5</f>
+        <v/>
+      </c>
+      <c r="GV5">
         <f>FJ5</f>
         <v/>
       </c>
-      <c r="FV5" s="0">
-        <f>EQ5</f>
-        <v/>
-      </c>
-      <c r="FW5" s="0">
-        <f>FF5</f>
-        <v/>
-      </c>
-      <c r="FX5" s="0">
-        <f>EJ5+AP5</f>
-        <v/>
-      </c>
-      <c r="FY5" s="0">
-        <f>FK5+FB5</f>
-        <v/>
-      </c>
-      <c r="FZ5" s="0">
-        <f>FL5</f>
-        <v/>
-      </c>
-      <c r="GA5" s="0">
-        <f>FF5</f>
-        <v/>
-      </c>
-      <c r="GB5" s="0">
-        <f>EJ5</f>
-        <v/>
-      </c>
-      <c r="GC5" s="0">
+      <c r="GW5">
         <f>FK5</f>
-        <v/>
-      </c>
-      <c r="GD5" s="0">
-        <f>FB5</f>
-        <v/>
-      </c>
-      <c r="GE5" s="0">
-        <f>AP5</f>
-        <v/>
-      </c>
-      <c r="GF5" s="0">
-        <f>EJ5-FK5</f>
-        <v/>
-      </c>
-      <c r="GG5" s="0">
-        <f>-FB5</f>
-        <v/>
-      </c>
-      <c r="GH5" s="0">
-        <f>FL5-FF5</f>
-        <v/>
-      </c>
-      <c r="GI5" s="0">
-        <f>FL5</f>
-        <v/>
-      </c>
-      <c r="GJ5" s="0">
-        <f>FL5</f>
-        <v/>
-      </c>
-      <c r="GK5" s="0">
-        <f>FO5</f>
-        <v/>
-      </c>
-      <c r="GL5" s="0">
-        <f>FE5</f>
-        <v/>
-      </c>
-      <c r="GM5" s="0">
-        <f>FL5+FO5+FE5</f>
-        <v/>
-      </c>
-      <c r="GN5" s="0">
-        <f>AS5</f>
-        <v/>
-      </c>
-      <c r="GO5" s="0">
-        <f>FL5+FO5+FE5-AS5</f>
-        <v/>
-      </c>
-      <c r="GP5" s="0">
-        <f>FL5+FO5+FE5</f>
-        <v/>
-      </c>
-      <c r="GQ5" s="0">
-        <f>AP5</f>
-        <v/>
-      </c>
-      <c r="GR5" s="0">
-        <f>AR5</f>
-        <v/>
-      </c>
-      <c r="GS5" s="0">
-        <f>AS5</f>
-        <v/>
-      </c>
-      <c r="GT5" s="0">
-        <f>AT5</f>
-        <v/>
-      </c>
-      <c r="GU5" s="0">
-        <f>FI5</f>
-        <v/>
-      </c>
-      <c r="GV5" s="0">
-        <f>FJ5</f>
         <v/>
       </c>
     </row>

--- a/tests/oracle/ORACULO_sim1.xlsx
+++ b/tests/oracle/ORACULO_sim1.xlsx
@@ -3723,11 +3723,11 @@
         </is>
       </c>
       <c r="D7" s="186">
-        <f>B9&gt;B10</f>
+        <f>B11&gt;B10</f>
         <v/>
       </c>
       <c r="E7" s="186">
-        <f>IF(D7,0.25*B13*MIN(1,IFERROR((B9-B10)/B10,0)),0)</f>
+        <f>IF(D7,0.25*B13*MIN(1,IFERROR((B11-B10)/B10,0)),0)</f>
         <v/>
       </c>
       <c r="F7" s="186">
@@ -6125,7 +6125,7 @@
         <v/>
       </c>
       <c r="ED2" s="0">
-        <f>ROUND(MIN(100,AI2*10),0)</f>
+        <f>IFERROR(ROUND(DY2/SUMIF($C$2:$C$5,"1|SEG-01",$DY$2:$DY$5)*100,0),0)</f>
         <v/>
       </c>
       <c r="EE2" s="0">
@@ -6161,7 +6161,7 @@
         <v/>
       </c>
       <c r="EM2" s="0">
-        <f>IF(I2&gt;CE2,0.25*DT2*IFERROR(MIN(1,(I2-CE2)/CE2),1),0)</f>
+        <f>IF(CZ2&gt;CE2,0.25*DT2*IFERROR(MIN(1,(CZ2-CE2)/CE2),1),0)</f>
         <v/>
       </c>
       <c r="EN2" s="0">
@@ -6208,7 +6208,7 @@
         <v/>
       </c>
       <c r="EY2" s="0">
-        <f>I2&gt;CE2</f>
+        <f>CZ2&gt;CE2</f>
         <v/>
       </c>
       <c r="EZ2" s="0">
@@ -6903,7 +6903,7 @@
         <v/>
       </c>
       <c r="ED3" s="0">
-        <f>ROUND(MIN(100,AI3*10),0)</f>
+        <f>IFERROR(ROUND(DY3/SUMIF($C$2:$C$5,"1|SEG-01",$DY$2:$DY$5)*100,0),0)</f>
         <v/>
       </c>
       <c r="EE3" s="0">
@@ -6939,7 +6939,7 @@
         <v/>
       </c>
       <c r="EM3" s="0">
-        <f>IF(I3&gt;CE3,0.25*DT3*IFERROR(MIN(1,(I3-CE3)/CE3),1),0)</f>
+        <f>IF(CZ3&gt;CE3,0.25*DT3*IFERROR(MIN(1,(CZ3-CE3)/CE3),1),0)</f>
         <v/>
       </c>
       <c r="EN3" s="0">
@@ -6986,7 +6986,7 @@
         <v/>
       </c>
       <c r="EY3" s="0">
-        <f>I3&gt;CE3</f>
+        <f>CZ3&gt;CE3</f>
         <v/>
       </c>
       <c r="EZ3" s="0">
@@ -7681,7 +7681,7 @@
         <v/>
       </c>
       <c r="ED4" s="0">
-        <f>ROUND(MIN(100,AI4*10),0)</f>
+        <f>IFERROR(ROUND(DY4/SUMIF($C$2:$C$5,"1|SEG-01",$DY$2:$DY$5)*100,0),0)</f>
         <v/>
       </c>
       <c r="EE4" s="0">
@@ -7717,7 +7717,7 @@
         <v/>
       </c>
       <c r="EM4" s="0">
-        <f>IF(I4&gt;CE4,0.25*DT4*IFERROR(MIN(1,(I4-CE4)/CE4),1),0)</f>
+        <f>IF(CZ4&gt;CE4,0.25*DT4*IFERROR(MIN(1,(CZ4-CE4)/CE4),1),0)</f>
         <v/>
       </c>
       <c r="EN4" s="0">
@@ -7764,7 +7764,7 @@
         <v/>
       </c>
       <c r="EY4" s="0">
-        <f>I4&gt;CE4</f>
+        <f>CZ4&gt;CE4</f>
         <v/>
       </c>
       <c r="EZ4" s="0">
@@ -8459,7 +8459,7 @@
         <v/>
       </c>
       <c r="ED5" s="0">
-        <f>ROUND(MIN(100,AI5*10),0)</f>
+        <f>IFERROR(ROUND(DY5/SUMIF($C$2:$C$5,"1|SEG-01",$DY$2:$DY$5)*100,0),0)</f>
         <v/>
       </c>
       <c r="EE5" s="0">
@@ -8495,7 +8495,7 @@
         <v/>
       </c>
       <c r="EM5" s="0">
-        <f>IF(I5&gt;CE5,0.25*DT5*IFERROR(MIN(1,(I5-CE5)/CE5),1),0)</f>
+        <f>IF(CZ5&gt;CE5,0.25*DT5*IFERROR(MIN(1,(CZ5-CE5)/CE5),1),0)</f>
         <v/>
       </c>
       <c r="EN5" s="0">
@@ -8542,7 +8542,7 @@
         <v/>
       </c>
       <c r="EY5" s="0">
-        <f>I5&gt;CE5</f>
+        <f>CZ5&gt;CE5</f>
         <v/>
       </c>
       <c r="EZ5" s="0">
@@ -15175,7 +15175,7 @@
         <v/>
       </c>
       <c r="H2" s="0">
-        <f>IFERROR(ROUND(G2/SUMIFS($G$2:$G$13,$D$2:$D$13,D2,$E$2:$E$13,TRUE())*100,0),0)</f>
+        <f>IFERROR(ROUND(G2/SUMIFS($G$2:$G$13,$D$2:$D$13,"1|SEG-01",$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
       <c r="I2" s="0">
@@ -15235,7 +15235,7 @@
         <v/>
       </c>
       <c r="H3" s="0">
-        <f>IFERROR(ROUND(G3/SUMIFS($G$2:$G$13,$D$2:$D$13,D3,$E$2:$E$13,TRUE())*100,0),0)</f>
+        <f>IFERROR(ROUND(G3/SUMIFS($G$2:$G$13,$D$2:$D$13,"1|SEG-01",$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
       <c r="I3" s="0">
@@ -15295,7 +15295,7 @@
         <v/>
       </c>
       <c r="H4" s="0">
-        <f>IFERROR(ROUND(G4/SUMIFS($G$2:$G$13,$D$2:$D$13,D4,$E$2:$E$13,TRUE())*100,0),0)</f>
+        <f>IFERROR(ROUND(G4/SUMIFS($G$2:$G$13,$D$2:$D$13,"1|SEG-01",$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
       <c r="I4" s="0">
@@ -15355,7 +15355,7 @@
         <v/>
       </c>
       <c r="H5" s="0">
-        <f>IFERROR(ROUND(G5/SUMIFS($G$2:$G$13,$D$2:$D$13,D5,$E$2:$E$13,TRUE())*100,0),0)</f>
+        <f>IFERROR(ROUND(G5/SUMIFS($G$2:$G$13,$D$2:$D$13,"1|SEG-01",$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
       <c r="I5" s="0">
@@ -15415,7 +15415,7 @@
         <v/>
       </c>
       <c r="H6" s="0">
-        <f>IFERROR(ROUND(G6/SUMIFS($G$2:$G$13,$D$2:$D$13,D6,$E$2:$E$13,TRUE())*100,0),0)</f>
+        <f>IFERROR(ROUND(G6/SUMIFS($G$2:$G$13,$D$2:$D$13,"1|SEG-01",$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
       <c r="I6" s="0">
@@ -15475,7 +15475,7 @@
         <v/>
       </c>
       <c r="H7" s="0">
-        <f>IFERROR(ROUND(G7/SUMIFS($G$2:$G$13,$D$2:$D$13,D7,$E$2:$E$13,TRUE())*100,0),0)</f>
+        <f>IFERROR(ROUND(G7/SUMIFS($G$2:$G$13,$D$2:$D$13,"1|SEG-01",$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
       <c r="I7" s="0">
@@ -15535,7 +15535,7 @@
         <v/>
       </c>
       <c r="H8" s="0">
-        <f>IFERROR(ROUND(G8/SUMIFS($G$2:$G$13,$D$2:$D$13,D8,$E$2:$E$13,TRUE())*100,0),0)</f>
+        <f>IFERROR(ROUND(G8/SUMIFS($G$2:$G$13,$D$2:$D$13,"1|SEG-01",$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
       <c r="I8" s="0">
@@ -15595,7 +15595,7 @@
         <v/>
       </c>
       <c r="H9" s="0">
-        <f>IFERROR(ROUND(G9/SUMIFS($G$2:$G$13,$D$2:$D$13,D9,$E$2:$E$13,TRUE())*100,0),0)</f>
+        <f>IFERROR(ROUND(G9/SUMIFS($G$2:$G$13,$D$2:$D$13,"1|SEG-01",$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
       <c r="I9" s="0">
@@ -15655,7 +15655,7 @@
         <v/>
       </c>
       <c r="H10" s="0">
-        <f>IFERROR(ROUND(G10/SUMIFS($G$2:$G$13,$D$2:$D$13,D10,$E$2:$E$13,TRUE())*100,0),0)</f>
+        <f>IFERROR(ROUND(G10/SUMIFS($G$2:$G$13,$D$2:$D$13,"1|SEG-01",$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
       <c r="I10" s="0">
@@ -15715,7 +15715,7 @@
         <v/>
       </c>
       <c r="H11" s="0">
-        <f>IFERROR(ROUND(G11/SUMIFS($G$2:$G$13,$D$2:$D$13,D11,$E$2:$E$13,TRUE())*100,0),0)</f>
+        <f>IFERROR(ROUND(G11/SUMIFS($G$2:$G$13,$D$2:$D$13,"1|SEG-01",$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
       <c r="I11" s="0">
@@ -15775,7 +15775,7 @@
         <v/>
       </c>
       <c r="H12" s="0">
-        <f>IFERROR(ROUND(G12/SUMIFS($G$2:$G$13,$D$2:$D$13,D12,$E$2:$E$13,TRUE())*100,0),0)</f>
+        <f>IFERROR(ROUND(G12/SUMIFS($G$2:$G$13,$D$2:$D$13,"1|SEG-01",$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
       <c r="I12" s="0">
@@ -15835,7 +15835,7 @@
         <v/>
       </c>
       <c r="H13" s="0">
-        <f>IFERROR(ROUND(G13/SUMIFS($G$2:$G$13,$D$2:$D$13,D13,$E$2:$E$13,TRUE())*100,0),0)</f>
+        <f>IFERROR(ROUND(G13/SUMIFS($G$2:$G$13,$D$2:$D$13,"1|SEG-01",$E$2:$E$13,TRUE())*100,0),0)</f>
         <v/>
       </c>
       <c r="I13" s="0">
